--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="F14" t="n">
-        <v>5.81</v>
+        <v>4.85</v>
       </c>
       <c r="G14" t="n">
-        <v>137.6</v>
+        <v>122.8</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>36.8</v>
+        <v>-10.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-26.99</v>
+        <v>-32.59</v>
       </c>
       <c r="L14" t="n">
-        <v>45.63</v>
+        <v>34.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:32:03</t>
+          <t>07:31:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,13 +667,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="F15" t="n">
-        <v>5.61</v>
+        <v>5.59</v>
       </c>
       <c r="G15" t="n">
-        <v>136</v>
+        <v>125.5</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -682,19 +682,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.38</v>
+        <v>49.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-82.42</v>
+        <v>-59.31</v>
       </c>
       <c r="L15" t="n">
-        <v>94.08</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:33:46</t>
+          <t>07:34:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="F16" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="G16" t="n">
-        <v>128.5</v>
+        <v>145.7</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>20.73</v>
+        <v>74.17</v>
       </c>
       <c r="K16" t="n">
-        <v>-145.24</v>
+        <v>21.84</v>
       </c>
       <c r="L16" t="n">
-        <v>146.71</v>
+        <v>77.31999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:37:32</t>
+          <t>07:38:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="F17" t="n">
-        <v>4.95</v>
+        <v>5.76</v>
       </c>
       <c r="G17" t="n">
-        <v>137.4</v>
+        <v>129.9</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-31.66</v>
+        <v>-21.62</v>
       </c>
       <c r="K17" t="n">
-        <v>7.57</v>
+        <v>-177.25</v>
       </c>
       <c r="L17" t="n">
-        <v>32.55</v>
+        <v>178.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:38:33</t>
+          <t>07:39:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="F18" t="n">
-        <v>5.99</v>
+        <v>6.08</v>
       </c>
       <c r="G18" t="n">
-        <v>133.1</v>
+        <v>132.6</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-80.15000000000001</v>
+        <v>-55.59</v>
       </c>
       <c r="K18" t="n">
-        <v>-85.93000000000001</v>
+        <v>-38.13</v>
       </c>
       <c r="L18" t="n">
-        <v>117.51</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:40:03</t>
+          <t>07:41:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="F19" t="n">
-        <v>5.34</v>
+        <v>5.62</v>
       </c>
       <c r="G19" t="n">
-        <v>134.9</v>
+        <v>136</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>197.04</v>
+        <v>31.15</v>
       </c>
       <c r="K19" t="n">
-        <v>34.46</v>
+        <v>-38.98</v>
       </c>
       <c r="L19" t="n">
-        <v>200.03</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:43:52</t>
+          <t>07:46:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="F20" t="n">
-        <v>5.22</v>
+        <v>4.65</v>
       </c>
       <c r="G20" t="n">
-        <v>113.4</v>
+        <v>135.4</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-222.57</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>13.37</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>222.98</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:45:13</t>
+          <t>07:48:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="F21" t="n">
-        <v>5.61</v>
+        <v>4.91</v>
       </c>
       <c r="G21" t="n">
-        <v>129.6</v>
+        <v>119.5</v>
       </c>
       <c r="H21" t="n">
-        <v>92.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>90.02</v>
+        <v>-48.88</v>
       </c>
       <c r="K21" t="n">
-        <v>-89.45</v>
+        <v>119.78</v>
       </c>
       <c r="L21" t="n">
-        <v>126.91</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:47:29</t>
+          <t>07:50:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="F22" t="n">
-        <v>5.91</v>
+        <v>5.74</v>
       </c>
       <c r="G22" t="n">
-        <v>136.5</v>
+        <v>133</v>
       </c>
       <c r="H22" t="n">
-        <v>98.09999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>317.86</v>
+        <v>-150.18</v>
       </c>
       <c r="K22" t="n">
-        <v>168.86</v>
+        <v>92.37</v>
       </c>
       <c r="L22" t="n">
-        <v>359.93</v>
+        <v>176.32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:51:51</t>
+          <t>07:56:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="F23" t="n">
-        <v>6.81</v>
+        <v>5.63</v>
       </c>
       <c r="G23" t="n">
-        <v>146</v>
+        <v>128.2</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>450</v>
+        <v>-164.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-215.02</v>
+        <v>-268.66</v>
       </c>
       <c r="L23" t="n">
-        <v>498.73</v>
+        <v>315.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:53:41</t>
+          <t>07:58:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="F24" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="G24" t="n">
-        <v>130.1</v>
+        <v>131.8</v>
       </c>
       <c r="H24" t="n">
-        <v>95.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>144.64</v>
+        <v>188.77</v>
       </c>
       <c r="K24" t="n">
-        <v>368.91</v>
+        <v>176.42</v>
       </c>
       <c r="L24" t="n">
-        <v>396.25</v>
+        <v>258.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:55:34</t>
+          <t>07:59:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="F25" t="n">
-        <v>5.65</v>
+        <v>6.26</v>
       </c>
       <c r="G25" t="n">
-        <v>114.8</v>
+        <v>119.4</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-75.05</v>
+        <v>87.11</v>
       </c>
       <c r="K25" t="n">
-        <v>-68.22</v>
+        <v>-283.71</v>
       </c>
       <c r="L25" t="n">
-        <v>101.42</v>
+        <v>296.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:59:57</t>
+          <t>08:05:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="F26" t="n">
-        <v>5.5</v>
+        <v>5.93</v>
       </c>
       <c r="G26" t="n">
-        <v>133.4</v>
+        <v>131.3</v>
       </c>
       <c r="H26" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>747.46</v>
+        <v>142.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-201.35</v>
+        <v>-105.19</v>
       </c>
       <c r="L26" t="n">
-        <v>774.1</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:00:56</t>
+          <t>08:06:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>5.65</v>
+        <v>6.37</v>
       </c>
       <c r="G27" t="n">
-        <v>124.5</v>
+        <v>155.1</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>88.93000000000001</v>
+        <v>-33.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.1</v>
+        <v>-151.75</v>
       </c>
       <c r="L27" t="n">
-        <v>89.20999999999999</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:03:00</t>
+          <t>08:08:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="F28" t="n">
-        <v>5.79</v>
+        <v>5.09</v>
       </c>
       <c r="G28" t="n">
-        <v>141.4</v>
+        <v>113.9</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>441.3</v>
+        <v>43.37</v>
       </c>
       <c r="K28" t="n">
-        <v>-119.26</v>
+        <v>-314.45</v>
       </c>
       <c r="L28" t="n">
-        <v>457.13</v>
+        <v>317.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:15:49</t>
+          <t>08:20:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="F29" t="n">
-        <v>5.95</v>
+        <v>5.53</v>
       </c>
       <c r="G29" t="n">
-        <v>135.9</v>
+        <v>126.3</v>
       </c>
       <c r="H29" t="n">
-        <v>99.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>18.33</v>
+        <v>37.06</v>
       </c>
       <c r="K29" t="n">
-        <v>43.61</v>
+        <v>49.12</v>
       </c>
       <c r="L29" t="n">
-        <v>47.3</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:17:17</t>
+          <t>08:22:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="F30" t="n">
-        <v>6.21</v>
+        <v>5.86</v>
       </c>
       <c r="G30" t="n">
-        <v>122.9</v>
+        <v>126.7</v>
       </c>
       <c r="H30" t="n">
-        <v>99.5</v>
+        <v>96.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>25.29</v>
+        <v>-0.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.03</v>
+        <v>-23.06</v>
       </c>
       <c r="L30" t="n">
-        <v>25.47</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:18:57</t>
+          <t>08:23:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="F31" t="n">
-        <v>5.66</v>
+        <v>5.34</v>
       </c>
       <c r="G31" t="n">
-        <v>134.9</v>
+        <v>126.9</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>1.27</v>
+        <v>76.52</v>
       </c>
       <c r="K31" t="n">
-        <v>5.43</v>
+        <v>-85.34</v>
       </c>
       <c r="L31" t="n">
-        <v>5.58</v>
+        <v>114.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:23:20</t>
+          <t>08:29:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="F32" t="n">
-        <v>6.41</v>
+        <v>6.02</v>
       </c>
       <c r="G32" t="n">
-        <v>120.3</v>
+        <v>132.2</v>
       </c>
       <c r="H32" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>65.48</v>
+        <v>57.33</v>
       </c>
       <c r="K32" t="n">
-        <v>13.57</v>
+        <v>-142.51</v>
       </c>
       <c r="L32" t="n">
-        <v>66.87</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:24:39</t>
+          <t>08:31:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="F33" t="n">
-        <v>5.67</v>
+        <v>5.47</v>
       </c>
       <c r="G33" t="n">
-        <v>122.5</v>
+        <v>139.1</v>
       </c>
       <c r="H33" t="n">
-        <v>98.2</v>
+        <v>93.5</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-84.52</v>
+        <v>-0.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-58.83</v>
+        <v>-36.27</v>
       </c>
       <c r="L33" t="n">
-        <v>102.98</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:26:03</t>
+          <t>08:33:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,13 +1465,13 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="F34" t="n">
-        <v>5.88</v>
+        <v>5.76</v>
       </c>
       <c r="G34" t="n">
-        <v>136.3</v>
+        <v>127.5</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -1480,19 +1480,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-126.09</v>
+        <v>-46.67</v>
       </c>
       <c r="K34" t="n">
-        <v>123.3</v>
+        <v>-89.42</v>
       </c>
       <c r="L34" t="n">
-        <v>176.35</v>
+        <v>100.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:29:29</t>
+          <t>08:39:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="F35" t="n">
-        <v>5.55</v>
+        <v>6.11</v>
       </c>
       <c r="G35" t="n">
-        <v>136.1</v>
+        <v>141.9</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-253.12</v>
+        <v>-25.53</v>
       </c>
       <c r="K35" t="n">
-        <v>-42.03</v>
+        <v>37.48</v>
       </c>
       <c r="L35" t="n">
-        <v>256.59</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:30:43</t>
+          <t>08:40:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="F36" t="n">
-        <v>5.44</v>
+        <v>6.3</v>
       </c>
       <c r="G36" t="n">
-        <v>134.9</v>
+        <v>118.1</v>
       </c>
       <c r="H36" t="n">
-        <v>94.5</v>
+        <v>93.7</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.48</v>
+        <v>43.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-114.64</v>
+        <v>-47.32</v>
       </c>
       <c r="L36" t="n">
-        <v>115.82</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:33:17</t>
+          <t>08:41:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="F37" t="n">
-        <v>4.82</v>
+        <v>5.75</v>
       </c>
       <c r="G37" t="n">
-        <v>128.5</v>
+        <v>154.7</v>
       </c>
       <c r="H37" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>161.49</v>
+        <v>-214.87</v>
       </c>
       <c r="K37" t="n">
-        <v>-80.29000000000001</v>
+        <v>141.98</v>
       </c>
       <c r="L37" t="n">
-        <v>180.35</v>
+        <v>257.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:38:27</t>
+          <t>08:47:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="F38" t="n">
-        <v>5.46</v>
+        <v>5.8</v>
       </c>
       <c r="G38" t="n">
-        <v>136.1</v>
+        <v>146.3</v>
       </c>
       <c r="H38" t="n">
-        <v>95.3</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-21.73</v>
+        <v>-101.76</v>
       </c>
       <c r="K38" t="n">
-        <v>229.83</v>
+        <v>133.76</v>
       </c>
       <c r="L38" t="n">
-        <v>230.85</v>
+        <v>168.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:39:35</t>
+          <t>08:48:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F39" t="n">
-        <v>5.75</v>
+        <v>5.38</v>
       </c>
       <c r="G39" t="n">
-        <v>138.7</v>
+        <v>136.1</v>
       </c>
       <c r="H39" t="n">
-        <v>94.5</v>
+        <v>95.7</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>162.3</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-241.59</v>
+        <v>273.08</v>
       </c>
       <c r="L39" t="n">
-        <v>291.05</v>
+        <v>288.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:40:54</t>
+          <t>08:49:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="F40" t="n">
-        <v>5.97</v>
+        <v>6.3</v>
       </c>
       <c r="G40" t="n">
-        <v>140.3</v>
+        <v>133</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>133.68</v>
+        <v>231.35</v>
       </c>
       <c r="K40" t="n">
-        <v>53.09</v>
+        <v>-151.65</v>
       </c>
       <c r="L40" t="n">
-        <v>143.84</v>
+        <v>276.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:45:57</t>
+          <t>08:54:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="F41" t="n">
-        <v>5.54</v>
+        <v>5.94</v>
       </c>
       <c r="G41" t="n">
-        <v>132.9</v>
+        <v>125.7</v>
       </c>
       <c r="H41" t="n">
-        <v>93.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>667.2</v>
+        <v>-366.77</v>
       </c>
       <c r="K41" t="n">
-        <v>-433.76</v>
+        <v>-35.3</v>
       </c>
       <c r="L41" t="n">
-        <v>795.8099999999999</v>
+        <v>368.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:47:20</t>
+          <t>08:56:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="F42" t="n">
-        <v>5.91</v>
+        <v>5.39</v>
       </c>
       <c r="G42" t="n">
-        <v>140.7</v>
+        <v>136.3</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-101.15</v>
+        <v>259.15</v>
       </c>
       <c r="K42" t="n">
-        <v>76.34</v>
+        <v>-159.62</v>
       </c>
       <c r="L42" t="n">
-        <v>126.72</v>
+        <v>304.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:48:12</t>
+          <t>08:58:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="F43" t="n">
-        <v>5.42</v>
+        <v>5.27</v>
       </c>
       <c r="G43" t="n">
-        <v>119.7</v>
+        <v>116.8</v>
       </c>
       <c r="H43" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>19.31</v>
+        <v>217.44</v>
       </c>
       <c r="K43" t="n">
-        <v>-246.69</v>
+        <v>-487.64</v>
       </c>
       <c r="L43" t="n">
-        <v>247.44</v>
+        <v>533.9299999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:57:01</t>
+          <t>09:07:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="F44" t="n">
-        <v>6.6</v>
+        <v>5.84</v>
       </c>
       <c r="G44" t="n">
-        <v>124.1</v>
+        <v>129.1</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-106.41</v>
+        <v>-6.19</v>
       </c>
       <c r="K44" t="n">
-        <v>-27.46</v>
+        <v>-144.39</v>
       </c>
       <c r="L44" t="n">
-        <v>109.89</v>
+        <v>144.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:58:05</t>
+          <t>09:08:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="F45" t="n">
-        <v>5.6</v>
+        <v>5.35</v>
       </c>
       <c r="G45" t="n">
-        <v>144.3</v>
+        <v>130.2</v>
       </c>
       <c r="H45" t="n">
-        <v>98.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>2.45</v>
+        <v>-11.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-68.53</v>
+        <v>-50.2</v>
       </c>
       <c r="L45" t="n">
-        <v>68.58</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:59:03</t>
+          <t>09:10:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="F46" t="n">
-        <v>4.94</v>
+        <v>5.45</v>
       </c>
       <c r="G46" t="n">
-        <v>140.5</v>
+        <v>128.6</v>
       </c>
       <c r="H46" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>9.960000000000001</v>
+        <v>-17.85</v>
       </c>
       <c r="K46" t="n">
-        <v>16.46</v>
+        <v>43.43</v>
       </c>
       <c r="L46" t="n">
-        <v>19.24</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:04:04</t>
+          <t>09:14:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="F47" t="n">
-        <v>5.45</v>
+        <v>6.12</v>
       </c>
       <c r="G47" t="n">
-        <v>139.2</v>
+        <v>133.3</v>
       </c>
       <c r="H47" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-16.27</v>
+        <v>-39.46</v>
       </c>
       <c r="K47" t="n">
-        <v>116.25</v>
+        <v>-7.61</v>
       </c>
       <c r="L47" t="n">
-        <v>117.39</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:06:16</t>
+          <t>09:15:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.02</v>
+        <v>2.03</v>
       </c>
       <c r="F48" t="n">
-        <v>5.47</v>
+        <v>6.36</v>
       </c>
       <c r="G48" t="n">
-        <v>137.5</v>
+        <v>127.8</v>
       </c>
       <c r="H48" t="n">
-        <v>98.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.140000000000001</v>
+        <v>131.25</v>
       </c>
       <c r="K48" t="n">
-        <v>-31.34</v>
+        <v>251.91</v>
       </c>
       <c r="L48" t="n">
-        <v>32.38</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:08:34</t>
+          <t>09:17:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="F49" t="n">
-        <v>5.5</v>
+        <v>6.61</v>
       </c>
       <c r="G49" t="n">
-        <v>135.9</v>
+        <v>142.5</v>
       </c>
       <c r="H49" t="n">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>80.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="K49" t="n">
-        <v>-87.39</v>
+        <v>-78.66</v>
       </c>
       <c r="L49" t="n">
-        <v>119.09</v>
+        <v>95.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:14:14</t>
+          <t>09:20:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="F50" t="n">
-        <v>5.99</v>
+        <v>4.95</v>
       </c>
       <c r="G50" t="n">
-        <v>125.6</v>
+        <v>137.7</v>
       </c>
       <c r="H50" t="n">
-        <v>96.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>110.96</v>
+        <v>40.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-116.26</v>
+        <v>47.38</v>
       </c>
       <c r="L50" t="n">
-        <v>160.72</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:16:26</t>
+          <t>09:22:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>5.12</v>
+        <v>6.4</v>
       </c>
       <c r="G51" t="n">
-        <v>121.3</v>
+        <v>145.5</v>
       </c>
       <c r="H51" t="n">
-        <v>96.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-173.55</v>
+        <v>20.62</v>
       </c>
       <c r="K51" t="n">
-        <v>-24.21</v>
+        <v>-25.68</v>
       </c>
       <c r="L51" t="n">
-        <v>175.23</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:18:28</t>
+          <t>09:23:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="F52" t="n">
-        <v>5.91</v>
+        <v>5.48</v>
       </c>
       <c r="G52" t="n">
-        <v>132.4</v>
+        <v>136.1</v>
       </c>
       <c r="H52" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-53.8</v>
+        <v>-100.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-126.03</v>
+        <v>-27.47</v>
       </c>
       <c r="L52" t="n">
-        <v>137.03</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:22:33</t>
+          <t>09:27:40</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="F53" t="n">
-        <v>5.67</v>
+        <v>6.11</v>
       </c>
       <c r="G53" t="n">
-        <v>130</v>
+        <v>133.7</v>
       </c>
       <c r="H53" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>118.69</v>
+        <v>-238</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.92</v>
+        <v>-201.55</v>
       </c>
       <c r="L53" t="n">
-        <v>121.93</v>
+        <v>311.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:24:19</t>
+          <t>09:29:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="F54" t="n">
-        <v>6.11</v>
+        <v>6.38</v>
       </c>
       <c r="G54" t="n">
-        <v>122.7</v>
+        <v>133.1</v>
       </c>
       <c r="H54" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-72.59</v>
+        <v>-98.3</v>
       </c>
       <c r="K54" t="n">
-        <v>232.06</v>
+        <v>-72.2</v>
       </c>
       <c r="L54" t="n">
-        <v>243.15</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:25:45</t>
+          <t>09:31:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="F55" t="n">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="G55" t="n">
-        <v>132.6</v>
+        <v>141.8</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>171.25</v>
+        <v>335.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-171.16</v>
+        <v>3.87</v>
       </c>
       <c r="L55" t="n">
-        <v>242.12</v>
+        <v>335.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:30:06</t>
+          <t>09:36:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="F56" t="n">
-        <v>5.69</v>
+        <v>6.06</v>
       </c>
       <c r="G56" t="n">
-        <v>125.5</v>
+        <v>132.2</v>
       </c>
       <c r="H56" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-322.38</v>
+        <v>13.27</v>
       </c>
       <c r="K56" t="n">
-        <v>431.08</v>
+        <v>-171.31</v>
       </c>
       <c r="L56" t="n">
-        <v>538.3</v>
+        <v>171.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:31:32</t>
+          <t>09:38:08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="F57" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="G57" t="n">
-        <v>123</v>
+        <v>147.2</v>
       </c>
       <c r="H57" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>116.98</v>
+        <v>239.85</v>
       </c>
       <c r="K57" t="n">
-        <v>-102.09</v>
+        <v>-321.05</v>
       </c>
       <c r="L57" t="n">
-        <v>155.26</v>
+        <v>400.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:33:53</t>
+          <t>09:39:54</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="F58" t="n">
-        <v>6.02</v>
+        <v>6.18</v>
       </c>
       <c r="G58" t="n">
-        <v>126.3</v>
+        <v>135.8</v>
       </c>
       <c r="H58" t="n">
-        <v>96.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>8.42</v>
+        <v>-239.92</v>
       </c>
       <c r="K58" t="n">
-        <v>166.28</v>
+        <v>-94.06999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>166.49</v>
+        <v>257.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:41:48</t>
+          <t>09:51:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="F59" t="n">
-        <v>6.05</v>
+        <v>6.33</v>
       </c>
       <c r="G59" t="n">
-        <v>124.5</v>
+        <v>136.3</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.73</v>
+        <v>80.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-34.68</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>35.76</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:43:20</t>
+          <t>09:53:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="F60" t="n">
-        <v>5.69</v>
+        <v>5.84</v>
       </c>
       <c r="G60" t="n">
-        <v>125.8</v>
+        <v>120.7</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-55.77</v>
+        <v>34.74</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.05</v>
+        <v>-109.34</v>
       </c>
       <c r="L60" t="n">
-        <v>55.85</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:45:21</t>
+          <t>09:55:37</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="F61" t="n">
-        <v>5.81</v>
+        <v>6.15</v>
       </c>
       <c r="G61" t="n">
-        <v>129.3</v>
+        <v>128.7</v>
       </c>
       <c r="H61" t="n">
-        <v>93.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>7.66</v>
+        <v>12.88</v>
       </c>
       <c r="K61" t="n">
-        <v>24.43</v>
+        <v>-21.81</v>
       </c>
       <c r="L61" t="n">
-        <v>25.61</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:49:57</t>
+          <t>09:59:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="F62" t="n">
-        <v>4.78</v>
+        <v>6.18</v>
       </c>
       <c r="G62" t="n">
-        <v>138.3</v>
+        <v>128.9</v>
       </c>
       <c r="H62" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>7.28</v>
+        <v>-79.84</v>
       </c>
       <c r="K62" t="n">
-        <v>19.79</v>
+        <v>-16</v>
       </c>
       <c r="L62" t="n">
-        <v>21.09</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:52:25</t>
+          <t>10:02:31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="F63" t="n">
-        <v>5.97</v>
+        <v>6.14</v>
       </c>
       <c r="G63" t="n">
-        <v>119.8</v>
+        <v>129.1</v>
       </c>
       <c r="H63" t="n">
-        <v>94.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>16.27</v>
+        <v>228.87</v>
       </c>
       <c r="K63" t="n">
-        <v>17.16</v>
+        <v>-19.28</v>
       </c>
       <c r="L63" t="n">
-        <v>23.65</v>
+        <v>229.68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:53:45</t>
+          <t>10:03:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="F64" t="n">
-        <v>5.16</v>
+        <v>4.92</v>
       </c>
       <c r="G64" t="n">
-        <v>125.3</v>
+        <v>142.1</v>
       </c>
       <c r="H64" t="n">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>52.96</v>
+        <v>41.89</v>
       </c>
       <c r="K64" t="n">
-        <v>76.29000000000001</v>
+        <v>107.66</v>
       </c>
       <c r="L64" t="n">
-        <v>92.87</v>
+        <v>115.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:58:38</t>
+          <t>10:07:35</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="F65" t="n">
-        <v>5.88</v>
+        <v>6.28</v>
       </c>
       <c r="G65" t="n">
-        <v>130.2</v>
+        <v>115.5</v>
       </c>
       <c r="H65" t="n">
         <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-91.8</v>
+        <v>60.44</v>
       </c>
       <c r="K65" t="n">
-        <v>61.52</v>
+        <v>26.16</v>
       </c>
       <c r="L65" t="n">
-        <v>110.51</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:59:52</t>
+          <t>10:10:09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="F66" t="n">
-        <v>4.75</v>
+        <v>6.03</v>
       </c>
       <c r="G66" t="n">
-        <v>137.3</v>
+        <v>124.6</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-214.74</v>
+        <v>-116.6</v>
       </c>
       <c r="K66" t="n">
-        <v>27.47</v>
+        <v>54.09</v>
       </c>
       <c r="L66" t="n">
-        <v>216.49</v>
+        <v>128.53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:01:35</t>
+          <t>10:11:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="F67" t="n">
-        <v>5.92</v>
+        <v>5.76</v>
       </c>
       <c r="G67" t="n">
-        <v>127</v>
+        <v>124.2</v>
       </c>
       <c r="H67" t="n">
         <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-54.79</v>
+        <v>-150.58</v>
       </c>
       <c r="K67" t="n">
-        <v>1.83</v>
+        <v>22.99</v>
       </c>
       <c r="L67" t="n">
-        <v>54.82</v>
+        <v>152.33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:07:09</t>
+          <t>10:14:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="F68" t="n">
-        <v>5.47</v>
+        <v>6.07</v>
       </c>
       <c r="G68" t="n">
-        <v>145.1</v>
+        <v>131.2</v>
       </c>
       <c r="H68" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>26.2</v>
+        <v>159.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-149.65</v>
+        <v>58.95</v>
       </c>
       <c r="L68" t="n">
-        <v>151.92</v>
+        <v>170.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:08:11</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="F69" t="n">
-        <v>5.54</v>
+        <v>5.67</v>
       </c>
       <c r="G69" t="n">
-        <v>129</v>
+        <v>130.9</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>214.01</v>
+        <v>-136.45</v>
       </c>
       <c r="K69" t="n">
-        <v>224.14</v>
+        <v>358.88</v>
       </c>
       <c r="L69" t="n">
-        <v>309.9</v>
+        <v>383.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:09:28</t>
+          <t>10:18:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="F70" t="n">
-        <v>4.96</v>
+        <v>5.65</v>
       </c>
       <c r="G70" t="n">
-        <v>138.7</v>
+        <v>124.6</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-172.82</v>
+        <v>-4.01</v>
       </c>
       <c r="K70" t="n">
-        <v>-115.05</v>
+        <v>276.31</v>
       </c>
       <c r="L70" t="n">
-        <v>207.61</v>
+        <v>276.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:14:28</t>
+          <t>10:24:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="F71" t="n">
-        <v>5.78</v>
+        <v>5.19</v>
       </c>
       <c r="G71" t="n">
-        <v>123.2</v>
+        <v>136.9</v>
       </c>
       <c r="H71" t="n">
-        <v>91.5</v>
+        <v>99.3</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>317.18</v>
+        <v>65.41</v>
       </c>
       <c r="K71" t="n">
-        <v>94.78</v>
+        <v>-104.24</v>
       </c>
       <c r="L71" t="n">
-        <v>331.03</v>
+        <v>123.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:15:21</t>
+          <t>10:26:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="F72" t="n">
-        <v>6.53</v>
+        <v>5.79</v>
       </c>
       <c r="G72" t="n">
-        <v>136.1</v>
+        <v>128.4</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>110.79</v>
+        <v>-155.73</v>
       </c>
       <c r="K72" t="n">
-        <v>321.97</v>
+        <v>140.53</v>
       </c>
       <c r="L72" t="n">
-        <v>340.49</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:17:08</t>
+          <t>10:28:36</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="F73" t="n">
-        <v>5.46</v>
+        <v>6.51</v>
       </c>
       <c r="G73" t="n">
-        <v>123.5</v>
+        <v>131.5</v>
       </c>
       <c r="H73" t="n">
-        <v>92.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>372.32</v>
+        <v>-310.21</v>
       </c>
       <c r="K73" t="n">
-        <v>-188.05</v>
+        <v>157.75</v>
       </c>
       <c r="L73" t="n">
-        <v>417.11</v>
+        <v>348.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:27:50</t>
+          <t>10:40:43</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="G74" t="n">
-        <v>123.7</v>
+        <v>148.8</v>
       </c>
       <c r="H74" t="n">
-        <v>91.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>58.53</v>
+        <v>-48.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-71.61</v>
+        <v>51.48</v>
       </c>
       <c r="L74" t="n">
-        <v>92.48999999999999</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:29:15</t>
+          <t>10:42:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="F75" t="n">
-        <v>5.21</v>
+        <v>5.92</v>
       </c>
       <c r="G75" t="n">
-        <v>138</v>
+        <v>155.9</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>74</v>
+        <v>17.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-83.58</v>
+        <v>49.9</v>
       </c>
       <c r="L75" t="n">
-        <v>111.63</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:30:28</t>
+          <t>10:44:34</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="F76" t="n">
-        <v>5.63</v>
+        <v>5.36</v>
       </c>
       <c r="G76" t="n">
-        <v>120.7</v>
+        <v>139.5</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-32.14</v>
+        <v>148</v>
       </c>
       <c r="K76" t="n">
-        <v>41.47</v>
+        <v>58.93</v>
       </c>
       <c r="L76" t="n">
-        <v>52.47</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:34:11</t>
+          <t>10:48:05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="F77" t="n">
-        <v>5.94</v>
+        <v>6.31</v>
       </c>
       <c r="G77" t="n">
-        <v>130.8</v>
+        <v>115.1</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.69</v>
+        <v>-151.36</v>
       </c>
       <c r="K77" t="n">
-        <v>138.41</v>
+        <v>80.48</v>
       </c>
       <c r="L77" t="n">
-        <v>155.42</v>
+        <v>171.43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:35:39</t>
+          <t>10:49:19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="F78" t="n">
-        <v>5.15</v>
+        <v>5.7</v>
       </c>
       <c r="G78" t="n">
-        <v>124.3</v>
+        <v>118.7</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-111.42</v>
+        <v>13.1</v>
       </c>
       <c r="K78" t="n">
-        <v>20.09</v>
+        <v>-174.37</v>
       </c>
       <c r="L78" t="n">
-        <v>113.21</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:37:05</t>
+          <t>10:50:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="F79" t="n">
-        <v>5.73</v>
+        <v>5.33</v>
       </c>
       <c r="G79" t="n">
-        <v>143.8</v>
+        <v>154.1</v>
       </c>
       <c r="H79" t="n">
-        <v>93.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-33.35</v>
+        <v>24.98</v>
       </c>
       <c r="K79" t="n">
-        <v>-59.88</v>
+        <v>194.48</v>
       </c>
       <c r="L79" t="n">
-        <v>68.54000000000001</v>
+        <v>196.08</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:41:53</t>
+          <t>10:55:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="F80" t="n">
-        <v>5.24</v>
+        <v>5.35</v>
       </c>
       <c r="G80" t="n">
-        <v>127</v>
+        <v>124.1</v>
       </c>
       <c r="H80" t="n">
         <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-137.78</v>
+        <v>162.33</v>
       </c>
       <c r="K80" t="n">
-        <v>164.28</v>
+        <v>32.75</v>
       </c>
       <c r="L80" t="n">
-        <v>214.41</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:43:15</t>
+          <t>10:57:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="F81" t="n">
-        <v>5.16</v>
+        <v>6.18</v>
       </c>
       <c r="G81" t="n">
-        <v>145.1</v>
+        <v>112.6</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>336.14</v>
+        <v>140.68</v>
       </c>
       <c r="K81" t="n">
-        <v>-114.83</v>
+        <v>-17.93</v>
       </c>
       <c r="L81" t="n">
-        <v>355.21</v>
+        <v>141.82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:44:56</t>
+          <t>10:59:17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="F82" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="G82" t="n">
-        <v>136.5</v>
+        <v>134.7</v>
       </c>
       <c r="H82" t="n">
         <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>51.43</v>
+        <v>-229.21</v>
       </c>
       <c r="K82" t="n">
-        <v>231.04</v>
+        <v>-15.79</v>
       </c>
       <c r="L82" t="n">
-        <v>236.7</v>
+        <v>229.75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:50:19</t>
+          <t>11:04:11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="F83" t="n">
-        <v>5.76</v>
+        <v>6.68</v>
       </c>
       <c r="G83" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H83" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>58.88</v>
+        <v>-60.35</v>
       </c>
       <c r="K83" t="n">
-        <v>-305.98</v>
+        <v>138.18</v>
       </c>
       <c r="L83" t="n">
-        <v>311.59</v>
+        <v>150.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:52:00</t>
+          <t>11:06:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="F84" t="n">
-        <v>5.21</v>
+        <v>5.84</v>
       </c>
       <c r="G84" t="n">
-        <v>144.3</v>
+        <v>118.2</v>
       </c>
       <c r="H84" t="n">
-        <v>93.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>189.64</v>
+        <v>76.5</v>
       </c>
       <c r="K84" t="n">
-        <v>140.66</v>
+        <v>135.85</v>
       </c>
       <c r="L84" t="n">
-        <v>236.11</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:53:56</t>
+          <t>11:08:32</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="F85" t="n">
-        <v>5.56</v>
+        <v>5.18</v>
       </c>
       <c r="G85" t="n">
-        <v>128.6</v>
+        <v>134</v>
       </c>
       <c r="H85" t="n">
         <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-568.46</v>
+        <v>105.89</v>
       </c>
       <c r="K85" t="n">
-        <v>202.51</v>
+        <v>298.16</v>
       </c>
       <c r="L85" t="n">
-        <v>603.46</v>
+        <v>316.41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:58:21</t>
+          <t>11:12:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="F86" t="n">
-        <v>5.33</v>
+        <v>5.94</v>
       </c>
       <c r="G86" t="n">
-        <v>127.1</v>
+        <v>136.7</v>
       </c>
       <c r="H86" t="n">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>702.55</v>
+        <v>166.46</v>
       </c>
       <c r="K86" t="n">
-        <v>80.31999999999999</v>
+        <v>258.13</v>
       </c>
       <c r="L86" t="n">
-        <v>707.12</v>
+        <v>307.15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:59:19</t>
+          <t>11:14:03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="F87" t="n">
-        <v>5.68</v>
+        <v>6.03</v>
       </c>
       <c r="G87" t="n">
-        <v>137.6</v>
+        <v>144</v>
       </c>
       <c r="H87" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-123.63</v>
+        <v>-179.69</v>
       </c>
       <c r="K87" t="n">
-        <v>-218.67</v>
+        <v>257.15</v>
       </c>
       <c r="L87" t="n">
-        <v>251.2</v>
+        <v>313.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:00:40</t>
+          <t>11:15:53</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="F88" t="n">
-        <v>6.13</v>
+        <v>5.41</v>
       </c>
       <c r="G88" t="n">
-        <v>131.3</v>
+        <v>124.1</v>
       </c>
       <c r="H88" t="n">
         <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>132.71</v>
+        <v>84.47</v>
       </c>
       <c r="K88" t="n">
-        <v>-68.69</v>
+        <v>-147.92</v>
       </c>
       <c r="L88" t="n">
-        <v>149.43</v>
+        <v>170.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.06</v>
+        <v>-14.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-32.59</v>
+        <v>-46.91</v>
       </c>
       <c r="L14" t="n">
-        <v>34.11</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>49.46</v>
+        <v>49.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-59.31</v>
+        <v>-59</v>
       </c>
       <c r="L15" t="n">
-        <v>77.23</v>
+        <v>76.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>74.17</v>
+        <v>64.13</v>
       </c>
       <c r="K16" t="n">
-        <v>21.84</v>
+        <v>18.88</v>
       </c>
       <c r="L16" t="n">
-        <v>77.31999999999999</v>
+        <v>66.84999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-21.62</v>
+        <v>-17.12</v>
       </c>
       <c r="K17" t="n">
-        <v>-177.25</v>
+        <v>-140.38</v>
       </c>
       <c r="L17" t="n">
-        <v>178.56</v>
+        <v>141.42</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-55.59</v>
+        <v>-66.76000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.13</v>
+        <v>-45.79</v>
       </c>
       <c r="L18" t="n">
-        <v>67.41</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>31.15</v>
+        <v>40.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-38.98</v>
+        <v>-50.33</v>
       </c>
       <c r="L19" t="n">
-        <v>49.89</v>
+        <v>64.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>85.40000000000001</v>
+        <v>100.42</v>
       </c>
       <c r="K20" t="n">
-        <v>-64.45999999999999</v>
+        <v>-75.79000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>106.99</v>
+        <v>125.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-48.88</v>
+        <v>-53.47</v>
       </c>
       <c r="K21" t="n">
-        <v>119.78</v>
+        <v>131.03</v>
       </c>
       <c r="L21" t="n">
-        <v>129.37</v>
+        <v>141.52</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-150.18</v>
+        <v>-146.05</v>
       </c>
       <c r="K22" t="n">
-        <v>92.37</v>
+        <v>89.83</v>
       </c>
       <c r="L22" t="n">
-        <v>176.32</v>
+        <v>171.46</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-164.78</v>
+        <v>-149.59</v>
       </c>
       <c r="K23" t="n">
-        <v>-268.66</v>
+        <v>-243.9</v>
       </c>
       <c r="L23" t="n">
-        <v>315.17</v>
+        <v>286.12</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>188.77</v>
+        <v>202.86</v>
       </c>
       <c r="K24" t="n">
-        <v>176.42</v>
+        <v>189.59</v>
       </c>
       <c r="L24" t="n">
-        <v>258.37</v>
+        <v>277.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>87.11</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-283.71</v>
+        <v>-279.14</v>
       </c>
       <c r="L25" t="n">
-        <v>296.78</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>142.42</v>
+        <v>212.72</v>
       </c>
       <c r="K26" t="n">
-        <v>-105.19</v>
+        <v>-157.12</v>
       </c>
       <c r="L26" t="n">
-        <v>177.06</v>
+        <v>264.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-33.02</v>
+        <v>-56.37</v>
       </c>
       <c r="K27" t="n">
-        <v>-151.75</v>
+        <v>-259.09</v>
       </c>
       <c r="L27" t="n">
-        <v>155.3</v>
+        <v>265.15</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>43.37</v>
+        <v>56.02</v>
       </c>
       <c r="K28" t="n">
-        <v>-314.45</v>
+        <v>-406.17</v>
       </c>
       <c r="L28" t="n">
-        <v>317.43</v>
+        <v>410.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>37.06</v>
+        <v>35.46</v>
       </c>
       <c r="K29" t="n">
-        <v>49.12</v>
+        <v>46.99</v>
       </c>
       <c r="L29" t="n">
-        <v>61.53</v>
+        <v>58.86</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.37</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.06</v>
+        <v>-43.13</v>
       </c>
       <c r="L30" t="n">
-        <v>23.06</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>76.52</v>
+        <v>59.23</v>
       </c>
       <c r="K31" t="n">
-        <v>-85.34</v>
+        <v>-66.06</v>
       </c>
       <c r="L31" t="n">
-        <v>114.62</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>57.33</v>
+        <v>50.1</v>
       </c>
       <c r="K32" t="n">
-        <v>-142.51</v>
+        <v>-124.53</v>
       </c>
       <c r="L32" t="n">
-        <v>153.61</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5</v>
+        <v>-0.77</v>
       </c>
       <c r="K33" t="n">
-        <v>-36.27</v>
+        <v>-55.46</v>
       </c>
       <c r="L33" t="n">
-        <v>36.27</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.67</v>
+        <v>-49.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-89.42</v>
+        <v>-94.14</v>
       </c>
       <c r="L34" t="n">
-        <v>100.87</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.53</v>
+        <v>-53.04</v>
       </c>
       <c r="K35" t="n">
-        <v>37.48</v>
+        <v>77.87</v>
       </c>
       <c r="L35" t="n">
-        <v>45.34</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>43.87</v>
+        <v>65.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-47.32</v>
+        <v>-70.5</v>
       </c>
       <c r="L36" t="n">
-        <v>64.53</v>
+        <v>96.13</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-214.87</v>
+        <v>-199.29</v>
       </c>
       <c r="K37" t="n">
-        <v>141.98</v>
+        <v>131.68</v>
       </c>
       <c r="L37" t="n">
-        <v>257.54</v>
+        <v>238.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-101.76</v>
+        <v>-109.11</v>
       </c>
       <c r="K38" t="n">
-        <v>133.76</v>
+        <v>143.42</v>
       </c>
       <c r="L38" t="n">
-        <v>168.06</v>
+        <v>180.21</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-91.90000000000001</v>
+        <v>-92.51000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>273.08</v>
+        <v>274.88</v>
       </c>
       <c r="L39" t="n">
-        <v>288.13</v>
+        <v>290.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>231.35</v>
+        <v>222.12</v>
       </c>
       <c r="K40" t="n">
-        <v>-151.65</v>
+        <v>-145.6</v>
       </c>
       <c r="L40" t="n">
-        <v>276.62</v>
+        <v>265.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-366.77</v>
+        <v>-428.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-35.3</v>
+        <v>-41.21</v>
       </c>
       <c r="L41" t="n">
-        <v>368.47</v>
+        <v>430.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>259.15</v>
+        <v>293.67</v>
       </c>
       <c r="K42" t="n">
-        <v>-159.62</v>
+        <v>-180.88</v>
       </c>
       <c r="L42" t="n">
-        <v>304.36</v>
+        <v>344.91</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>217.44</v>
+        <v>215.16</v>
       </c>
       <c r="K43" t="n">
-        <v>-487.64</v>
+        <v>-482.54</v>
       </c>
       <c r="L43" t="n">
-        <v>533.9299999999999</v>
+        <v>528.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.19</v>
+        <v>-4.33</v>
       </c>
       <c r="K44" t="n">
-        <v>-144.39</v>
+        <v>-101.16</v>
       </c>
       <c r="L44" t="n">
-        <v>144.52</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.4</v>
+        <v>-13.01</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.2</v>
+        <v>-57.27</v>
       </c>
       <c r="L45" t="n">
-        <v>51.48</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.85</v>
+        <v>-19.64</v>
       </c>
       <c r="K46" t="n">
-        <v>43.43</v>
+        <v>47.79</v>
       </c>
       <c r="L46" t="n">
-        <v>46.96</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-39.46</v>
+        <v>-52.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.61</v>
+        <v>-10.15</v>
       </c>
       <c r="L47" t="n">
-        <v>40.19</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>131.25</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>251.91</v>
+        <v>182.82</v>
       </c>
       <c r="L48" t="n">
-        <v>284.05</v>
+        <v>206.15</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>54.1</v>
+        <v>50.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-78.66</v>
+        <v>-73.40000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>95.47</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>40.39</v>
+        <v>63.55</v>
       </c>
       <c r="K50" t="n">
-        <v>47.38</v>
+        <v>74.55</v>
       </c>
       <c r="L50" t="n">
-        <v>62.25</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>20.62</v>
+        <v>47.92</v>
       </c>
       <c r="K51" t="n">
-        <v>-25.68</v>
+        <v>-59.69</v>
       </c>
       <c r="L51" t="n">
-        <v>32.93</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-100.92</v>
+        <v>-121.66</v>
       </c>
       <c r="K52" t="n">
-        <v>-27.47</v>
+        <v>-33.12</v>
       </c>
       <c r="L52" t="n">
-        <v>104.59</v>
+        <v>126.09</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-238</v>
+        <v>-233.66</v>
       </c>
       <c r="K53" t="n">
-        <v>-201.55</v>
+        <v>-197.87</v>
       </c>
       <c r="L53" t="n">
-        <v>311.88</v>
+        <v>306.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-98.3</v>
+        <v>-146.76</v>
       </c>
       <c r="K54" t="n">
-        <v>-72.2</v>
+        <v>-107.79</v>
       </c>
       <c r="L54" t="n">
-        <v>121.96</v>
+        <v>182.09</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>335.25</v>
+        <v>311.08</v>
       </c>
       <c r="K55" t="n">
-        <v>3.87</v>
+        <v>3.59</v>
       </c>
       <c r="L55" t="n">
-        <v>335.27</v>
+        <v>311.1</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>13.27</v>
+        <v>20.89</v>
       </c>
       <c r="K56" t="n">
-        <v>-171.31</v>
+        <v>-269.64</v>
       </c>
       <c r="L56" t="n">
-        <v>171.82</v>
+        <v>270.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>239.85</v>
+        <v>264.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-321.05</v>
+        <v>-354.24</v>
       </c>
       <c r="L57" t="n">
-        <v>400.75</v>
+        <v>442.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-239.92</v>
+        <v>-323.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-94.06999999999999</v>
+        <v>-126.66</v>
       </c>
       <c r="L58" t="n">
-        <v>257.7</v>
+        <v>346.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>80.53</v>
+        <v>53.94</v>
       </c>
       <c r="K59" t="n">
-        <v>93.31999999999999</v>
+        <v>62.52</v>
       </c>
       <c r="L59" t="n">
-        <v>123.26</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>34.74</v>
+        <v>27.49</v>
       </c>
       <c r="K60" t="n">
-        <v>-109.34</v>
+        <v>-86.52</v>
       </c>
       <c r="L60" t="n">
-        <v>114.72</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>12.88</v>
+        <v>17.77</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.81</v>
+        <v>-30.1</v>
       </c>
       <c r="L61" t="n">
-        <v>25.33</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-79.84</v>
+        <v>-91.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-16</v>
+        <v>-18.41</v>
       </c>
       <c r="L62" t="n">
-        <v>81.43000000000001</v>
+        <v>93.65000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>228.87</v>
+        <v>190.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-19.28</v>
+        <v>-16.06</v>
       </c>
       <c r="L63" t="n">
-        <v>229.68</v>
+        <v>191.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>41.89</v>
+        <v>40.75</v>
       </c>
       <c r="K64" t="n">
-        <v>107.66</v>
+        <v>104.72</v>
       </c>
       <c r="L64" t="n">
-        <v>115.53</v>
+        <v>112.37</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>60.44</v>
+        <v>84.12</v>
       </c>
       <c r="K65" t="n">
-        <v>26.16</v>
+        <v>36.4</v>
       </c>
       <c r="L65" t="n">
-        <v>65.86</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-116.6</v>
+        <v>-119.83</v>
       </c>
       <c r="K66" t="n">
-        <v>54.09</v>
+        <v>55.59</v>
       </c>
       <c r="L66" t="n">
-        <v>128.53</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-150.58</v>
+        <v>-141.13</v>
       </c>
       <c r="K67" t="n">
-        <v>22.99</v>
+        <v>21.54</v>
       </c>
       <c r="L67" t="n">
-        <v>152.33</v>
+        <v>142.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>159.92</v>
+        <v>174.66</v>
       </c>
       <c r="K68" t="n">
-        <v>58.95</v>
+        <v>64.39</v>
       </c>
       <c r="L68" t="n">
-        <v>170.44</v>
+        <v>186.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-136.45</v>
+        <v>-131.6</v>
       </c>
       <c r="K69" t="n">
-        <v>358.88</v>
+        <v>346.13</v>
       </c>
       <c r="L69" t="n">
-        <v>383.94</v>
+        <v>370.31</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.01</v>
+        <v>-3.89</v>
       </c>
       <c r="K70" t="n">
-        <v>276.31</v>
+        <v>268.28</v>
       </c>
       <c r="L70" t="n">
-        <v>276.34</v>
+        <v>268.31</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>65.41</v>
+        <v>119.93</v>
       </c>
       <c r="K71" t="n">
-        <v>-104.24</v>
+        <v>-191.14</v>
       </c>
       <c r="L71" t="n">
-        <v>123.06</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-155.73</v>
+        <v>-227.75</v>
       </c>
       <c r="K72" t="n">
-        <v>140.53</v>
+        <v>205.52</v>
       </c>
       <c r="L72" t="n">
-        <v>209.77</v>
+        <v>306.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-310.21</v>
+        <v>-327.97</v>
       </c>
       <c r="K73" t="n">
-        <v>157.75</v>
+        <v>166.78</v>
       </c>
       <c r="L73" t="n">
-        <v>348.02</v>
+        <v>367.94</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.04</v>
+        <v>-39.54</v>
       </c>
       <c r="K74" t="n">
-        <v>51.48</v>
+        <v>42.37</v>
       </c>
       <c r="L74" t="n">
-        <v>70.42</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>17.19</v>
+        <v>15.95</v>
       </c>
       <c r="K75" t="n">
-        <v>49.9</v>
+        <v>46.31</v>
       </c>
       <c r="L75" t="n">
-        <v>52.78</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>148</v>
+        <v>102.23</v>
       </c>
       <c r="K76" t="n">
-        <v>58.93</v>
+        <v>40.7</v>
       </c>
       <c r="L76" t="n">
-        <v>159.3</v>
+        <v>110.03</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-151.36</v>
+        <v>-117.25</v>
       </c>
       <c r="K77" t="n">
-        <v>80.48</v>
+        <v>62.34</v>
       </c>
       <c r="L77" t="n">
-        <v>171.43</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>13.1</v>
+        <v>11.29</v>
       </c>
       <c r="K78" t="n">
-        <v>-174.37</v>
+        <v>-150.3</v>
       </c>
       <c r="L78" t="n">
-        <v>174.86</v>
+        <v>150.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>24.98</v>
+        <v>20.33</v>
       </c>
       <c r="K79" t="n">
-        <v>194.48</v>
+        <v>158.26</v>
       </c>
       <c r="L79" t="n">
-        <v>196.08</v>
+        <v>159.56</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>162.33</v>
+        <v>179.46</v>
       </c>
       <c r="K80" t="n">
-        <v>32.75</v>
+        <v>36.21</v>
       </c>
       <c r="L80" t="n">
-        <v>165.6</v>
+        <v>183.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>140.68</v>
+        <v>134.81</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.93</v>
+        <v>-17.18</v>
       </c>
       <c r="L81" t="n">
-        <v>141.82</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-229.21</v>
+        <v>-209.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-15.79</v>
+        <v>-14.41</v>
       </c>
       <c r="L82" t="n">
-        <v>229.75</v>
+        <v>209.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.35</v>
+        <v>-105.36</v>
       </c>
       <c r="K83" t="n">
-        <v>138.18</v>
+        <v>241.24</v>
       </c>
       <c r="L83" t="n">
-        <v>150.78</v>
+        <v>263.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>76.5</v>
+        <v>100.85</v>
       </c>
       <c r="K84" t="n">
-        <v>135.85</v>
+        <v>179.09</v>
       </c>
       <c r="L84" t="n">
-        <v>155.9</v>
+        <v>205.54</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>105.89</v>
+        <v>93.69</v>
       </c>
       <c r="K85" t="n">
-        <v>298.16</v>
+        <v>263.81</v>
       </c>
       <c r="L85" t="n">
-        <v>316.41</v>
+        <v>279.95</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>166.46</v>
+        <v>188.2</v>
       </c>
       <c r="K86" t="n">
-        <v>258.13</v>
+        <v>291.84</v>
       </c>
       <c r="L86" t="n">
-        <v>307.15</v>
+        <v>347.27</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-179.69</v>
+        <v>-220.12</v>
       </c>
       <c r="K87" t="n">
-        <v>257.15</v>
+        <v>315.01</v>
       </c>
       <c r="L87" t="n">
-        <v>313.71</v>
+        <v>384.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>84.47</v>
+        <v>146.82</v>
       </c>
       <c r="K88" t="n">
-        <v>-147.92</v>
+        <v>-257.12</v>
       </c>
       <c r="L88" t="n">
-        <v>170.34</v>
+        <v>296.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.47</v>
+        <v>-12.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.91</v>
+        <v>-40.55</v>
       </c>
       <c r="L14" t="n">
-        <v>49.09</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>49.21</v>
+        <v>35.86</v>
       </c>
       <c r="K15" t="n">
-        <v>-59</v>
+        <v>-43</v>
       </c>
       <c r="L15" t="n">
-        <v>76.83</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>64.13</v>
+        <v>53.43</v>
       </c>
       <c r="K16" t="n">
-        <v>18.88</v>
+        <v>15.73</v>
       </c>
       <c r="L16" t="n">
-        <v>66.84999999999999</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.12</v>
+        <v>-13.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-140.38</v>
+        <v>-109.62</v>
       </c>
       <c r="L17" t="n">
-        <v>141.42</v>
+        <v>110.43</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.76000000000001</v>
+        <v>-48.88</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.79</v>
+        <v>-33.52</v>
       </c>
       <c r="L18" t="n">
-        <v>80.95</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>40.22</v>
+        <v>31.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-50.33</v>
+        <v>-39.77</v>
       </c>
       <c r="L19" t="n">
-        <v>64.43000000000001</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>100.42</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-75.79000000000001</v>
+        <v>-50.49</v>
       </c>
       <c r="L20" t="n">
-        <v>125.81</v>
+        <v>83.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-53.47</v>
+        <v>-35.91</v>
       </c>
       <c r="K21" t="n">
-        <v>131.03</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
-        <v>141.52</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-146.05</v>
+        <v>-97.73999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>89.83</v>
+        <v>60.12</v>
       </c>
       <c r="L22" t="n">
-        <v>171.46</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-149.59</v>
+        <v>-97.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-243.9</v>
+        <v>-158.47</v>
       </c>
       <c r="L23" t="n">
-        <v>286.12</v>
+        <v>185.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>202.86</v>
+        <v>111.93</v>
       </c>
       <c r="K24" t="n">
-        <v>189.59</v>
+        <v>104.61</v>
       </c>
       <c r="L24" t="n">
-        <v>277.66</v>
+        <v>153.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>85.70999999999999</v>
+        <v>50.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-279.14</v>
+        <v>-164.55</v>
       </c>
       <c r="L25" t="n">
-        <v>292</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>212.72</v>
+        <v>115.95</v>
       </c>
       <c r="K26" t="n">
-        <v>-157.12</v>
+        <v>-85.65000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>264.45</v>
+        <v>144.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-56.37</v>
+        <v>-28.71</v>
       </c>
       <c r="K27" t="n">
-        <v>-259.09</v>
+        <v>-131.97</v>
       </c>
       <c r="L27" t="n">
-        <v>265.15</v>
+        <v>135.05</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>56.02</v>
+        <v>28.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-406.17</v>
+        <v>-205.12</v>
       </c>
       <c r="L28" t="n">
-        <v>410.02</v>
+        <v>207.07</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>35.46</v>
+        <v>29.37</v>
       </c>
       <c r="K29" t="n">
-        <v>46.99</v>
+        <v>38.92</v>
       </c>
       <c r="L29" t="n">
-        <v>58.86</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="K30" t="n">
-        <v>-43.13</v>
+        <v>-31.69</v>
       </c>
       <c r="L30" t="n">
-        <v>43.13</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>59.23</v>
+        <v>51.11</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.06</v>
+        <v>-57</v>
       </c>
       <c r="L31" t="n">
-        <v>88.73</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>50.1</v>
+        <v>36.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-124.53</v>
+        <v>-91.37</v>
       </c>
       <c r="L32" t="n">
-        <v>134.23</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.77</v>
+        <v>-0.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-55.46</v>
+        <v>-44.72</v>
       </c>
       <c r="L33" t="n">
-        <v>55.47</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.13</v>
+        <v>-36.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-94.14</v>
+        <v>-70.86</v>
       </c>
       <c r="L34" t="n">
-        <v>106.19</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-53.04</v>
+        <v>-33.21</v>
       </c>
       <c r="K35" t="n">
-        <v>77.87</v>
+        <v>48.75</v>
       </c>
       <c r="L35" t="n">
-        <v>94.22</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>65.36</v>
+        <v>47.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-70.5</v>
+        <v>-51.19</v>
       </c>
       <c r="L36" t="n">
-        <v>96.13</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-199.29</v>
+        <v>-125.18</v>
       </c>
       <c r="K37" t="n">
-        <v>131.68</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>238.86</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.11</v>
+        <v>-73</v>
       </c>
       <c r="K38" t="n">
-        <v>143.42</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>180.21</v>
+        <v>120.57</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.51000000000001</v>
+        <v>-54.61</v>
       </c>
       <c r="K39" t="n">
-        <v>274.88</v>
+        <v>162.27</v>
       </c>
       <c r="L39" t="n">
-        <v>290.03</v>
+        <v>171.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>222.12</v>
+        <v>139.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-145.6</v>
+        <v>-91.44</v>
       </c>
       <c r="L40" t="n">
-        <v>265.59</v>
+        <v>166.8</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-428.18</v>
+        <v>-223.11</v>
       </c>
       <c r="K41" t="n">
-        <v>-41.21</v>
+        <v>-21.48</v>
       </c>
       <c r="L41" t="n">
-        <v>430.16</v>
+        <v>224.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>293.67</v>
+        <v>168.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-180.88</v>
+        <v>-103.88</v>
       </c>
       <c r="L42" t="n">
-        <v>344.91</v>
+        <v>198.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>215.16</v>
+        <v>118.07</v>
       </c>
       <c r="K43" t="n">
-        <v>-482.54</v>
+        <v>-264.79</v>
       </c>
       <c r="L43" t="n">
-        <v>528.34</v>
+        <v>289.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.33</v>
+        <v>-3.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-101.16</v>
+        <v>-86.22</v>
       </c>
       <c r="L44" t="n">
-        <v>101.26</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.01</v>
+        <v>-10.77</v>
       </c>
       <c r="K45" t="n">
-        <v>-57.27</v>
+        <v>-47.4</v>
       </c>
       <c r="L45" t="n">
-        <v>58.73</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.64</v>
+        <v>-15.58</v>
       </c>
       <c r="K46" t="n">
-        <v>47.79</v>
+        <v>37.9</v>
       </c>
       <c r="L46" t="n">
-        <v>51.67</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-52.64</v>
+        <v>-43.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.15</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>53.61</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>95.26000000000001</v>
+        <v>74.83</v>
       </c>
       <c r="K48" t="n">
-        <v>182.82</v>
+        <v>143.62</v>
       </c>
       <c r="L48" t="n">
-        <v>206.15</v>
+        <v>161.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>50.48</v>
+        <v>42.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-73.40000000000001</v>
+        <v>-62.08</v>
       </c>
       <c r="L49" t="n">
-        <v>89.08</v>
+        <v>75.34999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>63.55</v>
+        <v>41.47</v>
       </c>
       <c r="K50" t="n">
-        <v>74.55</v>
+        <v>48.65</v>
       </c>
       <c r="L50" t="n">
-        <v>97.97</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>47.92</v>
+        <v>33.44</v>
       </c>
       <c r="K51" t="n">
-        <v>-59.69</v>
+        <v>-41.65</v>
       </c>
       <c r="L51" t="n">
-        <v>76.55</v>
+        <v>53.42</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-121.66</v>
+        <v>-79.75</v>
       </c>
       <c r="K52" t="n">
-        <v>-33.12</v>
+        <v>-21.71</v>
       </c>
       <c r="L52" t="n">
-        <v>126.09</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-233.66</v>
+        <v>-141.79</v>
       </c>
       <c r="K53" t="n">
-        <v>-197.87</v>
+        <v>-120.07</v>
       </c>
       <c r="L53" t="n">
-        <v>306.18</v>
+        <v>185.8</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-146.76</v>
+        <v>-80.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-107.79</v>
+        <v>-59.11</v>
       </c>
       <c r="L54" t="n">
-        <v>182.09</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>311.08</v>
+        <v>185.56</v>
       </c>
       <c r="K55" t="n">
-        <v>3.59</v>
+        <v>2.14</v>
       </c>
       <c r="L55" t="n">
-        <v>311.1</v>
+        <v>185.57</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>20.89</v>
+        <v>11.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-269.64</v>
+        <v>-148.86</v>
       </c>
       <c r="L56" t="n">
-        <v>270.45</v>
+        <v>149.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>264.65</v>
+        <v>149.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-354.24</v>
+        <v>-200.38</v>
       </c>
       <c r="L57" t="n">
-        <v>442.19</v>
+        <v>250.13</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-323.03</v>
+        <v>-167.82</v>
       </c>
       <c r="K58" t="n">
-        <v>-126.66</v>
+        <v>-65.8</v>
       </c>
       <c r="L58" t="n">
-        <v>346.98</v>
+        <v>180.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>53.94</v>
+        <v>49.82</v>
       </c>
       <c r="K59" t="n">
-        <v>62.52</v>
+        <v>57.74</v>
       </c>
       <c r="L59" t="n">
-        <v>82.56999999999999</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>27.49</v>
+        <v>21.9</v>
       </c>
       <c r="K60" t="n">
-        <v>-86.52</v>
+        <v>-68.93000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>90.78</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>17.77</v>
+        <v>17.5</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.1</v>
+        <v>-29.64</v>
       </c>
       <c r="L61" t="n">
-        <v>34.96</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-91.83</v>
+        <v>-68.81</v>
       </c>
       <c r="K62" t="n">
-        <v>-18.41</v>
+        <v>-13.79</v>
       </c>
       <c r="L62" t="n">
-        <v>93.65000000000001</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>190.7</v>
+        <v>140.9</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.06</v>
+        <v>-11.87</v>
       </c>
       <c r="L63" t="n">
-        <v>191.37</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>40.75</v>
+        <v>30.8</v>
       </c>
       <c r="K64" t="n">
-        <v>104.72</v>
+        <v>79.16</v>
       </c>
       <c r="L64" t="n">
-        <v>112.37</v>
+        <v>84.94</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>84.12</v>
+        <v>66.44</v>
       </c>
       <c r="K65" t="n">
-        <v>36.4</v>
+        <v>28.75</v>
       </c>
       <c r="L65" t="n">
-        <v>91.66</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-119.83</v>
+        <v>-89.28</v>
       </c>
       <c r="K66" t="n">
-        <v>55.59</v>
+        <v>41.42</v>
       </c>
       <c r="L66" t="n">
-        <v>132.1</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-141.13</v>
+        <v>-102.77</v>
       </c>
       <c r="K67" t="n">
-        <v>21.54</v>
+        <v>15.69</v>
       </c>
       <c r="L67" t="n">
-        <v>142.76</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>174.66</v>
+        <v>112.42</v>
       </c>
       <c r="K68" t="n">
-        <v>64.39</v>
+        <v>41.44</v>
       </c>
       <c r="L68" t="n">
-        <v>186.15</v>
+        <v>119.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-131.6</v>
+        <v>-78.56</v>
       </c>
       <c r="K69" t="n">
-        <v>346.13</v>
+        <v>206.64</v>
       </c>
       <c r="L69" t="n">
-        <v>370.31</v>
+        <v>221.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.89</v>
+        <v>-2.44</v>
       </c>
       <c r="K70" t="n">
-        <v>268.28</v>
+        <v>167.88</v>
       </c>
       <c r="L70" t="n">
-        <v>268.31</v>
+        <v>167.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>119.93</v>
+        <v>66.72</v>
       </c>
       <c r="K71" t="n">
-        <v>-191.14</v>
+        <v>-106.33</v>
       </c>
       <c r="L71" t="n">
-        <v>225.65</v>
+        <v>125.53</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-227.75</v>
+        <v>-130.8</v>
       </c>
       <c r="K72" t="n">
-        <v>205.52</v>
+        <v>118.03</v>
       </c>
       <c r="L72" t="n">
-        <v>306.78</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-327.97</v>
+        <v>-196.55</v>
       </c>
       <c r="K73" t="n">
-        <v>166.78</v>
+        <v>99.95</v>
       </c>
       <c r="L73" t="n">
-        <v>367.94</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-39.54</v>
+        <v>-36.75</v>
       </c>
       <c r="K74" t="n">
-        <v>42.37</v>
+        <v>39.38</v>
       </c>
       <c r="L74" t="n">
-        <v>57.96</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>15.95</v>
+        <v>16.07</v>
       </c>
       <c r="K75" t="n">
-        <v>46.31</v>
+        <v>46.64</v>
       </c>
       <c r="L75" t="n">
-        <v>48.98</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>102.23</v>
+        <v>94.14</v>
       </c>
       <c r="K76" t="n">
-        <v>40.7</v>
+        <v>37.48</v>
       </c>
       <c r="L76" t="n">
-        <v>110.03</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-117.25</v>
+        <v>-99.76000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>62.34</v>
+        <v>53.04</v>
       </c>
       <c r="L77" t="n">
-        <v>132.8</v>
+        <v>112.99</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>11.29</v>
+        <v>8.74</v>
       </c>
       <c r="K78" t="n">
-        <v>-150.3</v>
+        <v>-116.37</v>
       </c>
       <c r="L78" t="n">
-        <v>150.72</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>20.33</v>
+        <v>16.01</v>
       </c>
       <c r="K79" t="n">
-        <v>158.26</v>
+        <v>124.63</v>
       </c>
       <c r="L79" t="n">
-        <v>159.56</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>179.46</v>
+        <v>116.35</v>
       </c>
       <c r="K80" t="n">
-        <v>36.21</v>
+        <v>23.47</v>
       </c>
       <c r="L80" t="n">
-        <v>183.07</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>134.81</v>
+        <v>104.43</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.18</v>
+        <v>-13.31</v>
       </c>
       <c r="L81" t="n">
-        <v>135.9</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-209.17</v>
+        <v>-150.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-14.41</v>
+        <v>-10.39</v>
       </c>
       <c r="L82" t="n">
-        <v>209.66</v>
+        <v>151.19</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-105.36</v>
+        <v>-55.83</v>
       </c>
       <c r="K83" t="n">
-        <v>241.24</v>
+        <v>127.84</v>
       </c>
       <c r="L83" t="n">
-        <v>263.24</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>100.85</v>
+        <v>59.39</v>
       </c>
       <c r="K84" t="n">
-        <v>179.09</v>
+        <v>105.47</v>
       </c>
       <c r="L84" t="n">
-        <v>205.54</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>93.69</v>
+        <v>64.72</v>
       </c>
       <c r="K85" t="n">
-        <v>263.81</v>
+        <v>182.23</v>
       </c>
       <c r="L85" t="n">
-        <v>279.95</v>
+        <v>193.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>188.2</v>
+        <v>106.12</v>
       </c>
       <c r="K86" t="n">
-        <v>291.84</v>
+        <v>164.55</v>
       </c>
       <c r="L86" t="n">
-        <v>347.27</v>
+        <v>195.8</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-220.12</v>
+        <v>-118.82</v>
       </c>
       <c r="K87" t="n">
-        <v>315.01</v>
+        <v>170.04</v>
       </c>
       <c r="L87" t="n">
-        <v>384.29</v>
+        <v>207.44</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>146.82</v>
+        <v>79.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-257.12</v>
+        <v>-138.49</v>
       </c>
       <c r="L88" t="n">
-        <v>296.09</v>
+        <v>159.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.51</v>
+        <v>-13.31</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.55</v>
+        <v>-43.14</v>
       </c>
       <c r="L14" t="n">
-        <v>42.43</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>35.86</v>
+        <v>38.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-43</v>
+        <v>-45.76</v>
       </c>
       <c r="L15" t="n">
-        <v>55.99</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>53.43</v>
+        <v>56.53</v>
       </c>
       <c r="K16" t="n">
-        <v>15.73</v>
+        <v>16.64</v>
       </c>
       <c r="L16" t="n">
-        <v>55.7</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-13.37</v>
+        <v>-14.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-109.62</v>
+        <v>-118.22</v>
       </c>
       <c r="L17" t="n">
-        <v>110.43</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.88</v>
+        <v>-53.28</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.52</v>
+        <v>-36.54</v>
       </c>
       <c r="L18" t="n">
-        <v>59.27</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>31.78</v>
+        <v>34.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-39.77</v>
+        <v>-42.78</v>
       </c>
       <c r="L19" t="n">
-        <v>50.91</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>66.90000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.49</v>
+        <v>-57.26</v>
       </c>
       <c r="L20" t="n">
-        <v>83.81</v>
+        <v>95.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-35.91</v>
+        <v>-40.72</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>99.78</v>
       </c>
       <c r="L21" t="n">
-        <v>95.04000000000001</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-97.73999999999999</v>
+        <v>-111.33</v>
       </c>
       <c r="K22" t="n">
-        <v>60.12</v>
+        <v>68.48</v>
       </c>
       <c r="L22" t="n">
-        <v>114.75</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-97.2</v>
+        <v>-113.4</v>
       </c>
       <c r="K23" t="n">
-        <v>-158.47</v>
+        <v>-184.89</v>
       </c>
       <c r="L23" t="n">
-        <v>185.9</v>
+        <v>216.89</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>111.93</v>
+        <v>132.72</v>
       </c>
       <c r="K24" t="n">
-        <v>104.61</v>
+        <v>124.04</v>
       </c>
       <c r="L24" t="n">
-        <v>153.21</v>
+        <v>181.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>50.53</v>
+        <v>59.45</v>
       </c>
       <c r="K25" t="n">
-        <v>-164.55</v>
+        <v>-193.6</v>
       </c>
       <c r="L25" t="n">
-        <v>172.13</v>
+        <v>202.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>115.95</v>
+        <v>137.84</v>
       </c>
       <c r="K26" t="n">
-        <v>-85.65000000000001</v>
+        <v>-101.81</v>
       </c>
       <c r="L26" t="n">
-        <v>144.16</v>
+        <v>171.36</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-28.71</v>
+        <v>-34.43</v>
       </c>
       <c r="K27" t="n">
-        <v>-131.97</v>
+        <v>-158.24</v>
       </c>
       <c r="L27" t="n">
-        <v>135.05</v>
+        <v>161.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>28.29</v>
+        <v>34.12</v>
       </c>
       <c r="K28" t="n">
-        <v>-205.12</v>
+        <v>-247.39</v>
       </c>
       <c r="L28" t="n">
-        <v>207.07</v>
+        <v>249.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>29.37</v>
+        <v>30.86</v>
       </c>
       <c r="K29" t="n">
-        <v>38.92</v>
+        <v>40.9</v>
       </c>
       <c r="L29" t="n">
-        <v>48.76</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="K30" t="n">
-        <v>-31.69</v>
+        <v>-33.87</v>
       </c>
       <c r="L30" t="n">
-        <v>31.7</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>51.11</v>
+        <v>54.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-57</v>
+        <v>-60.37</v>
       </c>
       <c r="L31" t="n">
-        <v>76.56</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>36.76</v>
+        <v>40.02</v>
       </c>
       <c r="K32" t="n">
-        <v>-91.37</v>
+        <v>-99.48</v>
       </c>
       <c r="L32" t="n">
-        <v>98.48999999999999</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.62</v>
+        <v>-0.66</v>
       </c>
       <c r="K33" t="n">
-        <v>-44.72</v>
+        <v>-47.61</v>
       </c>
       <c r="L33" t="n">
-        <v>44.73</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-36.98</v>
+        <v>-40.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-70.86</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>79.93000000000001</v>
+        <v>88.18000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-33.21</v>
+        <v>-38.11</v>
       </c>
       <c r="K35" t="n">
-        <v>48.75</v>
+        <v>55.95</v>
       </c>
       <c r="L35" t="n">
-        <v>58.99</v>
+        <v>67.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>47.46</v>
+        <v>53.39</v>
       </c>
       <c r="K36" t="n">
-        <v>-51.19</v>
+        <v>-57.59</v>
       </c>
       <c r="L36" t="n">
-        <v>69.81</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-125.18</v>
+        <v>-144.65</v>
       </c>
       <c r="K37" t="n">
-        <v>82.70999999999999</v>
+        <v>95.58</v>
       </c>
       <c r="L37" t="n">
-        <v>150.03</v>
+        <v>173.38</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-73</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>95.95999999999999</v>
+        <v>111.45</v>
       </c>
       <c r="L38" t="n">
-        <v>120.57</v>
+        <v>140.03</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-54.61</v>
+        <v>-64.3</v>
       </c>
       <c r="K39" t="n">
-        <v>162.27</v>
+        <v>191.07</v>
       </c>
       <c r="L39" t="n">
-        <v>171.21</v>
+        <v>201.6</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>139.5</v>
+        <v>163.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-91.44</v>
+        <v>-107.25</v>
       </c>
       <c r="L40" t="n">
-        <v>166.8</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-223.11</v>
+        <v>-265.3</v>
       </c>
       <c r="K41" t="n">
-        <v>-21.48</v>
+        <v>-25.54</v>
       </c>
       <c r="L41" t="n">
-        <v>224.14</v>
+        <v>266.53</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>168.66</v>
+        <v>198.99</v>
       </c>
       <c r="K42" t="n">
-        <v>-103.88</v>
+        <v>-122.56</v>
       </c>
       <c r="L42" t="n">
-        <v>198.08</v>
+        <v>233.71</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>118.07</v>
+        <v>140.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-264.79</v>
+        <v>-314.19</v>
       </c>
       <c r="L43" t="n">
-        <v>289.93</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.69</v>
+        <v>-3.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-86.22</v>
+        <v>-91.29000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>86.3</v>
+        <v>91.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.77</v>
+        <v>-11.44</v>
       </c>
       <c r="K45" t="n">
-        <v>-47.4</v>
+        <v>-50.37</v>
       </c>
       <c r="L45" t="n">
-        <v>48.61</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.58</v>
+        <v>-16.57</v>
       </c>
       <c r="K46" t="n">
-        <v>37.9</v>
+        <v>40.32</v>
       </c>
       <c r="L46" t="n">
-        <v>40.98</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-43.95</v>
+        <v>-46.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="L47" t="n">
-        <v>44.75</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>74.83</v>
+        <v>80.98</v>
       </c>
       <c r="K48" t="n">
-        <v>143.62</v>
+        <v>155.41</v>
       </c>
       <c r="L48" t="n">
-        <v>161.95</v>
+        <v>175.24</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>42.7</v>
+        <v>45.72</v>
       </c>
       <c r="K49" t="n">
-        <v>-62.08</v>
+        <v>-66.47</v>
       </c>
       <c r="L49" t="n">
-        <v>75.34999999999999</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>41.47</v>
+        <v>47.21</v>
       </c>
       <c r="K50" t="n">
-        <v>48.65</v>
+        <v>55.39</v>
       </c>
       <c r="L50" t="n">
-        <v>63.93</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>33.44</v>
+        <v>37.98</v>
       </c>
       <c r="K51" t="n">
-        <v>-41.65</v>
+        <v>-47.31</v>
       </c>
       <c r="L51" t="n">
-        <v>53.42</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-79.75</v>
+        <v>-91.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.71</v>
+        <v>-24.86</v>
       </c>
       <c r="L52" t="n">
-        <v>82.66</v>
+        <v>94.66</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-141.79</v>
+        <v>-167.43</v>
       </c>
       <c r="K53" t="n">
-        <v>-120.07</v>
+        <v>-141.78</v>
       </c>
       <c r="L53" t="n">
-        <v>185.8</v>
+        <v>219.4</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-80.48</v>
+        <v>-96.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-59.11</v>
+        <v>-70.67</v>
       </c>
       <c r="L54" t="n">
-        <v>99.84999999999999</v>
+        <v>119.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>185.56</v>
+        <v>217.61</v>
       </c>
       <c r="K55" t="n">
-        <v>2.14</v>
+        <v>2.51</v>
       </c>
       <c r="L55" t="n">
-        <v>185.57</v>
+        <v>217.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>11.53</v>
+        <v>13.69</v>
       </c>
       <c r="K56" t="n">
-        <v>-148.86</v>
+        <v>-176.7</v>
       </c>
       <c r="L56" t="n">
-        <v>149.31</v>
+        <v>177.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>149.7</v>
+        <v>176.61</v>
       </c>
       <c r="K57" t="n">
-        <v>-200.38</v>
+        <v>-236.39</v>
       </c>
       <c r="L57" t="n">
-        <v>250.13</v>
+        <v>295.08</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-167.82</v>
+        <v>-199.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-65.8</v>
+        <v>-78.28</v>
       </c>
       <c r="L58" t="n">
-        <v>180.26</v>
+        <v>214.44</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>49.82</v>
+        <v>51.81</v>
       </c>
       <c r="K59" t="n">
-        <v>57.74</v>
+        <v>60.05</v>
       </c>
       <c r="L59" t="n">
-        <v>76.26000000000001</v>
+        <v>79.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>21.9</v>
+        <v>23.36</v>
       </c>
       <c r="K60" t="n">
-        <v>-68.93000000000001</v>
+        <v>-73.51000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>72.33</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.64</v>
+        <v>-31</v>
       </c>
       <c r="L61" t="n">
-        <v>34.42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-68.81</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-13.79</v>
+        <v>-15.23</v>
       </c>
       <c r="L62" t="n">
-        <v>70.18000000000001</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>140.9</v>
+        <v>155.85</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.87</v>
+        <v>-13.13</v>
       </c>
       <c r="L63" t="n">
-        <v>141.4</v>
+        <v>156.4</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>30.8</v>
+        <v>33.96</v>
       </c>
       <c r="K64" t="n">
-        <v>79.16</v>
+        <v>87.27</v>
       </c>
       <c r="L64" t="n">
-        <v>84.94</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>66.44</v>
+        <v>74.58</v>
       </c>
       <c r="K65" t="n">
-        <v>28.75</v>
+        <v>32.28</v>
       </c>
       <c r="L65" t="n">
-        <v>72.40000000000001</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-89.28</v>
+        <v>-100.24</v>
       </c>
       <c r="K66" t="n">
-        <v>41.42</v>
+        <v>46.5</v>
       </c>
       <c r="L66" t="n">
-        <v>98.42</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-102.77</v>
+        <v>-115.96</v>
       </c>
       <c r="K67" t="n">
-        <v>15.69</v>
+        <v>17.7</v>
       </c>
       <c r="L67" t="n">
-        <v>103.96</v>
+        <v>117.31</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>112.42</v>
+        <v>131.26</v>
       </c>
       <c r="K68" t="n">
-        <v>41.44</v>
+        <v>48.39</v>
       </c>
       <c r="L68" t="n">
-        <v>119.82</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-78.56</v>
+        <v>-92.22</v>
       </c>
       <c r="K69" t="n">
-        <v>206.64</v>
+        <v>242.56</v>
       </c>
       <c r="L69" t="n">
-        <v>221.07</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.44</v>
+        <v>-2.86</v>
       </c>
       <c r="K70" t="n">
-        <v>167.88</v>
+        <v>196.91</v>
       </c>
       <c r="L70" t="n">
-        <v>167.89</v>
+        <v>196.93</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>66.72</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-106.33</v>
+        <v>-126.32</v>
       </c>
       <c r="L71" t="n">
-        <v>125.53</v>
+        <v>149.13</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-130.8</v>
+        <v>-152.55</v>
       </c>
       <c r="K72" t="n">
-        <v>118.03</v>
+        <v>137.66</v>
       </c>
       <c r="L72" t="n">
-        <v>176.18</v>
+        <v>205.48</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-196.55</v>
+        <v>-230.09</v>
       </c>
       <c r="K73" t="n">
-        <v>99.95</v>
+        <v>117.01</v>
       </c>
       <c r="L73" t="n">
-        <v>220.5</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-36.75</v>
+        <v>-38.4</v>
       </c>
       <c r="K74" t="n">
-        <v>39.38</v>
+        <v>41.15</v>
       </c>
       <c r="L74" t="n">
-        <v>53.86</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>16.07</v>
+        <v>16.69</v>
       </c>
       <c r="K75" t="n">
-        <v>46.64</v>
+        <v>48.46</v>
       </c>
       <c r="L75" t="n">
-        <v>49.33</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>94.14</v>
+        <v>99.19</v>
       </c>
       <c r="K76" t="n">
-        <v>37.48</v>
+        <v>39.49</v>
       </c>
       <c r="L76" t="n">
-        <v>101.33</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-99.76000000000001</v>
+        <v>-107.94</v>
       </c>
       <c r="K77" t="n">
-        <v>53.04</v>
+        <v>57.39</v>
       </c>
       <c r="L77" t="n">
-        <v>112.99</v>
+        <v>122.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>8.74</v>
+        <v>9.6</v>
       </c>
       <c r="K78" t="n">
-        <v>-116.37</v>
+        <v>-127.82</v>
       </c>
       <c r="L78" t="n">
-        <v>116.7</v>
+        <v>128.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>16.01</v>
+        <v>17.52</v>
       </c>
       <c r="K79" t="n">
-        <v>124.63</v>
+        <v>136.38</v>
       </c>
       <c r="L79" t="n">
-        <v>125.66</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>116.35</v>
+        <v>134.45</v>
       </c>
       <c r="K80" t="n">
-        <v>23.47</v>
+        <v>27.13</v>
       </c>
       <c r="L80" t="n">
-        <v>118.7</v>
+        <v>137.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>104.43</v>
+        <v>117.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-13.31</v>
+        <v>-14.92</v>
       </c>
       <c r="L81" t="n">
-        <v>105.28</v>
+        <v>117.99</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-150.83</v>
+        <v>-171.07</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.39</v>
+        <v>-11.78</v>
       </c>
       <c r="L82" t="n">
-        <v>151.19</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-55.83</v>
+        <v>-65.95999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>127.84</v>
+        <v>151.03</v>
       </c>
       <c r="L83" t="n">
-        <v>139.5</v>
+        <v>164.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>59.39</v>
+        <v>70.02</v>
       </c>
       <c r="K84" t="n">
-        <v>105.47</v>
+        <v>124.35</v>
       </c>
       <c r="L84" t="n">
-        <v>121.04</v>
+        <v>142.71</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>64.72</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>182.23</v>
+        <v>210.66</v>
       </c>
       <c r="L85" t="n">
-        <v>193.38</v>
+        <v>223.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>106.12</v>
+        <v>124.77</v>
       </c>
       <c r="K86" t="n">
-        <v>164.55</v>
+        <v>193.47</v>
       </c>
       <c r="L86" t="n">
-        <v>195.8</v>
+        <v>230.21</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-118.82</v>
+        <v>-141.87</v>
       </c>
       <c r="K87" t="n">
-        <v>170.04</v>
+        <v>203.03</v>
       </c>
       <c r="L87" t="n">
-        <v>207.44</v>
+        <v>247.69</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>79.08</v>
+        <v>93.56</v>
       </c>
       <c r="K88" t="n">
-        <v>-138.49</v>
+        <v>-163.86</v>
       </c>
       <c r="L88" t="n">
-        <v>159.47</v>
+        <v>188.69</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.31</v>
+        <v>-8.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-43.14</v>
+        <v>-28.43</v>
       </c>
       <c r="L14" t="n">
-        <v>45.14</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>38.16</v>
+        <v>28.62</v>
       </c>
       <c r="K15" t="n">
-        <v>-45.76</v>
+        <v>-34.32</v>
       </c>
       <c r="L15" t="n">
-        <v>59.58</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>56.53</v>
+        <v>41.15</v>
       </c>
       <c r="K16" t="n">
-        <v>16.64</v>
+        <v>12.11</v>
       </c>
       <c r="L16" t="n">
-        <v>58.93</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-14.42</v>
+        <v>-10.82</v>
       </c>
       <c r="K17" t="n">
-        <v>-118.22</v>
+        <v>-88.67</v>
       </c>
       <c r="L17" t="n">
-        <v>119.1</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-53.28</v>
+        <v>-39.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-36.54</v>
+        <v>-27.32</v>
       </c>
       <c r="L18" t="n">
-        <v>64.61</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>34.18</v>
+        <v>25.64</v>
       </c>
       <c r="K19" t="n">
-        <v>-42.78</v>
+        <v>-32.09</v>
       </c>
       <c r="L19" t="n">
-        <v>54.76</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>75.87</v>
+        <v>56.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-57.26</v>
+        <v>-42.95</v>
       </c>
       <c r="L20" t="n">
-        <v>95.06</v>
+        <v>71.29000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-40.72</v>
+        <v>-30.54</v>
       </c>
       <c r="K21" t="n">
-        <v>99.78</v>
+        <v>74.83</v>
       </c>
       <c r="L21" t="n">
-        <v>107.76</v>
+        <v>80.81999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-111.33</v>
+        <v>-83.5</v>
       </c>
       <c r="K22" t="n">
-        <v>68.48</v>
+        <v>51.36</v>
       </c>
       <c r="L22" t="n">
-        <v>130.7</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-113.4</v>
+        <v>-80.05</v>
       </c>
       <c r="K23" t="n">
-        <v>-184.89</v>
+        <v>-130.52</v>
       </c>
       <c r="L23" t="n">
-        <v>216.89</v>
+        <v>153.12</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>132.72</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>124.04</v>
+        <v>93.03</v>
       </c>
       <c r="L24" t="n">
-        <v>181.66</v>
+        <v>136.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>59.45</v>
+        <v>44.59</v>
       </c>
       <c r="K25" t="n">
-        <v>-193.6</v>
+        <v>-145.2</v>
       </c>
       <c r="L25" t="n">
-        <v>202.53</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>137.84</v>
+        <v>103.38</v>
       </c>
       <c r="K26" t="n">
-        <v>-101.81</v>
+        <v>-76.36</v>
       </c>
       <c r="L26" t="n">
-        <v>171.36</v>
+        <v>128.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-34.43</v>
+        <v>-25.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-158.24</v>
+        <v>-118.68</v>
       </c>
       <c r="L27" t="n">
-        <v>161.95</v>
+        <v>121.46</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>34.12</v>
+        <v>24.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-247.39</v>
+        <v>-176.1</v>
       </c>
       <c r="L28" t="n">
-        <v>249.73</v>
+        <v>177.77</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>30.86</v>
+        <v>22.55</v>
       </c>
       <c r="K29" t="n">
-        <v>40.9</v>
+        <v>29.88</v>
       </c>
       <c r="L29" t="n">
-        <v>51.24</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.54</v>
+        <v>-0.25</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.87</v>
+        <v>-15.52</v>
       </c>
       <c r="L30" t="n">
-        <v>33.87</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>54.13</v>
+        <v>37.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-60.37</v>
+        <v>-41.41</v>
       </c>
       <c r="L31" t="n">
-        <v>81.08</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>40.02</v>
+        <v>30.01</v>
       </c>
       <c r="K32" t="n">
-        <v>-99.48</v>
+        <v>-74.61</v>
       </c>
       <c r="L32" t="n">
-        <v>107.22</v>
+        <v>80.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.66</v>
+        <v>-0.49</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.61</v>
+        <v>-35.71</v>
       </c>
       <c r="L33" t="n">
-        <v>47.61</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-40.8</v>
+        <v>-27.92</v>
       </c>
       <c r="K34" t="n">
-        <v>-78.18000000000001</v>
+        <v>-53.5</v>
       </c>
       <c r="L34" t="n">
-        <v>88.18000000000001</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-38.11</v>
+        <v>-20.14</v>
       </c>
       <c r="K35" t="n">
-        <v>55.95</v>
+        <v>29.57</v>
       </c>
       <c r="L35" t="n">
-        <v>67.69</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>53.39</v>
+        <v>37.68</v>
       </c>
       <c r="K36" t="n">
-        <v>-57.59</v>
+        <v>-40.64</v>
       </c>
       <c r="L36" t="n">
-        <v>78.53</v>
+        <v>55.42</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-144.65</v>
+        <v>-104.6</v>
       </c>
       <c r="K37" t="n">
-        <v>95.58</v>
+        <v>69.11</v>
       </c>
       <c r="L37" t="n">
-        <v>173.38</v>
+        <v>125.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-84.79000000000001</v>
+        <v>-61.55</v>
       </c>
       <c r="K38" t="n">
-        <v>111.45</v>
+        <v>80.91</v>
       </c>
       <c r="L38" t="n">
-        <v>140.03</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-64.3</v>
+        <v>-46.24</v>
       </c>
       <c r="K39" t="n">
-        <v>191.07</v>
+        <v>137.4</v>
       </c>
       <c r="L39" t="n">
-        <v>201.6</v>
+        <v>144.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>163.62</v>
+        <v>117.94</v>
       </c>
       <c r="K40" t="n">
-        <v>-107.25</v>
+        <v>-77.31</v>
       </c>
       <c r="L40" t="n">
-        <v>195.64</v>
+        <v>141.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-265.3</v>
+        <v>-194.22</v>
       </c>
       <c r="K41" t="n">
-        <v>-25.54</v>
+        <v>-18.69</v>
       </c>
       <c r="L41" t="n">
-        <v>266.53</v>
+        <v>195.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>198.99</v>
+        <v>146.37</v>
       </c>
       <c r="K42" t="n">
-        <v>-122.56</v>
+        <v>-90.15000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>233.71</v>
+        <v>171.91</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>140.09</v>
+        <v>104.05</v>
       </c>
       <c r="K43" t="n">
-        <v>-314.19</v>
+        <v>-233.34</v>
       </c>
       <c r="L43" t="n">
-        <v>344</v>
+        <v>255.49</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.91</v>
+        <v>-2.81</v>
       </c>
       <c r="K44" t="n">
-        <v>-91.29000000000001</v>
+        <v>-65.52</v>
       </c>
       <c r="L44" t="n">
-        <v>91.38</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.44</v>
+        <v>-7.66</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.37</v>
+        <v>-33.75</v>
       </c>
       <c r="L45" t="n">
-        <v>51.65</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.57</v>
+        <v>-12.2</v>
       </c>
       <c r="K46" t="n">
-        <v>40.32</v>
+        <v>29.67</v>
       </c>
       <c r="L46" t="n">
-        <v>43.59</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-46.28</v>
+        <v>-34.71</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.92</v>
+        <v>-6.69</v>
       </c>
       <c r="L47" t="n">
-        <v>47.14</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>80.98</v>
+        <v>57.38</v>
       </c>
       <c r="K48" t="n">
-        <v>155.41</v>
+        <v>110.12</v>
       </c>
       <c r="L48" t="n">
-        <v>175.24</v>
+        <v>124.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>45.72</v>
+        <v>33.62</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.47</v>
+        <v>-48.89</v>
       </c>
       <c r="L49" t="n">
-        <v>80.68000000000001</v>
+        <v>59.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>47.21</v>
+        <v>35.41</v>
       </c>
       <c r="K50" t="n">
-        <v>55.39</v>
+        <v>41.54</v>
       </c>
       <c r="L50" t="n">
-        <v>72.78</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>37.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-47.31</v>
+        <v>-12.41</v>
       </c>
       <c r="L51" t="n">
-        <v>60.67</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-91.33</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-24.86</v>
+        <v>-18.31</v>
       </c>
       <c r="L52" t="n">
-        <v>94.66</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-167.43</v>
+        <v>-115.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-141.78</v>
+        <v>-98.13</v>
       </c>
       <c r="L53" t="n">
-        <v>219.4</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-96.22</v>
+        <v>-69.86</v>
       </c>
       <c r="K54" t="n">
-        <v>-70.67</v>
+        <v>-51.31</v>
       </c>
       <c r="L54" t="n">
-        <v>119.39</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>217.61</v>
+        <v>161.95</v>
       </c>
       <c r="K55" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
       <c r="L55" t="n">
-        <v>217.62</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>13.69</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-176.7</v>
+        <v>-120.85</v>
       </c>
       <c r="L56" t="n">
-        <v>177.23</v>
+        <v>121.21</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>176.61</v>
+        <v>118</v>
       </c>
       <c r="K57" t="n">
-        <v>-236.39</v>
+        <v>-157.94</v>
       </c>
       <c r="L57" t="n">
-        <v>295.08</v>
+        <v>197.15</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-199.64</v>
+        <v>-142.11</v>
       </c>
       <c r="K58" t="n">
-        <v>-78.28</v>
+        <v>-55.72</v>
       </c>
       <c r="L58" t="n">
-        <v>214.44</v>
+        <v>152.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>51.81</v>
+        <v>37.85</v>
       </c>
       <c r="K59" t="n">
-        <v>60.05</v>
+        <v>43.86</v>
       </c>
       <c r="L59" t="n">
-        <v>79.31</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>23.36</v>
+        <v>16.82</v>
       </c>
       <c r="K60" t="n">
-        <v>-73.51000000000001</v>
+        <v>-52.94</v>
       </c>
       <c r="L60" t="n">
-        <v>77.13</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
-        <v>-31</v>
+        <v>-20.33</v>
       </c>
       <c r="L61" t="n">
-        <v>36</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-75.95999999999999</v>
+        <v>-51.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-15.23</v>
+        <v>-10.34</v>
       </c>
       <c r="L62" t="n">
-        <v>77.48</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>155.85</v>
+        <v>102.98</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.13</v>
+        <v>-8.67</v>
       </c>
       <c r="L63" t="n">
-        <v>156.4</v>
+        <v>103.35</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>33.96</v>
+        <v>23.44</v>
       </c>
       <c r="K64" t="n">
-        <v>87.27</v>
+        <v>60.23</v>
       </c>
       <c r="L64" t="n">
-        <v>93.64</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>74.58</v>
+        <v>49.05</v>
       </c>
       <c r="K65" t="n">
-        <v>32.28</v>
+        <v>21.23</v>
       </c>
       <c r="L65" t="n">
-        <v>81.27</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-100.24</v>
+        <v>-68.66</v>
       </c>
       <c r="K66" t="n">
-        <v>46.5</v>
+        <v>31.85</v>
       </c>
       <c r="L66" t="n">
-        <v>110.5</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-115.96</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>17.7</v>
+        <v>12.99</v>
       </c>
       <c r="L67" t="n">
-        <v>117.31</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>131.26</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>48.39</v>
+        <v>35.13</v>
       </c>
       <c r="L68" t="n">
-        <v>139.9</v>
+        <v>101.56</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-92.22</v>
+        <v>-62.25</v>
       </c>
       <c r="K69" t="n">
-        <v>242.56</v>
+        <v>163.72</v>
       </c>
       <c r="L69" t="n">
-        <v>259.5</v>
+        <v>175.15</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.86</v>
+        <v>-2.02</v>
       </c>
       <c r="K70" t="n">
-        <v>196.91</v>
+        <v>139.32</v>
       </c>
       <c r="L70" t="n">
-        <v>196.93</v>
+        <v>139.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>79.26000000000001</v>
+        <v>56.04</v>
       </c>
       <c r="K71" t="n">
-        <v>-126.32</v>
+        <v>-89.31</v>
       </c>
       <c r="L71" t="n">
-        <v>149.13</v>
+        <v>105.43</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-152.55</v>
+        <v>-96.55</v>
       </c>
       <c r="K72" t="n">
-        <v>137.66</v>
+        <v>87.13</v>
       </c>
       <c r="L72" t="n">
-        <v>205.48</v>
+        <v>130.05</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-230.09</v>
+        <v>-161.94</v>
       </c>
       <c r="K73" t="n">
-        <v>117.01</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>258.14</v>
+        <v>181.68</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-38.4</v>
+        <v>-27.28</v>
       </c>
       <c r="K74" t="n">
-        <v>41.15</v>
+        <v>29.24</v>
       </c>
       <c r="L74" t="n">
-        <v>56.29</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>16.69</v>
+        <v>11.15</v>
       </c>
       <c r="K75" t="n">
-        <v>48.46</v>
+        <v>32.38</v>
       </c>
       <c r="L75" t="n">
-        <v>51.25</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>99.19</v>
+        <v>65.2</v>
       </c>
       <c r="K76" t="n">
-        <v>39.49</v>
+        <v>25.96</v>
       </c>
       <c r="L76" t="n">
-        <v>106.76</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-107.94</v>
+        <v>-73.66</v>
       </c>
       <c r="K77" t="n">
-        <v>57.39</v>
+        <v>39.17</v>
       </c>
       <c r="L77" t="n">
-        <v>122.25</v>
+        <v>83.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>9.6</v>
+        <v>6.57</v>
       </c>
       <c r="K78" t="n">
-        <v>-127.82</v>
+        <v>-87.48</v>
       </c>
       <c r="L78" t="n">
-        <v>128.18</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>17.52</v>
+        <v>11.7</v>
       </c>
       <c r="K79" t="n">
-        <v>136.38</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>137.5</v>
+        <v>91.81999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>134.45</v>
+        <v>88.69</v>
       </c>
       <c r="K80" t="n">
-        <v>27.13</v>
+        <v>17.89</v>
       </c>
       <c r="L80" t="n">
-        <v>137.16</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>117.05</v>
+        <v>79.91</v>
       </c>
       <c r="K81" t="n">
-        <v>-14.92</v>
+        <v>-10.19</v>
       </c>
       <c r="L81" t="n">
-        <v>117.99</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-171.07</v>
+        <v>-108.92</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.78</v>
+        <v>-7.5</v>
       </c>
       <c r="L82" t="n">
-        <v>171.47</v>
+        <v>109.18</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-65.95999999999999</v>
+        <v>-40.12</v>
       </c>
       <c r="K83" t="n">
-        <v>151.03</v>
+        <v>91.87</v>
       </c>
       <c r="L83" t="n">
-        <v>164.8</v>
+        <v>100.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>70.02</v>
+        <v>48.46</v>
       </c>
       <c r="K84" t="n">
-        <v>124.35</v>
+        <v>86.06</v>
       </c>
       <c r="L84" t="n">
-        <v>142.71</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>74.81999999999999</v>
+        <v>50.91</v>
       </c>
       <c r="K85" t="n">
-        <v>210.66</v>
+        <v>143.36</v>
       </c>
       <c r="L85" t="n">
-        <v>223.56</v>
+        <v>152.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>124.77</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>193.47</v>
+        <v>145.1</v>
       </c>
       <c r="L86" t="n">
-        <v>230.21</v>
+        <v>172.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-141.87</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>203.03</v>
+        <v>141.94</v>
       </c>
       <c r="L87" t="n">
-        <v>247.69</v>
+        <v>173.16</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>93.56</v>
+        <v>60.15</v>
       </c>
       <c r="K88" t="n">
-        <v>-163.86</v>
+        <v>-105.34</v>
       </c>
       <c r="L88" t="n">
-        <v>188.69</v>
+        <v>121.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.77</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.43</v>
+        <v>-31.15</v>
       </c>
       <c r="L14" t="n">
-        <v>29.75</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>28.62</v>
+        <v>28.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.32</v>
+        <v>-34.59</v>
       </c>
       <c r="L15" t="n">
-        <v>44.69</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>41.15</v>
+        <v>41.65</v>
       </c>
       <c r="K16" t="n">
-        <v>12.11</v>
+        <v>12.26</v>
       </c>
       <c r="L16" t="n">
-        <v>42.89</v>
+        <v>43.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.82</v>
+        <v>-10.43</v>
       </c>
       <c r="K17" t="n">
-        <v>-88.67</v>
+        <v>-85.54000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>89.31999999999999</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-39.83</v>
+        <v>-41.77</v>
       </c>
       <c r="K18" t="n">
-        <v>-27.32</v>
+        <v>-28.65</v>
       </c>
       <c r="L18" t="n">
-        <v>48.3</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>25.64</v>
+        <v>27.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-32.09</v>
+        <v>-34.02</v>
       </c>
       <c r="L19" t="n">
-        <v>41.07</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>56.9</v>
+        <v>58.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-42.95</v>
+        <v>-44.53</v>
       </c>
       <c r="L20" t="n">
-        <v>71.29000000000001</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.54</v>
+        <v>-30.97</v>
       </c>
       <c r="K21" t="n">
-        <v>74.83</v>
+        <v>75.89</v>
       </c>
       <c r="L21" t="n">
-        <v>80.81999999999999</v>
+        <v>81.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-83.5</v>
+        <v>-82.83</v>
       </c>
       <c r="K22" t="n">
-        <v>51.36</v>
+        <v>50.94</v>
       </c>
       <c r="L22" t="n">
-        <v>98.03</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-80.05</v>
+        <v>-78.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-130.52</v>
+        <v>-127.37</v>
       </c>
       <c r="L23" t="n">
-        <v>153.12</v>
+        <v>149.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>99.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>93.03</v>
+        <v>91.87</v>
       </c>
       <c r="L24" t="n">
-        <v>136.25</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>44.59</v>
+        <v>43.35</v>
       </c>
       <c r="K25" t="n">
-        <v>-145.2</v>
+        <v>-141.17</v>
       </c>
       <c r="L25" t="n">
-        <v>151.89</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>103.38</v>
+        <v>108.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-76.36</v>
+        <v>-79.83</v>
       </c>
       <c r="L26" t="n">
-        <v>128.52</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-25.82</v>
+        <v>-27.48</v>
       </c>
       <c r="K27" t="n">
-        <v>-118.68</v>
+        <v>-126.31</v>
       </c>
       <c r="L27" t="n">
-        <v>121.46</v>
+        <v>129.27</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>24.29</v>
+        <v>24.59</v>
       </c>
       <c r="K28" t="n">
-        <v>-176.1</v>
+        <v>-178.31</v>
       </c>
       <c r="L28" t="n">
-        <v>177.77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>22.55</v>
+        <v>23.29</v>
       </c>
       <c r="K29" t="n">
-        <v>29.88</v>
+        <v>30.86</v>
       </c>
       <c r="L29" t="n">
-        <v>37.43</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="K30" t="n">
-        <v>-15.52</v>
+        <v>-15.18</v>
       </c>
       <c r="L30" t="n">
-        <v>15.52</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>37.13</v>
+        <v>36.85</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.41</v>
+        <v>-41.09</v>
       </c>
       <c r="L31" t="n">
-        <v>55.62</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>30.01</v>
+        <v>29.42</v>
       </c>
       <c r="K32" t="n">
-        <v>-74.61</v>
+        <v>-73.12</v>
       </c>
       <c r="L32" t="n">
-        <v>80.42</v>
+        <v>78.81999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.49</v>
+        <v>-0.54</v>
       </c>
       <c r="K33" t="n">
-        <v>-35.71</v>
+        <v>-39.1</v>
       </c>
       <c r="L33" t="n">
-        <v>35.71</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.92</v>
+        <v>-28.63</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.5</v>
+        <v>-54.86</v>
       </c>
       <c r="L34" t="n">
-        <v>60.35</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-20.14</v>
+        <v>-19.69</v>
       </c>
       <c r="K35" t="n">
-        <v>29.57</v>
+        <v>28.9</v>
       </c>
       <c r="L35" t="n">
-        <v>35.78</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>37.68</v>
+        <v>40.89</v>
       </c>
       <c r="K36" t="n">
-        <v>-40.64</v>
+        <v>-44.11</v>
       </c>
       <c r="L36" t="n">
-        <v>55.42</v>
+        <v>60.14</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-104.6</v>
+        <v>-102.15</v>
       </c>
       <c r="K37" t="n">
-        <v>69.11</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>125.37</v>
+        <v>122.43</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-61.55</v>
+        <v>-62.76</v>
       </c>
       <c r="K38" t="n">
-        <v>80.91</v>
+        <v>82.5</v>
       </c>
       <c r="L38" t="n">
-        <v>101.66</v>
+        <v>103.66</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-46.24</v>
+        <v>-45.57</v>
       </c>
       <c r="K39" t="n">
-        <v>137.4</v>
+        <v>135.42</v>
       </c>
       <c r="L39" t="n">
-        <v>144.97</v>
+        <v>142.88</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>117.94</v>
+        <v>116.14</v>
       </c>
       <c r="K40" t="n">
-        <v>-77.31</v>
+        <v>-76.13</v>
       </c>
       <c r="L40" t="n">
-        <v>141.02</v>
+        <v>138.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-194.22</v>
+        <v>-193.46</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.69</v>
+        <v>-18.62</v>
       </c>
       <c r="L41" t="n">
-        <v>195.12</v>
+        <v>194.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>146.37</v>
+        <v>147.11</v>
       </c>
       <c r="K42" t="n">
-        <v>-90.15000000000001</v>
+        <v>-90.61</v>
       </c>
       <c r="L42" t="n">
-        <v>171.91</v>
+        <v>172.77</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>104.05</v>
+        <v>100.37</v>
       </c>
       <c r="K43" t="n">
-        <v>-233.34</v>
+        <v>-225.11</v>
       </c>
       <c r="L43" t="n">
-        <v>255.49</v>
+        <v>246.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.81</v>
+        <v>-2.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-65.52</v>
+        <v>-63.01</v>
       </c>
       <c r="L44" t="n">
-        <v>65.58</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.66</v>
+        <v>-8.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-33.75</v>
+        <v>-35.66</v>
       </c>
       <c r="L45" t="n">
-        <v>34.61</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.2</v>
+        <v>-12.8</v>
       </c>
       <c r="K46" t="n">
-        <v>29.67</v>
+        <v>31.14</v>
       </c>
       <c r="L46" t="n">
-        <v>32.08</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.71</v>
+        <v>-37.4</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.69</v>
+        <v>-7.21</v>
       </c>
       <c r="L47" t="n">
-        <v>35.35</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>57.38</v>
+        <v>53.94</v>
       </c>
       <c r="K48" t="n">
-        <v>110.12</v>
+        <v>103.52</v>
       </c>
       <c r="L48" t="n">
-        <v>124.17</v>
+        <v>116.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>33.62</v>
+        <v>32.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.89</v>
+        <v>-46.75</v>
       </c>
       <c r="L49" t="n">
-        <v>59.33</v>
+        <v>56.74</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>35.41</v>
+        <v>37.9</v>
       </c>
       <c r="K50" t="n">
-        <v>41.54</v>
+        <v>44.46</v>
       </c>
       <c r="L50" t="n">
-        <v>54.58</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>9.970000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.41</v>
+        <v>-12.18</v>
       </c>
       <c r="L51" t="n">
-        <v>15.92</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-67.23999999999999</v>
+        <v>-69.68000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.31</v>
+        <v>-18.97</v>
       </c>
       <c r="L52" t="n">
-        <v>69.69</v>
+        <v>72.22</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-115.88</v>
+        <v>-113.19</v>
       </c>
       <c r="K53" t="n">
-        <v>-98.13</v>
+        <v>-95.86</v>
       </c>
       <c r="L53" t="n">
-        <v>151.84</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-69.86</v>
+        <v>-73.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-51.31</v>
+        <v>-53.97</v>
       </c>
       <c r="L54" t="n">
-        <v>86.68000000000001</v>
+        <v>91.17</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>161.95</v>
+        <v>155.79</v>
       </c>
       <c r="K55" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="L55" t="n">
-        <v>161.96</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>9.359999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-120.85</v>
+        <v>-127.68</v>
       </c>
       <c r="L56" t="n">
-        <v>121.21</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>118</v>
+        <v>116.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-157.94</v>
+        <v>-155.75</v>
       </c>
       <c r="L57" t="n">
-        <v>197.15</v>
+        <v>194.42</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-142.11</v>
+        <v>-145.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.72</v>
+        <v>-56.95</v>
       </c>
       <c r="L58" t="n">
-        <v>152.65</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>37.85</v>
+        <v>36.59</v>
       </c>
       <c r="K59" t="n">
-        <v>43.86</v>
+        <v>42.4</v>
       </c>
       <c r="L59" t="n">
-        <v>57.94</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>16.82</v>
+        <v>16.51</v>
       </c>
       <c r="K60" t="n">
-        <v>-52.94</v>
+        <v>-51.97</v>
       </c>
       <c r="L60" t="n">
-        <v>55.55</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>12</v>
+        <v>11.71</v>
       </c>
       <c r="K61" t="n">
-        <v>-20.33</v>
+        <v>-19.84</v>
       </c>
       <c r="L61" t="n">
-        <v>23.61</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.56</v>
+        <v>-53.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.34</v>
+        <v>-10.73</v>
       </c>
       <c r="L62" t="n">
-        <v>52.58</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>102.98</v>
+        <v>98.86</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.67</v>
+        <v>-8.33</v>
       </c>
       <c r="L63" t="n">
-        <v>103.35</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>23.44</v>
+        <v>23.6</v>
       </c>
       <c r="K64" t="n">
-        <v>60.23</v>
+        <v>60.64</v>
       </c>
       <c r="L64" t="n">
-        <v>64.63</v>
+        <v>65.06999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>49.05</v>
+        <v>52.9</v>
       </c>
       <c r="K65" t="n">
-        <v>21.23</v>
+        <v>22.89</v>
       </c>
       <c r="L65" t="n">
-        <v>53.44</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-68.66</v>
+        <v>-70.15000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>31.85</v>
+        <v>32.54</v>
       </c>
       <c r="L66" t="n">
-        <v>75.69</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.06999999999999</v>
+        <v>-85.09</v>
       </c>
       <c r="K67" t="n">
         <v>12.99</v>
       </c>
       <c r="L67" t="n">
-        <v>86.05</v>
+        <v>86.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>95.29000000000001</v>
+        <v>96.64</v>
       </c>
       <c r="K68" t="n">
-        <v>35.13</v>
+        <v>35.63</v>
       </c>
       <c r="L68" t="n">
-        <v>101.56</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-62.25</v>
+        <v>-60.14</v>
       </c>
       <c r="K69" t="n">
-        <v>163.72</v>
+        <v>158.18</v>
       </c>
       <c r="L69" t="n">
-        <v>175.15</v>
+        <v>169.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.02</v>
+        <v>-1.99</v>
       </c>
       <c r="K70" t="n">
-        <v>139.32</v>
+        <v>136.93</v>
       </c>
       <c r="L70" t="n">
-        <v>139.34</v>
+        <v>136.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>56.04</v>
+        <v>60.72</v>
       </c>
       <c r="K71" t="n">
-        <v>-89.31</v>
+        <v>-96.78</v>
       </c>
       <c r="L71" t="n">
-        <v>105.43</v>
+        <v>114.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-96.55</v>
+        <v>-100.76</v>
       </c>
       <c r="K72" t="n">
-        <v>87.13</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>130.05</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-161.94</v>
+        <v>-160.64</v>
       </c>
       <c r="K73" t="n">
-        <v>82.34999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="L73" t="n">
-        <v>181.68</v>
+        <v>180.22</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.28</v>
+        <v>-27.73</v>
       </c>
       <c r="K74" t="n">
-        <v>29.24</v>
+        <v>29.72</v>
       </c>
       <c r="L74" t="n">
-        <v>39.99</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>11.15</v>
+        <v>11.67</v>
       </c>
       <c r="K75" t="n">
-        <v>32.38</v>
+        <v>33.88</v>
       </c>
       <c r="L75" t="n">
-        <v>34.25</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>65.2</v>
+        <v>62.92</v>
       </c>
       <c r="K76" t="n">
-        <v>25.96</v>
+        <v>25.05</v>
       </c>
       <c r="L76" t="n">
-        <v>70.18000000000001</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-73.66</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>39.17</v>
+        <v>38.11</v>
       </c>
       <c r="L77" t="n">
-        <v>83.43000000000001</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>6.57</v>
+        <v>5.44</v>
       </c>
       <c r="K78" t="n">
-        <v>-87.48</v>
+        <v>-72.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>87.73</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>11.7</v>
+        <v>11.33</v>
       </c>
       <c r="K79" t="n">
-        <v>91.06999999999999</v>
+        <v>88.22</v>
       </c>
       <c r="L79" t="n">
-        <v>91.81999999999999</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>88.69</v>
+        <v>89.97</v>
       </c>
       <c r="K80" t="n">
-        <v>17.89</v>
+        <v>18.15</v>
       </c>
       <c r="L80" t="n">
-        <v>90.48</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>79.91</v>
+        <v>81.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-10.19</v>
+        <v>-10.33</v>
       </c>
       <c r="L81" t="n">
-        <v>80.56</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-108.92</v>
+        <v>-107.16</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.5</v>
+        <v>-7.38</v>
       </c>
       <c r="L82" t="n">
-        <v>109.18</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-40.12</v>
+        <v>-42.56</v>
       </c>
       <c r="K83" t="n">
-        <v>91.87</v>
+        <v>97.45</v>
       </c>
       <c r="L83" t="n">
-        <v>100.24</v>
+        <v>106.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>48.46</v>
+        <v>50.33</v>
       </c>
       <c r="K84" t="n">
-        <v>86.06</v>
+        <v>89.38</v>
       </c>
       <c r="L84" t="n">
-        <v>98.77</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>50.91</v>
+        <v>49.59</v>
       </c>
       <c r="K85" t="n">
-        <v>143.36</v>
+        <v>139.63</v>
       </c>
       <c r="L85" t="n">
-        <v>152.13</v>
+        <v>148.18</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>93.56999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="K86" t="n">
-        <v>145.1</v>
+        <v>144.9</v>
       </c>
       <c r="L86" t="n">
-        <v>172.66</v>
+        <v>172.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-99.18000000000001</v>
+        <v>-100.11</v>
       </c>
       <c r="K87" t="n">
-        <v>141.94</v>
+        <v>143.26</v>
       </c>
       <c r="L87" t="n">
-        <v>173.16</v>
+        <v>174.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>60.15</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-105.34</v>
+        <v>-112.45</v>
       </c>
       <c r="L88" t="n">
-        <v>121.3</v>
+        <v>129.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.609999999999999</v>
+        <v>-10.57</v>
       </c>
       <c r="K14" t="n">
-        <v>-31.15</v>
+        <v>-34.27</v>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>28.85</v>
+        <v>29.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.59</v>
+        <v>-34.91</v>
       </c>
       <c r="L15" t="n">
-        <v>45.05</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>41.65</v>
+        <v>42.22</v>
       </c>
       <c r="K16" t="n">
-        <v>12.26</v>
+        <v>12.43</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.43</v>
+        <v>-10</v>
       </c>
       <c r="K17" t="n">
-        <v>-85.54000000000001</v>
+        <v>-81.97</v>
       </c>
       <c r="L17" t="n">
-        <v>86.18000000000001</v>
+        <v>82.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-41.77</v>
+        <v>-43.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-28.65</v>
+        <v>-30.17</v>
       </c>
       <c r="L18" t="n">
-        <v>50.65</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>27.18</v>
+        <v>28.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.02</v>
+        <v>-36.23</v>
       </c>
       <c r="L19" t="n">
-        <v>43.55</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>58.99</v>
+        <v>61.38</v>
       </c>
       <c r="K20" t="n">
-        <v>-44.53</v>
+        <v>-46.33</v>
       </c>
       <c r="L20" t="n">
-        <v>73.91</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.97</v>
+        <v>-31.46</v>
       </c>
       <c r="K21" t="n">
-        <v>75.89</v>
+        <v>77.11</v>
       </c>
       <c r="L21" t="n">
-        <v>81.97</v>
+        <v>83.28</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-82.83</v>
+        <v>-82.06</v>
       </c>
       <c r="K22" t="n">
-        <v>50.94</v>
+        <v>50.47</v>
       </c>
       <c r="L22" t="n">
-        <v>97.23999999999999</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-78.12</v>
+        <v>-75.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-127.37</v>
+        <v>-123.76</v>
       </c>
       <c r="L23" t="n">
-        <v>149.41</v>
+        <v>145.18</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>98.29000000000001</v>
+        <v>96.87</v>
       </c>
       <c r="K24" t="n">
-        <v>91.87</v>
+        <v>90.53</v>
       </c>
       <c r="L24" t="n">
-        <v>134.54</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>43.35</v>
+        <v>41.93</v>
       </c>
       <c r="K25" t="n">
-        <v>-141.17</v>
+        <v>-136.55</v>
       </c>
       <c r="L25" t="n">
-        <v>147.67</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>108.08</v>
+        <v>113.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-79.83</v>
+        <v>-83.81</v>
       </c>
       <c r="L26" t="n">
-        <v>134.37</v>
+        <v>141.06</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-27.48</v>
+        <v>-29.38</v>
       </c>
       <c r="K27" t="n">
-        <v>-126.31</v>
+        <v>-135.04</v>
       </c>
       <c r="L27" t="n">
-        <v>129.27</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>24.59</v>
+        <v>24.94</v>
       </c>
       <c r="K28" t="n">
-        <v>-178.31</v>
+        <v>-180.83</v>
       </c>
       <c r="L28" t="n">
-        <v>180</v>
+        <v>182.54</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>23.29</v>
+        <v>24.13</v>
       </c>
       <c r="K29" t="n">
-        <v>30.86</v>
+        <v>31.98</v>
       </c>
       <c r="L29" t="n">
-        <v>38.66</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="K30" t="n">
-        <v>-15.18</v>
+        <v>-16.52</v>
       </c>
       <c r="L30" t="n">
-        <v>15.18</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>36.85</v>
+        <v>36.53</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.09</v>
+        <v>-40.74</v>
       </c>
       <c r="L31" t="n">
-        <v>55.2</v>
+        <v>54.72</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>29.42</v>
+        <v>28.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-73.12</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>78.81999999999999</v>
+        <v>76.98999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.1</v>
+        <v>-42.98</v>
       </c>
       <c r="L33" t="n">
-        <v>39.11</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-28.63</v>
+        <v>-29.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-54.86</v>
+        <v>-56.4</v>
       </c>
       <c r="L34" t="n">
-        <v>61.88</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-19.69</v>
+        <v>-21.49</v>
       </c>
       <c r="K35" t="n">
-        <v>28.9</v>
+        <v>31.55</v>
       </c>
       <c r="L35" t="n">
-        <v>34.97</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>40.89</v>
+        <v>44.56</v>
       </c>
       <c r="K36" t="n">
-        <v>-44.11</v>
+        <v>-48.07</v>
       </c>
       <c r="L36" t="n">
-        <v>60.14</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-102.15</v>
+        <v>-99.34999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>67.48999999999999</v>
+        <v>65.64</v>
       </c>
       <c r="L37" t="n">
-        <v>122.43</v>
+        <v>119.08</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-62.76</v>
+        <v>-64.14</v>
       </c>
       <c r="K38" t="n">
-        <v>82.5</v>
+        <v>84.31</v>
       </c>
       <c r="L38" t="n">
-        <v>103.66</v>
+        <v>105.94</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-45.57</v>
+        <v>-44.81</v>
       </c>
       <c r="K39" t="n">
-        <v>135.42</v>
+        <v>133.15</v>
       </c>
       <c r="L39" t="n">
-        <v>142.88</v>
+        <v>140.49</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>116.14</v>
+        <v>114.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-76.13</v>
+        <v>-74.78</v>
       </c>
       <c r="L40" t="n">
-        <v>138.87</v>
+        <v>136.41</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-193.46</v>
+        <v>-192.59</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.62</v>
+        <v>-18.54</v>
       </c>
       <c r="L41" t="n">
-        <v>194.35</v>
+        <v>193.48</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>147.11</v>
+        <v>147.95</v>
       </c>
       <c r="K42" t="n">
-        <v>-90.61</v>
+        <v>-91.13</v>
       </c>
       <c r="L42" t="n">
-        <v>172.77</v>
+        <v>173.76</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>100.37</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-225.11</v>
+        <v>-215.7</v>
       </c>
       <c r="L43" t="n">
-        <v>246.48</v>
+        <v>236.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.7</v>
+        <v>-2.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-63.01</v>
+        <v>-60.14</v>
       </c>
       <c r="L44" t="n">
-        <v>63.07</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.1</v>
+        <v>-8.59</v>
       </c>
       <c r="K45" t="n">
-        <v>-35.66</v>
+        <v>-37.84</v>
       </c>
       <c r="L45" t="n">
-        <v>36.56</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.8</v>
+        <v>-13.49</v>
       </c>
       <c r="K46" t="n">
-        <v>31.14</v>
+        <v>32.82</v>
       </c>
       <c r="L46" t="n">
-        <v>33.67</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-37.4</v>
+        <v>-40.47</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.21</v>
+        <v>-7.8</v>
       </c>
       <c r="L47" t="n">
-        <v>38.09</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>53.94</v>
+        <v>50.01</v>
       </c>
       <c r="K48" t="n">
-        <v>103.52</v>
+        <v>95.98</v>
       </c>
       <c r="L48" t="n">
-        <v>116.73</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>32.15</v>
+        <v>33.03</v>
       </c>
       <c r="K49" t="n">
-        <v>-46.75</v>
+        <v>-48.03</v>
       </c>
       <c r="L49" t="n">
-        <v>56.74</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>37.9</v>
+        <v>40.75</v>
       </c>
       <c r="K50" t="n">
-        <v>44.46</v>
+        <v>47.81</v>
       </c>
       <c r="L50" t="n">
-        <v>58.43</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>9.779999999999999</v>
+        <v>10.51</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.18</v>
+        <v>-13.09</v>
       </c>
       <c r="L51" t="n">
-        <v>15.62</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-69.68000000000001</v>
+        <v>-72.47</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.97</v>
+        <v>-19.73</v>
       </c>
       <c r="L52" t="n">
-        <v>72.22</v>
+        <v>75.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-113.19</v>
+        <v>-110.13</v>
       </c>
       <c r="K53" t="n">
-        <v>-95.86</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>148.33</v>
+        <v>144.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-73.48</v>
+        <v>-77.62</v>
       </c>
       <c r="K54" t="n">
-        <v>-53.97</v>
+        <v>-57.01</v>
       </c>
       <c r="L54" t="n">
-        <v>91.17</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>155.79</v>
+        <v>148.74</v>
       </c>
       <c r="K55" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="L55" t="n">
-        <v>155.8</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>9.890000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-127.68</v>
+        <v>-135.49</v>
       </c>
       <c r="L56" t="n">
-        <v>128.06</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>116.36</v>
+        <v>114.49</v>
       </c>
       <c r="K57" t="n">
-        <v>-155.75</v>
+        <v>-153.25</v>
       </c>
       <c r="L57" t="n">
-        <v>194.42</v>
+        <v>191.3</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-145.24</v>
+        <v>-148.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-56.95</v>
+        <v>-58.35</v>
       </c>
       <c r="L58" t="n">
-        <v>156</v>
+        <v>159.84</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>36.59</v>
+        <v>35.15</v>
       </c>
       <c r="K59" t="n">
-        <v>42.4</v>
+        <v>40.73</v>
       </c>
       <c r="L59" t="n">
-        <v>56.01</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>16.51</v>
+        <v>16.16</v>
       </c>
       <c r="K60" t="n">
-        <v>-51.97</v>
+        <v>-50.85</v>
       </c>
       <c r="L60" t="n">
-        <v>54.53</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>11.71</v>
+        <v>12.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.84</v>
+        <v>-21.79</v>
       </c>
       <c r="L61" t="n">
-        <v>23.04</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.51</v>
+        <v>-55.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.73</v>
+        <v>-11.17</v>
       </c>
       <c r="L62" t="n">
-        <v>54.57</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>98.86</v>
+        <v>94.16</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.33</v>
+        <v>-7.93</v>
       </c>
       <c r="L63" t="n">
-        <v>99.20999999999999</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>23.6</v>
+        <v>23.78</v>
       </c>
       <c r="K64" t="n">
-        <v>60.64</v>
+        <v>61.11</v>
       </c>
       <c r="L64" t="n">
-        <v>65.06999999999999</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>52.9</v>
+        <v>57.3</v>
       </c>
       <c r="K65" t="n">
-        <v>22.89</v>
+        <v>24.8</v>
       </c>
       <c r="L65" t="n">
-        <v>57.64</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-70.15000000000001</v>
+        <v>-71.84999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>32.54</v>
+        <v>33.33</v>
       </c>
       <c r="L66" t="n">
-        <v>77.33</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.09</v>
+        <v>-85.12</v>
       </c>
       <c r="K67" t="n">
         <v>12.99</v>
       </c>
       <c r="L67" t="n">
-        <v>86.08</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>96.64</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>35.63</v>
+        <v>36.2</v>
       </c>
       <c r="L68" t="n">
-        <v>103</v>
+        <v>104.64</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-60.14</v>
+        <v>-57.73</v>
       </c>
       <c r="K69" t="n">
-        <v>158.18</v>
+        <v>151.85</v>
       </c>
       <c r="L69" t="n">
-        <v>169.23</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.99</v>
+        <v>-1.95</v>
       </c>
       <c r="K70" t="n">
-        <v>136.93</v>
+        <v>134.19</v>
       </c>
       <c r="L70" t="n">
-        <v>136.94</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>60.72</v>
+        <v>66.08</v>
       </c>
       <c r="K71" t="n">
-        <v>-96.78</v>
+        <v>-105.31</v>
       </c>
       <c r="L71" t="n">
-        <v>114.25</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-100.76</v>
+        <v>-105.58</v>
       </c>
       <c r="K72" t="n">
-        <v>90.93000000000001</v>
+        <v>95.27</v>
       </c>
       <c r="L72" t="n">
-        <v>135.72</v>
+        <v>142.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-160.64</v>
+        <v>-159.15</v>
       </c>
       <c r="K73" t="n">
-        <v>81.69</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>180.22</v>
+        <v>178.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.73</v>
+        <v>-28.25</v>
       </c>
       <c r="K74" t="n">
-        <v>29.72</v>
+        <v>30.27</v>
       </c>
       <c r="L74" t="n">
-        <v>40.65</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>11.67</v>
+        <v>12.26</v>
       </c>
       <c r="K75" t="n">
-        <v>33.88</v>
+        <v>35.59</v>
       </c>
       <c r="L75" t="n">
-        <v>35.83</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>62.92</v>
+        <v>60.31</v>
       </c>
       <c r="K76" t="n">
-        <v>25.05</v>
+        <v>24.01</v>
       </c>
       <c r="L76" t="n">
-        <v>67.72</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-71.68000000000001</v>
+        <v>-69.41</v>
       </c>
       <c r="K77" t="n">
-        <v>38.11</v>
+        <v>36.91</v>
       </c>
       <c r="L77" t="n">
-        <v>81.18000000000001</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>5.44</v>
+        <v>5.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.40000000000001</v>
+        <v>-71.81999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>72.59999999999999</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>11.33</v>
+        <v>10.92</v>
       </c>
       <c r="K79" t="n">
-        <v>88.22</v>
+        <v>84.97</v>
       </c>
       <c r="L79" t="n">
-        <v>88.95</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>89.97</v>
+        <v>91.42</v>
       </c>
       <c r="K80" t="n">
-        <v>18.15</v>
+        <v>18.44</v>
       </c>
       <c r="L80" t="n">
-        <v>91.78</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>81.06</v>
+        <v>82.38</v>
       </c>
       <c r="K81" t="n">
-        <v>-10.33</v>
+        <v>-10.5</v>
       </c>
       <c r="L81" t="n">
-        <v>81.72</v>
+        <v>83.04000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-107.16</v>
+        <v>-105.14</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.38</v>
+        <v>-7.24</v>
       </c>
       <c r="L82" t="n">
-        <v>107.41</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-42.56</v>
+        <v>-45.35</v>
       </c>
       <c r="K83" t="n">
-        <v>97.45</v>
+        <v>103.84</v>
       </c>
       <c r="L83" t="n">
-        <v>106.34</v>
+        <v>113.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>50.33</v>
+        <v>52.47</v>
       </c>
       <c r="K84" t="n">
-        <v>89.38</v>
+        <v>93.17</v>
       </c>
       <c r="L84" t="n">
-        <v>102.58</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>49.59</v>
+        <v>48.08</v>
       </c>
       <c r="K85" t="n">
-        <v>139.63</v>
+        <v>135.37</v>
       </c>
       <c r="L85" t="n">
-        <v>148.18</v>
+        <v>143.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>93.44</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>144.9</v>
+        <v>144.67</v>
       </c>
       <c r="L86" t="n">
-        <v>172.42</v>
+        <v>172.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-100.11</v>
+        <v>-101.17</v>
       </c>
       <c r="K87" t="n">
-        <v>143.26</v>
+        <v>144.78</v>
       </c>
       <c r="L87" t="n">
-        <v>174.78</v>
+        <v>176.63</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>64.20999999999999</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-112.45</v>
+        <v>-120.57</v>
       </c>
       <c r="L88" t="n">
-        <v>129.49</v>
+        <v>138.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="F14" t="n">
-        <v>4.85</v>
+        <v>4.39</v>
       </c>
       <c r="G14" t="n">
-        <v>122.8</v>
+        <v>126.6</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.57</v>
+        <v>56.78</v>
       </c>
       <c r="K14" t="n">
-        <v>-34.27</v>
+        <v>-36.3</v>
       </c>
       <c r="L14" t="n">
-        <v>35.86</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:31:49</t>
+          <t>07:32:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.59</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>125.5</v>
+        <v>128</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>29.11</v>
+        <v>67.36</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.91</v>
+        <v>-39.87</v>
       </c>
       <c r="L15" t="n">
-        <v>45.45</v>
+        <v>78.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:34:15</t>
+          <t>07:33:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="F16" t="n">
-        <v>5.31</v>
+        <v>5.8</v>
       </c>
       <c r="G16" t="n">
-        <v>145.7</v>
+        <v>149.6</v>
       </c>
       <c r="H16" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>42.22</v>
+        <v>25.23</v>
       </c>
       <c r="K16" t="n">
-        <v>12.43</v>
+        <v>-41.68</v>
       </c>
       <c r="L16" t="n">
-        <v>44.01</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:38:21</t>
+          <t>07:37:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="F17" t="n">
-        <v>5.76</v>
+        <v>4.53</v>
       </c>
       <c r="G17" t="n">
-        <v>129.9</v>
+        <v>124</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-10</v>
+        <v>2.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-81.97</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>82.58</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:39:45</t>
+          <t>07:39:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="F18" t="n">
-        <v>6.08</v>
+        <v>3.86</v>
       </c>
       <c r="G18" t="n">
-        <v>132.6</v>
+        <v>141.5</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.99</v>
+        <v>75.08</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.17</v>
+        <v>26.32</v>
       </c>
       <c r="L18" t="n">
-        <v>53.34</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:41:33</t>
+          <t>07:42:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="F19" t="n">
-        <v>5.62</v>
+        <v>5.47</v>
       </c>
       <c r="G19" t="n">
-        <v>136</v>
+        <v>138.4</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>28.95</v>
+        <v>17.74</v>
       </c>
       <c r="K19" t="n">
-        <v>-36.23</v>
+        <v>-125.73</v>
       </c>
       <c r="L19" t="n">
-        <v>46.38</v>
+        <v>126.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:46:21</t>
+          <t>07:46:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="F20" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>135.4</v>
+        <v>132.2</v>
       </c>
       <c r="H20" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>61.38</v>
+        <v>-63.31</v>
       </c>
       <c r="K20" t="n">
-        <v>-46.33</v>
+        <v>-116.42</v>
       </c>
       <c r="L20" t="n">
-        <v>76.90000000000001</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:48:45</t>
+          <t>07:48:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="F21" t="n">
-        <v>4.91</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>119.5</v>
+        <v>135.4</v>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>98.3</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-31.46</v>
+        <v>19.53</v>
       </c>
       <c r="K21" t="n">
-        <v>77.11</v>
+        <v>5.58</v>
       </c>
       <c r="L21" t="n">
-        <v>83.28</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:50:22</t>
+          <t>07:50:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="F22" t="n">
-        <v>5.74</v>
+        <v>6.22</v>
       </c>
       <c r="G22" t="n">
-        <v>133</v>
+        <v>145.9</v>
       </c>
       <c r="H22" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-82.06</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>50.47</v>
+        <v>-83.39</v>
       </c>
       <c r="L22" t="n">
-        <v>96.34</v>
+        <v>120.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:56:40</t>
+          <t>07:54:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="F23" t="n">
-        <v>5.63</v>
+        <v>3.27</v>
       </c>
       <c r="G23" t="n">
-        <v>128.2</v>
+        <v>104.4</v>
       </c>
       <c r="H23" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-75.91</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-123.76</v>
+        <v>-137.48</v>
       </c>
       <c r="L23" t="n">
-        <v>145.18</v>
+        <v>137.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:58:54</t>
+          <t>07:56:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="F24" t="n">
-        <v>5.32</v>
+        <v>6.55</v>
       </c>
       <c r="G24" t="n">
-        <v>131.8</v>
+        <v>123.5</v>
       </c>
       <c r="H24" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>96.87</v>
+        <v>50.35</v>
       </c>
       <c r="K24" t="n">
-        <v>90.53</v>
+        <v>-193.65</v>
       </c>
       <c r="L24" t="n">
-        <v>132.59</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:59:50</t>
+          <t>07:57:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="F25" t="n">
-        <v>6.26</v>
+        <v>6.55</v>
       </c>
       <c r="G25" t="n">
-        <v>119.4</v>
+        <v>117.4</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>41.93</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-136.55</v>
+        <v>129.72</v>
       </c>
       <c r="L25" t="n">
-        <v>142.84</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:05:16</t>
+          <t>08:01:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="F26" t="n">
-        <v>5.93</v>
+        <v>4.68</v>
       </c>
       <c r="G26" t="n">
-        <v>131.3</v>
+        <v>131.9</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>113.46</v>
+        <v>81.67</v>
       </c>
       <c r="K26" t="n">
-        <v>-83.81</v>
+        <v>335.18</v>
       </c>
       <c r="L26" t="n">
-        <v>141.06</v>
+        <v>344.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:06:11</t>
+          <t>08:03:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="F27" t="n">
-        <v>6.37</v>
+        <v>5.9</v>
       </c>
       <c r="G27" t="n">
-        <v>155.1</v>
+        <v>130.1</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-29.38</v>
+        <v>-277.79</v>
       </c>
       <c r="K27" t="n">
-        <v>-135.04</v>
+        <v>-229.05</v>
       </c>
       <c r="L27" t="n">
-        <v>138.2</v>
+        <v>360.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:08:15</t>
+          <t>08:04:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="F28" t="n">
-        <v>5.09</v>
+        <v>4.58</v>
       </c>
       <c r="G28" t="n">
-        <v>113.9</v>
+        <v>124.2</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>24.94</v>
+        <v>-197.72</v>
       </c>
       <c r="K28" t="n">
-        <v>-180.83</v>
+        <v>-164.3</v>
       </c>
       <c r="L28" t="n">
-        <v>182.54</v>
+        <v>257.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:20:33</t>
+          <t>08:16:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="F29" t="n">
-        <v>5.53</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>126.3</v>
+        <v>139.2</v>
       </c>
       <c r="H29" t="n">
-        <v>94.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>24.13</v>
+        <v>-47.91</v>
       </c>
       <c r="K29" t="n">
-        <v>31.98</v>
+        <v>26.05</v>
       </c>
       <c r="L29" t="n">
-        <v>40.07</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:22:16</t>
+          <t>08:18:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="F30" t="n">
-        <v>5.86</v>
+        <v>4.98</v>
       </c>
       <c r="G30" t="n">
-        <v>126.7</v>
+        <v>143</v>
       </c>
       <c r="H30" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.27</v>
+        <v>-65.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.52</v>
+        <v>-27.32</v>
       </c>
       <c r="L30" t="n">
-        <v>16.52</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:23:41</t>
+          <t>08:20:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="F31" t="n">
-        <v>5.34</v>
+        <v>6.55</v>
       </c>
       <c r="G31" t="n">
-        <v>126.9</v>
+        <v>120.8</v>
       </c>
       <c r="H31" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>36.53</v>
+        <v>-1.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.74</v>
+        <v>55.15</v>
       </c>
       <c r="L31" t="n">
-        <v>54.72</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:29:10</t>
+          <t>08:25:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="F32" t="n">
-        <v>6.02</v>
+        <v>3.03</v>
       </c>
       <c r="G32" t="n">
-        <v>132.2</v>
+        <v>140.2</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>28.74</v>
+        <v>-79.33</v>
       </c>
       <c r="K32" t="n">
-        <v>-71.43000000000001</v>
+        <v>38.28</v>
       </c>
       <c r="L32" t="n">
-        <v>76.98999999999999</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:31:47</t>
+          <t>08:27:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1426,31 +1426,31 @@
         <v>1.78</v>
       </c>
       <c r="F33" t="n">
-        <v>5.47</v>
+        <v>5.2</v>
       </c>
       <c r="G33" t="n">
-        <v>139.1</v>
+        <v>122.2</v>
       </c>
       <c r="H33" t="n">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-42.98</v>
+        <v>15.46</v>
       </c>
       <c r="L33" t="n">
-        <v>42.99</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:33:54</t>
+          <t>08:28:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="F34" t="n">
-        <v>5.76</v>
+        <v>4.28</v>
       </c>
       <c r="G34" t="n">
-        <v>127.5</v>
+        <v>124.5</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.43</v>
+        <v>-29.17</v>
       </c>
       <c r="K34" t="n">
-        <v>-56.4</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>63.62</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:39:49</t>
+          <t>08:31:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="F35" t="n">
-        <v>6.11</v>
+        <v>5.92</v>
       </c>
       <c r="G35" t="n">
-        <v>141.9</v>
+        <v>133.4</v>
       </c>
       <c r="H35" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.49</v>
+        <v>-125.01</v>
       </c>
       <c r="K35" t="n">
-        <v>31.55</v>
+        <v>102.96</v>
       </c>
       <c r="L35" t="n">
-        <v>38.17</v>
+        <v>161.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:40:30</t>
+          <t>08:34:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="F36" t="n">
-        <v>6.3</v>
+        <v>3.78</v>
       </c>
       <c r="G36" t="n">
-        <v>118.1</v>
+        <v>123.5</v>
       </c>
       <c r="H36" t="n">
-        <v>93.7</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>44.56</v>
+        <v>16.43</v>
       </c>
       <c r="K36" t="n">
-        <v>-48.07</v>
+        <v>159.85</v>
       </c>
       <c r="L36" t="n">
-        <v>65.54000000000001</v>
+        <v>160.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:41:23</t>
+          <t>08:35:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F37" t="n">
-        <v>5.75</v>
+        <v>3.03</v>
       </c>
       <c r="G37" t="n">
-        <v>154.7</v>
+        <v>134.8</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-99.34999999999999</v>
+        <v>126.7</v>
       </c>
       <c r="K37" t="n">
-        <v>65.64</v>
+        <v>12.13</v>
       </c>
       <c r="L37" t="n">
-        <v>119.08</v>
+        <v>127.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:47:33</t>
+          <t>08:39:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="F38" t="n">
-        <v>5.8</v>
+        <v>6.55</v>
       </c>
       <c r="G38" t="n">
-        <v>146.3</v>
+        <v>120.4</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-64.14</v>
+        <v>-143.59</v>
       </c>
       <c r="K38" t="n">
-        <v>84.31</v>
+        <v>53.64</v>
       </c>
       <c r="L38" t="n">
-        <v>105.94</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:48:21</t>
+          <t>08:39:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="F39" t="n">
-        <v>5.38</v>
+        <v>4.28</v>
       </c>
       <c r="G39" t="n">
-        <v>136.1</v>
+        <v>142.7</v>
       </c>
       <c r="H39" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-44.81</v>
+        <v>18.2</v>
       </c>
       <c r="K39" t="n">
-        <v>133.15</v>
+        <v>155.47</v>
       </c>
       <c r="L39" t="n">
-        <v>140.49</v>
+        <v>156.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:49:46</t>
+          <t>08:42:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="F40" t="n">
-        <v>6.3</v>
+        <v>3.91</v>
       </c>
       <c r="G40" t="n">
-        <v>133</v>
+        <v>136.9</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>114.08</v>
+        <v>-120.35</v>
       </c>
       <c r="K40" t="n">
-        <v>-74.78</v>
+        <v>-105.59</v>
       </c>
       <c r="L40" t="n">
-        <v>136.41</v>
+        <v>160.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:54:24</t>
+          <t>08:46:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="F41" t="n">
-        <v>5.94</v>
+        <v>3.63</v>
       </c>
       <c r="G41" t="n">
-        <v>125.7</v>
+        <v>134</v>
       </c>
       <c r="H41" t="n">
-        <v>94.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-192.59</v>
+        <v>124.02</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.54</v>
+        <v>-177.08</v>
       </c>
       <c r="L41" t="n">
-        <v>193.48</v>
+        <v>216.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:56:26</t>
+          <t>08:48:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="F42" t="n">
-        <v>5.39</v>
+        <v>4.59</v>
       </c>
       <c r="G42" t="n">
-        <v>136.3</v>
+        <v>120.6</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>147.95</v>
+        <v>78.98</v>
       </c>
       <c r="K42" t="n">
-        <v>-91.13</v>
+        <v>-284.7</v>
       </c>
       <c r="L42" t="n">
-        <v>173.76</v>
+        <v>295.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:58:09</t>
+          <t>08:50:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="F43" t="n">
-        <v>5.27</v>
+        <v>6.55</v>
       </c>
       <c r="G43" t="n">
-        <v>116.8</v>
+        <v>138.3</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>96.18000000000001</v>
+        <v>-160.58</v>
       </c>
       <c r="K43" t="n">
-        <v>-215.7</v>
+        <v>90.47</v>
       </c>
       <c r="L43" t="n">
-        <v>236.17</v>
+        <v>184.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:07:53</t>
+          <t>08:58:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="F44" t="n">
-        <v>5.84</v>
+        <v>6.55</v>
       </c>
       <c r="G44" t="n">
-        <v>129.1</v>
+        <v>132.3</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.58</v>
+        <v>-20.63</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.14</v>
+        <v>-69.55</v>
       </c>
       <c r="L44" t="n">
-        <v>60.2</v>
+        <v>72.54000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:08:55</t>
+          <t>08:59:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="F45" t="n">
-        <v>5.35</v>
+        <v>4.29</v>
       </c>
       <c r="G45" t="n">
-        <v>130.2</v>
+        <v>134.6</v>
       </c>
       <c r="H45" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.59</v>
+        <v>-37.19</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.84</v>
+        <v>-28.86</v>
       </c>
       <c r="L45" t="n">
-        <v>38.8</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:10:42</t>
+          <t>09:01:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="F46" t="n">
-        <v>5.45</v>
+        <v>3.94</v>
       </c>
       <c r="G46" t="n">
-        <v>128.6</v>
+        <v>137.3</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.49</v>
+        <v>5.27</v>
       </c>
       <c r="K46" t="n">
-        <v>32.82</v>
+        <v>52.78</v>
       </c>
       <c r="L46" t="n">
-        <v>35.48</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:14:20</t>
+          <t>09:05:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="F47" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="G47" t="n">
-        <v>133.3</v>
+        <v>121.3</v>
       </c>
       <c r="H47" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.47</v>
+        <v>98.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.8</v>
+        <v>0.37</v>
       </c>
       <c r="L47" t="n">
-        <v>41.21</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:15:40</t>
+          <t>09:06:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="F48" t="n">
-        <v>6.36</v>
+        <v>5.97</v>
       </c>
       <c r="G48" t="n">
-        <v>127.8</v>
+        <v>130.5</v>
       </c>
       <c r="H48" t="n">
-        <v>94.3</v>
+        <v>95.2</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>50.01</v>
+        <v>59.17</v>
       </c>
       <c r="K48" t="n">
-        <v>95.98</v>
+        <v>103.18</v>
       </c>
       <c r="L48" t="n">
-        <v>108.22</v>
+        <v>118.94</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:17:02</t>
+          <t>09:08:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="F49" t="n">
-        <v>6.61</v>
+        <v>4.74</v>
       </c>
       <c r="G49" t="n">
-        <v>142.5</v>
+        <v>123.4</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>33.03</v>
+        <v>-92.65000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.03</v>
+        <v>-38.6</v>
       </c>
       <c r="L49" t="n">
-        <v>58.29</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:20:25</t>
+          <t>09:11:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="F50" t="n">
-        <v>4.95</v>
+        <v>6.12</v>
       </c>
       <c r="G50" t="n">
-        <v>137.7</v>
+        <v>145.2</v>
       </c>
       <c r="H50" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>40.75</v>
+        <v>118.45</v>
       </c>
       <c r="K50" t="n">
-        <v>47.81</v>
+        <v>116.9</v>
       </c>
       <c r="L50" t="n">
-        <v>62.82</v>
+        <v>166.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:22:34</t>
+          <t>09:12:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="F51" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="G51" t="n">
-        <v>145.5</v>
+        <v>143.2</v>
       </c>
       <c r="H51" t="n">
-        <v>97.3</v>
+        <v>97.8</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>10.51</v>
+        <v>-49.15</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.09</v>
+        <v>-104.41</v>
       </c>
       <c r="L51" t="n">
-        <v>16.79</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:23:01</t>
+          <t>09:14:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="F52" t="n">
-        <v>5.48</v>
+        <v>6.55</v>
       </c>
       <c r="G52" t="n">
-        <v>136.1</v>
+        <v>139.8</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.47</v>
+        <v>25.41</v>
       </c>
       <c r="K52" t="n">
-        <v>-19.73</v>
+        <v>110.01</v>
       </c>
       <c r="L52" t="n">
-        <v>75.11</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:27:40</t>
+          <t>09:20:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="F53" t="n">
-        <v>6.11</v>
+        <v>4.68</v>
       </c>
       <c r="G53" t="n">
-        <v>133.7</v>
+        <v>143.5</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-110.13</v>
+        <v>172.55</v>
       </c>
       <c r="K53" t="n">
-        <v>-93.26000000000001</v>
+        <v>-83.34999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>144.31</v>
+        <v>191.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:29:00</t>
+          <t>09:21:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="F54" t="n">
-        <v>6.38</v>
+        <v>4.39</v>
       </c>
       <c r="G54" t="n">
-        <v>133.1</v>
+        <v>110.4</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-77.62</v>
+        <v>150.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-57.01</v>
+        <v>-43.02</v>
       </c>
       <c r="L54" t="n">
-        <v>96.3</v>
+        <v>156.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:31:38</t>
+          <t>09:23:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="F55" t="n">
-        <v>5.58</v>
+        <v>6.55</v>
       </c>
       <c r="G55" t="n">
-        <v>141.8</v>
+        <v>135.8</v>
       </c>
       <c r="H55" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>148.74</v>
+        <v>129.58</v>
       </c>
       <c r="K55" t="n">
-        <v>1.71</v>
+        <v>124.21</v>
       </c>
       <c r="L55" t="n">
-        <v>148.75</v>
+        <v>179.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:36:14</t>
+          <t>09:29:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="F56" t="n">
-        <v>6.06</v>
+        <v>6.55</v>
       </c>
       <c r="G56" t="n">
-        <v>132.2</v>
+        <v>142.1</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>10.5</v>
+        <v>284.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-135.49</v>
+        <v>-153.98</v>
       </c>
       <c r="L56" t="n">
-        <v>135.9</v>
+        <v>323.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:38:08</t>
+          <t>09:31:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="F57" t="n">
-        <v>5.36</v>
+        <v>3.75</v>
       </c>
       <c r="G57" t="n">
-        <v>147.2</v>
+        <v>118.3</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>114.49</v>
+        <v>228.14</v>
       </c>
       <c r="K57" t="n">
-        <v>-153.25</v>
+        <v>-25.02</v>
       </c>
       <c r="L57" t="n">
-        <v>191.3</v>
+        <v>229.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:39:54</t>
+          <t>09:33:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="F58" t="n">
-        <v>6.18</v>
+        <v>4.28</v>
       </c>
       <c r="G58" t="n">
-        <v>135.8</v>
+        <v>130.4</v>
       </c>
       <c r="H58" t="n">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-148.81</v>
+        <v>104.02</v>
       </c>
       <c r="K58" t="n">
-        <v>-58.35</v>
+        <v>212.86</v>
       </c>
       <c r="L58" t="n">
-        <v>159.84</v>
+        <v>236.91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:51:30</t>
+          <t>09:43:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="F59" t="n">
-        <v>6.33</v>
+        <v>6.55</v>
       </c>
       <c r="G59" t="n">
-        <v>136.3</v>
+        <v>129.2</v>
       </c>
       <c r="H59" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>35.15</v>
+        <v>20.53</v>
       </c>
       <c r="K59" t="n">
-        <v>40.73</v>
+        <v>-58.27</v>
       </c>
       <c r="L59" t="n">
-        <v>53.8</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:53:40</t>
+          <t>09:44:06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="F60" t="n">
-        <v>5.84</v>
+        <v>6.55</v>
       </c>
       <c r="G60" t="n">
-        <v>120.7</v>
+        <v>138</v>
       </c>
       <c r="H60" t="n">
-        <v>98.3</v>
+        <v>93.7</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>16.16</v>
+        <v>-24.66</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.85</v>
+        <v>57.85</v>
       </c>
       <c r="L60" t="n">
-        <v>53.36</v>
+        <v>62.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:55:37</t>
+          <t>09:46:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>6.15</v>
+        <v>5.87</v>
       </c>
       <c r="G61" t="n">
-        <v>128.7</v>
+        <v>139.3</v>
       </c>
       <c r="H61" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>12.87</v>
+        <v>52.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.79</v>
+        <v>-40.2</v>
       </c>
       <c r="L61" t="n">
-        <v>25.31</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:59:58</t>
+          <t>09:50:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="F62" t="n">
-        <v>6.18</v>
+        <v>6.55</v>
       </c>
       <c r="G62" t="n">
-        <v>128.9</v>
+        <v>139.7</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-55.73</v>
+        <v>-32.9</v>
       </c>
       <c r="K62" t="n">
-        <v>-11.17</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>56.84</v>
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:02:31</t>
+          <t>09:51:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="F63" t="n">
-        <v>6.14</v>
+        <v>5.68</v>
       </c>
       <c r="G63" t="n">
-        <v>129.1</v>
+        <v>134</v>
       </c>
       <c r="H63" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>94.16</v>
+        <v>-97.83</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.93</v>
+        <v>-24.27</v>
       </c>
       <c r="L63" t="n">
-        <v>94.48999999999999</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:03:51</t>
+          <t>09:53:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="F64" t="n">
-        <v>4.92</v>
+        <v>6.55</v>
       </c>
       <c r="G64" t="n">
-        <v>142.1</v>
+        <v>141.1</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>23.78</v>
+        <v>-99.16</v>
       </c>
       <c r="K64" t="n">
-        <v>61.11</v>
+        <v>65.84</v>
       </c>
       <c r="L64" t="n">
-        <v>65.56999999999999</v>
+        <v>119.03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:07:35</t>
+          <t>09:58:05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="F65" t="n">
-        <v>6.28</v>
+        <v>6.37</v>
       </c>
       <c r="G65" t="n">
-        <v>115.5</v>
+        <v>117.1</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>57.3</v>
+        <v>74.2</v>
       </c>
       <c r="K65" t="n">
-        <v>24.8</v>
+        <v>-119.48</v>
       </c>
       <c r="L65" t="n">
-        <v>62.43</v>
+        <v>140.64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:10:09</t>
+          <t>09:59:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="F66" t="n">
-        <v>6.03</v>
+        <v>4.19</v>
       </c>
       <c r="G66" t="n">
-        <v>124.6</v>
+        <v>133.3</v>
       </c>
       <c r="H66" t="n">
-        <v>92.2</v>
+        <v>97.8</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-71.84999999999999</v>
+        <v>-101.07</v>
       </c>
       <c r="K66" t="n">
-        <v>33.33</v>
+        <v>6.3</v>
       </c>
       <c r="L66" t="n">
-        <v>79.2</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:11:14</t>
+          <t>10:00:55</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="F67" t="n">
-        <v>5.76</v>
+        <v>6.55</v>
       </c>
       <c r="G67" t="n">
-        <v>124.2</v>
+        <v>138.4</v>
       </c>
       <c r="H67" t="n">
         <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.12</v>
+        <v>98.53</v>
       </c>
       <c r="K67" t="n">
-        <v>12.99</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>86.09999999999999</v>
+        <v>119.72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:14:45</t>
+          <t>10:06:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="F68" t="n">
-        <v>6.07</v>
+        <v>6.55</v>
       </c>
       <c r="G68" t="n">
-        <v>131.2</v>
+        <v>119.3</v>
       </c>
       <c r="H68" t="n">
         <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>98.18000000000001</v>
+        <v>-2.09</v>
       </c>
       <c r="K68" t="n">
-        <v>36.2</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>104.64</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:16:00</t>
+          <t>10:08:25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="F69" t="n">
-        <v>5.67</v>
+        <v>6.55</v>
       </c>
       <c r="G69" t="n">
-        <v>130.9</v>
+        <v>127.2</v>
       </c>
       <c r="H69" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-57.73</v>
+        <v>14.17</v>
       </c>
       <c r="K69" t="n">
-        <v>151.85</v>
+        <v>-29.01</v>
       </c>
       <c r="L69" t="n">
-        <v>162.46</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:18:01</t>
+          <t>10:10:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="F70" t="n">
-        <v>5.65</v>
+        <v>6.34</v>
       </c>
       <c r="G70" t="n">
-        <v>124.6</v>
+        <v>139.1</v>
       </c>
       <c r="H70" t="n">
-        <v>97.3</v>
+        <v>99.7</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.95</v>
+        <v>75.38</v>
       </c>
       <c r="K70" t="n">
-        <v>134.19</v>
+        <v>-159.64</v>
       </c>
       <c r="L70" t="n">
-        <v>134.2</v>
+        <v>176.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:24:13</t>
+          <t>10:15:20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="F71" t="n">
-        <v>5.19</v>
+        <v>5.53</v>
       </c>
       <c r="G71" t="n">
-        <v>136.9</v>
+        <v>134.3</v>
       </c>
       <c r="H71" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>66.08</v>
+        <v>-166.93</v>
       </c>
       <c r="K71" t="n">
-        <v>-105.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>124.33</v>
+        <v>167.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:26:42</t>
+          <t>10:17:43</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="F72" t="n">
-        <v>5.79</v>
+        <v>4.87</v>
       </c>
       <c r="G72" t="n">
-        <v>128.4</v>
+        <v>136.9</v>
       </c>
       <c r="H72" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-105.58</v>
+        <v>-52.1</v>
       </c>
       <c r="K72" t="n">
-        <v>95.27</v>
+        <v>-209.73</v>
       </c>
       <c r="L72" t="n">
-        <v>142.21</v>
+        <v>216.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:28:36</t>
+          <t>10:19:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="F73" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="G73" t="n">
-        <v>131.5</v>
+        <v>138.3</v>
       </c>
       <c r="H73" t="n">
-        <v>95.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-159.15</v>
+        <v>47.94</v>
       </c>
       <c r="K73" t="n">
-        <v>80.93000000000001</v>
+        <v>-204</v>
       </c>
       <c r="L73" t="n">
-        <v>178.54</v>
+        <v>209.56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:40:43</t>
+          <t>10:31:35</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F74" t="n">
-        <v>5.25</v>
+        <v>6.55</v>
       </c>
       <c r="G74" t="n">
-        <v>148.8</v>
+        <v>138.5</v>
       </c>
       <c r="H74" t="n">
-        <v>97.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-28.25</v>
+        <v>62.29</v>
       </c>
       <c r="K74" t="n">
-        <v>30.27</v>
+        <v>33.88</v>
       </c>
       <c r="L74" t="n">
-        <v>41.4</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:42:38</t>
+          <t>10:33:11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="F75" t="n">
-        <v>5.92</v>
+        <v>6.55</v>
       </c>
       <c r="G75" t="n">
-        <v>155.9</v>
+        <v>137.6</v>
       </c>
       <c r="H75" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>12.26</v>
+        <v>26.93</v>
       </c>
       <c r="K75" t="n">
-        <v>35.59</v>
+        <v>49.69</v>
       </c>
       <c r="L75" t="n">
-        <v>37.64</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:44:34</t>
+          <t>10:34:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="F76" t="n">
-        <v>5.36</v>
+        <v>6.55</v>
       </c>
       <c r="G76" t="n">
-        <v>139.5</v>
+        <v>139</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>60.31</v>
+        <v>11.32</v>
       </c>
       <c r="K76" t="n">
-        <v>24.01</v>
+        <v>-52.09</v>
       </c>
       <c r="L76" t="n">
-        <v>64.91</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:48:05</t>
+          <t>10:39:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="F77" t="n">
-        <v>6.31</v>
+        <v>6.55</v>
       </c>
       <c r="G77" t="n">
-        <v>115.1</v>
+        <v>139.7</v>
       </c>
       <c r="H77" t="n">
-        <v>99.2</v>
+        <v>93.3</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-69.41</v>
+        <v>-21.43</v>
       </c>
       <c r="K77" t="n">
-        <v>36.91</v>
+        <v>58.82</v>
       </c>
       <c r="L77" t="n">
-        <v>78.61</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:49:19</t>
+          <t>10:40:58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="F78" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>118.7</v>
+        <v>121.7</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>5.39</v>
+        <v>73.33</v>
       </c>
       <c r="K78" t="n">
-        <v>-71.81999999999999</v>
+        <v>25.58</v>
       </c>
       <c r="L78" t="n">
-        <v>72.02</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:50:25</t>
+          <t>10:43:23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="F79" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="G79" t="n">
-        <v>154.1</v>
+        <v>148.7</v>
       </c>
       <c r="H79" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>10.92</v>
+        <v>55.2</v>
       </c>
       <c r="K79" t="n">
-        <v>84.97</v>
+        <v>40.48</v>
       </c>
       <c r="L79" t="n">
-        <v>85.67</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:55:01</t>
+          <t>10:48:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="F80" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="G80" t="n">
-        <v>124.1</v>
+        <v>134.5</v>
       </c>
       <c r="H80" t="n">
         <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>91.42</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>18.44</v>
+        <v>-132.04</v>
       </c>
       <c r="L80" t="n">
-        <v>93.26000000000001</v>
+        <v>161.59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:57:26</t>
+          <t>10:50:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="F81" t="n">
-        <v>6.18</v>
+        <v>6.55</v>
       </c>
       <c r="G81" t="n">
-        <v>112.6</v>
+        <v>131.7</v>
       </c>
       <c r="H81" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>82.38</v>
+        <v>-10.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-10.5</v>
+        <v>87.88</v>
       </c>
       <c r="L81" t="n">
-        <v>83.04000000000001</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:59:17</t>
+          <t>10:52:18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="F82" t="n">
-        <v>5.84</v>
+        <v>6.55</v>
       </c>
       <c r="G82" t="n">
-        <v>134.7</v>
+        <v>132.1</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-105.14</v>
+        <v>27.21</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.24</v>
+        <v>-89.39</v>
       </c>
       <c r="L82" t="n">
-        <v>105.39</v>
+        <v>93.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:04:11</t>
+          <t>10:57:22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="F83" t="n">
-        <v>6.68</v>
+        <v>6.5</v>
       </c>
       <c r="G83" t="n">
-        <v>132</v>
+        <v>130.3</v>
       </c>
       <c r="H83" t="n">
         <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-45.35</v>
+        <v>34.17</v>
       </c>
       <c r="K83" t="n">
-        <v>103.84</v>
+        <v>150.73</v>
       </c>
       <c r="L83" t="n">
-        <v>113.31</v>
+        <v>154.55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:06:09</t>
+          <t>10:58:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="F84" t="n">
-        <v>5.84</v>
+        <v>6.55</v>
       </c>
       <c r="G84" t="n">
-        <v>118.2</v>
+        <v>134.9</v>
       </c>
       <c r="H84" t="n">
-        <v>95.3</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>52.47</v>
+        <v>69.06</v>
       </c>
       <c r="K84" t="n">
-        <v>93.17</v>
+        <v>-167.53</v>
       </c>
       <c r="L84" t="n">
-        <v>106.93</v>
+        <v>181.21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:08:32</t>
+          <t>11:00:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="F85" t="n">
-        <v>5.18</v>
+        <v>6.55</v>
       </c>
       <c r="G85" t="n">
-        <v>134</v>
+        <v>137.1</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>48.08</v>
+        <v>-184.74</v>
       </c>
       <c r="K85" t="n">
-        <v>135.37</v>
+        <v>19.69</v>
       </c>
       <c r="L85" t="n">
-        <v>143.66</v>
+        <v>185.78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:12:27</t>
+          <t>11:05:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>5.94</v>
+        <v>6.55</v>
       </c>
       <c r="G86" t="n">
-        <v>136.7</v>
+        <v>137.7</v>
       </c>
       <c r="H86" t="n">
-        <v>96.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>93.29000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="K86" t="n">
-        <v>144.67</v>
+        <v>-256.4</v>
       </c>
       <c r="L86" t="n">
-        <v>172.14</v>
+        <v>256.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:14:03</t>
+          <t>11:07:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="F87" t="n">
-        <v>6.03</v>
+        <v>6.55</v>
       </c>
       <c r="G87" t="n">
-        <v>144</v>
+        <v>148.9</v>
       </c>
       <c r="H87" t="n">
         <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-101.17</v>
+        <v>47.06</v>
       </c>
       <c r="K87" t="n">
-        <v>144.78</v>
+        <v>-228.18</v>
       </c>
       <c r="L87" t="n">
-        <v>176.63</v>
+        <v>232.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:15:53</t>
+          <t>11:09:17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="F88" t="n">
-        <v>5.41</v>
+        <v>6.55</v>
       </c>
       <c r="G88" t="n">
-        <v>124.1</v>
+        <v>135.6</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>68.84999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="K88" t="n">
-        <v>-120.57</v>
+        <v>-228.72</v>
       </c>
       <c r="L88" t="n">
-        <v>138.84</v>
+        <v>228.91</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>56.78</v>
+        <v>64.61</v>
       </c>
       <c r="K14" t="n">
-        <v>-36.3</v>
+        <v>-41.31</v>
       </c>
       <c r="L14" t="n">
-        <v>67.39</v>
+        <v>76.68000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>67.36</v>
+        <v>76.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.87</v>
+        <v>-45.37</v>
       </c>
       <c r="L15" t="n">
-        <v>78.28</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>25.23</v>
+        <v>28.71</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.68</v>
+        <v>-47.43</v>
       </c>
       <c r="L16" t="n">
-        <v>48.72</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>76.76000000000001</v>
+        <v>87.34</v>
       </c>
       <c r="L17" t="n">
-        <v>76.81999999999999</v>
+        <v>87.41</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>75.08</v>
+        <v>85.44</v>
       </c>
       <c r="K18" t="n">
-        <v>26.32</v>
+        <v>29.95</v>
       </c>
       <c r="L18" t="n">
-        <v>79.56</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>17.74</v>
+        <v>20.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-125.73</v>
+        <v>-143.07</v>
       </c>
       <c r="L19" t="n">
-        <v>126.97</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-63.31</v>
+        <v>-70.09</v>
       </c>
       <c r="K20" t="n">
-        <v>-116.42</v>
+        <v>-128.89</v>
       </c>
       <c r="L20" t="n">
-        <v>132.52</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>19.53</v>
+        <v>21.93</v>
       </c>
       <c r="K21" t="n">
-        <v>5.58</v>
+        <v>6.27</v>
       </c>
       <c r="L21" t="n">
-        <v>20.31</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-87.65000000000001</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-83.39</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>120.98</v>
+        <v>137.67</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>9.970000000000001</v>
+        <v>11.35</v>
       </c>
       <c r="K23" t="n">
-        <v>-137.48</v>
+        <v>-156.44</v>
       </c>
       <c r="L23" t="n">
-        <v>137.84</v>
+        <v>156.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>50.35</v>
+        <v>56.54</v>
       </c>
       <c r="K24" t="n">
-        <v>-193.65</v>
+        <v>-217.44</v>
       </c>
       <c r="L24" t="n">
-        <v>200.09</v>
+        <v>224.67</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>8.619999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>129.72</v>
+        <v>143.61</v>
       </c>
       <c r="L25" t="n">
-        <v>130</v>
+        <v>143.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>81.67</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>335.18</v>
+        <v>381.42</v>
       </c>
       <c r="L26" t="n">
-        <v>344.99</v>
+        <v>392.57</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-277.79</v>
+        <v>-316.11</v>
       </c>
       <c r="K27" t="n">
-        <v>-229.05</v>
+        <v>-260.64</v>
       </c>
       <c r="L27" t="n">
-        <v>360.05</v>
+        <v>409.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-197.72</v>
+        <v>-224.99</v>
       </c>
       <c r="K28" t="n">
-        <v>-164.3</v>
+        <v>-186.96</v>
       </c>
       <c r="L28" t="n">
-        <v>257.08</v>
+        <v>292.54</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-47.91</v>
+        <v>-54.52</v>
       </c>
       <c r="K29" t="n">
-        <v>26.05</v>
+        <v>29.64</v>
       </c>
       <c r="L29" t="n">
-        <v>54.54</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-65.33</v>
+        <v>-74.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-27.32</v>
+        <v>-31.09</v>
       </c>
       <c r="L30" t="n">
-        <v>70.81</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.84</v>
+        <v>-2.1</v>
       </c>
       <c r="K31" t="n">
-        <v>55.15</v>
+        <v>62.76</v>
       </c>
       <c r="L31" t="n">
-        <v>55.18</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-79.33</v>
+        <v>-90.27</v>
       </c>
       <c r="K32" t="n">
-        <v>38.28</v>
+        <v>43.56</v>
       </c>
       <c r="L32" t="n">
-        <v>88.08</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-67.09999999999999</v>
+        <v>-76.34999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>15.46</v>
+        <v>17.6</v>
       </c>
       <c r="L33" t="n">
-        <v>68.86</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.17</v>
+        <v>-33.19</v>
       </c>
       <c r="K34" t="n">
-        <v>74.76000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>80.25</v>
+        <v>91.31999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-125.01</v>
+        <v>-142.26</v>
       </c>
       <c r="K35" t="n">
-        <v>102.96</v>
+        <v>117.16</v>
       </c>
       <c r="L35" t="n">
-        <v>161.95</v>
+        <v>184.29</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>16.43</v>
+        <v>18.45</v>
       </c>
       <c r="K36" t="n">
-        <v>159.85</v>
+        <v>179.48</v>
       </c>
       <c r="L36" t="n">
-        <v>160.69</v>
+        <v>180.42</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>126.7</v>
+        <v>144.18</v>
       </c>
       <c r="K37" t="n">
-        <v>12.13</v>
+        <v>13.8</v>
       </c>
       <c r="L37" t="n">
-        <v>127.28</v>
+        <v>144.83</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-143.59</v>
+        <v>-161.23</v>
       </c>
       <c r="K38" t="n">
-        <v>53.64</v>
+        <v>60.23</v>
       </c>
       <c r="L38" t="n">
-        <v>153.28</v>
+        <v>172.11</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>18.2</v>
+        <v>20.71</v>
       </c>
       <c r="K39" t="n">
-        <v>155.47</v>
+        <v>176.92</v>
       </c>
       <c r="L39" t="n">
-        <v>156.53</v>
+        <v>178.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-120.35</v>
+        <v>-136.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-105.59</v>
+        <v>-120.16</v>
       </c>
       <c r="L40" t="n">
-        <v>160.11</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>124.02</v>
+        <v>141.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-177.08</v>
+        <v>-201.5</v>
       </c>
       <c r="L41" t="n">
-        <v>216.19</v>
+        <v>246.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>78.98</v>
+        <v>89.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-284.7</v>
+        <v>-323.97</v>
       </c>
       <c r="L42" t="n">
-        <v>295.45</v>
+        <v>336.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-160.58</v>
+        <v>-182.73</v>
       </c>
       <c r="K43" t="n">
-        <v>90.47</v>
+        <v>102.94</v>
       </c>
       <c r="L43" t="n">
-        <v>184.31</v>
+        <v>209.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-20.63</v>
+        <v>-23.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-69.55</v>
+        <v>-79.14</v>
       </c>
       <c r="L44" t="n">
-        <v>72.54000000000001</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-37.19</v>
+        <v>-41.18</v>
       </c>
       <c r="K45" t="n">
-        <v>-28.86</v>
+        <v>-31.95</v>
       </c>
       <c r="L45" t="n">
-        <v>47.08</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>5.27</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>52.78</v>
+        <v>60.06</v>
       </c>
       <c r="L46" t="n">
-        <v>53.04</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>98.75</v>
+        <v>112.37</v>
       </c>
       <c r="K47" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="L47" t="n">
-        <v>98.75</v>
+        <v>112.37</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>59.17</v>
+        <v>66.44</v>
       </c>
       <c r="K48" t="n">
-        <v>103.18</v>
+        <v>115.85</v>
       </c>
       <c r="L48" t="n">
-        <v>118.94</v>
+        <v>133.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-92.65000000000001</v>
+        <v>-105.43</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.6</v>
+        <v>-43.92</v>
       </c>
       <c r="L49" t="n">
-        <v>100.37</v>
+        <v>114.21</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>118.45</v>
+        <v>134.78</v>
       </c>
       <c r="K50" t="n">
-        <v>116.9</v>
+        <v>133.03</v>
       </c>
       <c r="L50" t="n">
-        <v>166.42</v>
+        <v>189.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-49.15</v>
+        <v>-54.41</v>
       </c>
       <c r="K51" t="n">
-        <v>-104.41</v>
+        <v>-115.59</v>
       </c>
       <c r="L51" t="n">
-        <v>115.4</v>
+        <v>127.76</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>25.41</v>
+        <v>28.13</v>
       </c>
       <c r="K52" t="n">
-        <v>110.01</v>
+        <v>121.8</v>
       </c>
       <c r="L52" t="n">
-        <v>112.9</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>172.55</v>
+        <v>196.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-83.34999999999999</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>191.63</v>
+        <v>218.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>150.45</v>
+        <v>171.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-43.02</v>
+        <v>-48.96</v>
       </c>
       <c r="L54" t="n">
-        <v>156.48</v>
+        <v>178.06</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>129.58</v>
+        <v>147.45</v>
       </c>
       <c r="K55" t="n">
-        <v>124.21</v>
+        <v>141.34</v>
       </c>
       <c r="L55" t="n">
-        <v>179.5</v>
+        <v>204.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>284.51</v>
+        <v>323.75</v>
       </c>
       <c r="K56" t="n">
-        <v>-153.98</v>
+        <v>-175.22</v>
       </c>
       <c r="L56" t="n">
-        <v>323.51</v>
+        <v>368.13</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>228.14</v>
+        <v>256.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-25.02</v>
+        <v>-28.09</v>
       </c>
       <c r="L57" t="n">
-        <v>229.51</v>
+        <v>257.69</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>104.02</v>
+        <v>115.16</v>
       </c>
       <c r="K58" t="n">
-        <v>212.86</v>
+        <v>235.66</v>
       </c>
       <c r="L58" t="n">
-        <v>236.91</v>
+        <v>262.29</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>20.53</v>
+        <v>23.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-58.27</v>
+        <v>-66.31</v>
       </c>
       <c r="L59" t="n">
-        <v>61.79</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.66</v>
+        <v>-28.06</v>
       </c>
       <c r="K60" t="n">
-        <v>57.85</v>
+        <v>65.83</v>
       </c>
       <c r="L60" t="n">
-        <v>62.89</v>
+        <v>71.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>52.65</v>
+        <v>59.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.2</v>
+        <v>-45.74</v>
       </c>
       <c r="L61" t="n">
-        <v>66.23999999999999</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-32.9</v>
+        <v>-37.43</v>
       </c>
       <c r="K62" t="n">
-        <v>86.70999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="L62" t="n">
-        <v>92.73999999999999</v>
+        <v>105.53</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-97.83</v>
+        <v>-111.32</v>
       </c>
       <c r="K63" t="n">
-        <v>-24.27</v>
+        <v>-27.61</v>
       </c>
       <c r="L63" t="n">
-        <v>100.8</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-99.16</v>
+        <v>-112.84</v>
       </c>
       <c r="K64" t="n">
-        <v>65.84</v>
+        <v>74.92</v>
       </c>
       <c r="L64" t="n">
-        <v>119.03</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>74.2</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-119.48</v>
+        <v>-135.96</v>
       </c>
       <c r="L65" t="n">
-        <v>140.64</v>
+        <v>160.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-101.07</v>
+        <v>-115.02</v>
       </c>
       <c r="K66" t="n">
-        <v>6.3</v>
+        <v>7.17</v>
       </c>
       <c r="L66" t="n">
-        <v>101.27</v>
+        <v>115.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>98.53</v>
+        <v>110.63</v>
       </c>
       <c r="K67" t="n">
-        <v>68.01000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="L67" t="n">
-        <v>119.72</v>
+        <v>134.43</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.09</v>
+        <v>-2.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-72.98999999999999</v>
+        <v>-83.06</v>
       </c>
       <c r="L68" t="n">
-        <v>73.02</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>14.17</v>
+        <v>15.69</v>
       </c>
       <c r="K69" t="n">
-        <v>-29.01</v>
+        <v>-32.11</v>
       </c>
       <c r="L69" t="n">
-        <v>32.28</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>75.38</v>
+        <v>85.77</v>
       </c>
       <c r="K70" t="n">
-        <v>-159.64</v>
+        <v>-181.66</v>
       </c>
       <c r="L70" t="n">
-        <v>176.54</v>
+        <v>200.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-166.93</v>
+        <v>-189.96</v>
       </c>
       <c r="K71" t="n">
-        <v>9.359999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="L71" t="n">
-        <v>167.2</v>
+        <v>190.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-52.1</v>
+        <v>-59.29</v>
       </c>
       <c r="K72" t="n">
-        <v>-209.73</v>
+        <v>-238.66</v>
       </c>
       <c r="L72" t="n">
-        <v>216.1</v>
+        <v>245.91</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>47.94</v>
+        <v>54.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-204</v>
+        <v>-232.14</v>
       </c>
       <c r="L73" t="n">
-        <v>209.56</v>
+        <v>238.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>62.29</v>
+        <v>70.88</v>
       </c>
       <c r="K74" t="n">
-        <v>33.88</v>
+        <v>38.56</v>
       </c>
       <c r="L74" t="n">
-        <v>70.91</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>26.93</v>
+        <v>29.81</v>
       </c>
       <c r="K75" t="n">
-        <v>49.69</v>
+        <v>55.01</v>
       </c>
       <c r="L75" t="n">
-        <v>56.51</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>11.32</v>
+        <v>12.89</v>
       </c>
       <c r="K76" t="n">
-        <v>-52.09</v>
+        <v>-59.28</v>
       </c>
       <c r="L76" t="n">
-        <v>53.31</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-21.43</v>
+        <v>-23.73</v>
       </c>
       <c r="K77" t="n">
-        <v>58.82</v>
+        <v>65.12</v>
       </c>
       <c r="L77" t="n">
-        <v>62.6</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>73.33</v>
+        <v>81.19</v>
       </c>
       <c r="K78" t="n">
-        <v>25.58</v>
+        <v>28.32</v>
       </c>
       <c r="L78" t="n">
-        <v>77.67</v>
+        <v>85.98999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>55.2</v>
+        <v>62.81</v>
       </c>
       <c r="K79" t="n">
-        <v>40.48</v>
+        <v>46.06</v>
       </c>
       <c r="L79" t="n">
-        <v>68.45</v>
+        <v>77.89</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>93.15000000000001</v>
+        <v>106</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.04</v>
+        <v>-150.25</v>
       </c>
       <c r="L80" t="n">
-        <v>161.59</v>
+        <v>183.88</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.22</v>
+        <v>-11.63</v>
       </c>
       <c r="K81" t="n">
-        <v>87.88</v>
+        <v>100.01</v>
       </c>
       <c r="L81" t="n">
-        <v>88.48</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>27.21</v>
+        <v>30.96</v>
       </c>
       <c r="K82" t="n">
-        <v>-89.39</v>
+        <v>-101.72</v>
       </c>
       <c r="L82" t="n">
-        <v>93.44</v>
+        <v>106.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>34.17</v>
+        <v>38.36</v>
       </c>
       <c r="K83" t="n">
-        <v>150.73</v>
+        <v>169.24</v>
       </c>
       <c r="L83" t="n">
-        <v>154.55</v>
+        <v>173.53</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>69.06</v>
+        <v>78.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.53</v>
+        <v>-190.64</v>
       </c>
       <c r="L84" t="n">
-        <v>181.21</v>
+        <v>206.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-184.74</v>
+        <v>-210.22</v>
       </c>
       <c r="K85" t="n">
-        <v>19.69</v>
+        <v>22.4</v>
       </c>
       <c r="L85" t="n">
-        <v>185.78</v>
+        <v>211.41</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>6.47</v>
+        <v>7.36</v>
       </c>
       <c r="K86" t="n">
-        <v>-256.4</v>
+        <v>-291.76</v>
       </c>
       <c r="L86" t="n">
-        <v>256.48</v>
+        <v>291.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>47.06</v>
+        <v>52.1</v>
       </c>
       <c r="K87" t="n">
-        <v>-228.18</v>
+        <v>-252.63</v>
       </c>
       <c r="L87" t="n">
-        <v>232.98</v>
+        <v>257.94</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>9.49</v>
+        <v>10.8</v>
       </c>
       <c r="K88" t="n">
-        <v>-228.72</v>
+        <v>-260.26</v>
       </c>
       <c r="L88" t="n">
-        <v>228.91</v>
+        <v>260.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="F14" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="G14" t="n">
-        <v>126.6</v>
+        <v>132.3</v>
       </c>
       <c r="H14" t="n">
-        <v>98.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>64.61</v>
+        <v>33.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-41.31</v>
+        <v>11.77</v>
       </c>
       <c r="L14" t="n">
-        <v>76.68000000000001</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:32:06</t>
+          <t>07:31:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="G15" t="n">
-        <v>128</v>
+        <v>125.1</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>24.5</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>76.66</v>
+        <v>-43.87</v>
       </c>
       <c r="K15" t="n">
-        <v>-45.37</v>
+        <v>-3.66</v>
       </c>
       <c r="L15" t="n">
-        <v>89.08</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:33:31</t>
+          <t>07:34:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="F16" t="n">
-        <v>5.8</v>
+        <v>6.55</v>
       </c>
       <c r="G16" t="n">
-        <v>149.6</v>
+        <v>141.8</v>
       </c>
       <c r="H16" t="n">
-        <v>99.5</v>
+        <v>74.8</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>28.71</v>
+        <v>-40.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.43</v>
+        <v>-19.19</v>
       </c>
       <c r="L16" t="n">
-        <v>55.44</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:37:43</t>
+          <t>07:37:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4.53</v>
+        <v>4.19</v>
       </c>
       <c r="G17" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>46.3</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>-15.17</v>
       </c>
       <c r="K17" t="n">
-        <v>87.34</v>
+        <v>-47.42</v>
       </c>
       <c r="L17" t="n">
-        <v>87.41</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="18">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="F18" t="n">
-        <v>3.86</v>
+        <v>5.42</v>
       </c>
       <c r="G18" t="n">
-        <v>141.5</v>
+        <v>145.4</v>
       </c>
       <c r="H18" t="n">
-        <v>94.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>85.44</v>
+        <v>-6.91</v>
       </c>
       <c r="K18" t="n">
-        <v>29.95</v>
+        <v>-45.83</v>
       </c>
       <c r="L18" t="n">
-        <v>90.53</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:42:03</t>
+          <t>07:40:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F19" t="n">
-        <v>5.47</v>
+        <v>6.55</v>
       </c>
       <c r="G19" t="n">
-        <v>138.4</v>
+        <v>132.6</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>20.18</v>
+        <v>46.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-143.07</v>
+        <v>-29.82</v>
       </c>
       <c r="L19" t="n">
-        <v>144.49</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:46:17</t>
+          <t>07:45:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>6.55</v>
       </c>
       <c r="G20" t="n">
-        <v>132.2</v>
+        <v>131.6</v>
       </c>
       <c r="H20" t="n">
-        <v>96.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-70.09</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-128.89</v>
+        <v>52.41</v>
       </c>
       <c r="L20" t="n">
-        <v>146.72</v>
+        <v>94.54000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:48:14</t>
+          <t>07:46:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>6.55</v>
       </c>
       <c r="G21" t="n">
-        <v>135.4</v>
+        <v>133.2</v>
       </c>
       <c r="H21" t="n">
-        <v>98.3</v>
+        <v>43.7</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>21.93</v>
+        <v>112.39</v>
       </c>
       <c r="K21" t="n">
-        <v>6.27</v>
+        <v>23.19</v>
       </c>
       <c r="L21" t="n">
-        <v>22.81</v>
+        <v>114.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:50:29</t>
+          <t>07:47:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="F22" t="n">
-        <v>6.22</v>
+        <v>6.44</v>
       </c>
       <c r="G22" t="n">
-        <v>145.9</v>
+        <v>120.8</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>40.8</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-99.73999999999999</v>
+        <v>-49.62</v>
       </c>
       <c r="K22" t="n">
-        <v>-94.90000000000001</v>
+        <v>-42.68</v>
       </c>
       <c r="L22" t="n">
-        <v>137.67</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:54:42</t>
+          <t>07:52:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="F23" t="n">
         <v>3.27</v>
       </c>
       <c r="G23" t="n">
-        <v>104.4</v>
+        <v>137.5</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>70.5</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>11.35</v>
+        <v>104.99</v>
       </c>
       <c r="K23" t="n">
-        <v>-156.44</v>
+        <v>-41.23</v>
       </c>
       <c r="L23" t="n">
-        <v>156.85</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:56:25</t>
+          <t>07:53:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="F24" t="n">
-        <v>6.55</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>123.5</v>
+        <v>141</v>
       </c>
       <c r="H24" t="n">
-        <v>98.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>56.54</v>
+        <v>-29.41</v>
       </c>
       <c r="K24" t="n">
-        <v>-217.44</v>
+        <v>125.88</v>
       </c>
       <c r="L24" t="n">
-        <v>224.67</v>
+        <v>129.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:57:20</t>
+          <t>07:54:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="F25" t="n">
-        <v>6.55</v>
+        <v>5.87</v>
       </c>
       <c r="G25" t="n">
-        <v>117.4</v>
+        <v>119.8</v>
       </c>
       <c r="H25" t="n">
-        <v>96.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>9.550000000000001</v>
+        <v>-22.51</v>
       </c>
       <c r="K25" t="n">
-        <v>143.61</v>
+        <v>-67.03</v>
       </c>
       <c r="L25" t="n">
-        <v>143.93</v>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:01:51</t>
+          <t>07:59:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="F26" t="n">
-        <v>4.68</v>
+        <v>5.39</v>
       </c>
       <c r="G26" t="n">
-        <v>131.9</v>
+        <v>130.2</v>
       </c>
       <c r="H26" t="n">
-        <v>99.2</v>
+        <v>61.2</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>92.93000000000001</v>
+        <v>-68.11</v>
       </c>
       <c r="K26" t="n">
-        <v>381.42</v>
+        <v>-161.62</v>
       </c>
       <c r="L26" t="n">
-        <v>392.57</v>
+        <v>175.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:03:57</t>
+          <t>08:00:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="F27" t="n">
-        <v>5.9</v>
+        <v>2.81</v>
       </c>
       <c r="G27" t="n">
-        <v>130.1</v>
+        <v>156.6</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>50.8</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-316.11</v>
+        <v>33.41</v>
       </c>
       <c r="K27" t="n">
-        <v>-260.64</v>
+        <v>141.89</v>
       </c>
       <c r="L27" t="n">
-        <v>409.71</v>
+        <v>145.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:04:46</t>
+          <t>08:03:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="F28" t="n">
-        <v>4.58</v>
+        <v>4.9</v>
       </c>
       <c r="G28" t="n">
-        <v>124.2</v>
+        <v>127.8</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>56.8</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-224.99</v>
+        <v>102.71</v>
       </c>
       <c r="K28" t="n">
-        <v>-186.96</v>
+        <v>237.67</v>
       </c>
       <c r="L28" t="n">
-        <v>292.54</v>
+        <v>258.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:16:02</t>
+          <t>08:12:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="G29" t="n">
-        <v>139.2</v>
+        <v>140.3</v>
       </c>
       <c r="H29" t="n">
-        <v>99.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-54.52</v>
+        <v>31.17</v>
       </c>
       <c r="K29" t="n">
-        <v>29.64</v>
+        <v>-21.4</v>
       </c>
       <c r="L29" t="n">
-        <v>62.06</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:18:16</t>
+          <t>08:14:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="F30" t="n">
-        <v>4.98</v>
+        <v>6.21</v>
       </c>
       <c r="G30" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-74.34</v>
+        <v>-10.61</v>
       </c>
       <c r="K30" t="n">
-        <v>-31.09</v>
+        <v>36.91</v>
       </c>
       <c r="L30" t="n">
-        <v>80.58</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:20:54</t>
+          <t>08:15:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="F31" t="n">
         <v>6.55</v>
       </c>
       <c r="G31" t="n">
-        <v>120.8</v>
+        <v>131.2</v>
       </c>
       <c r="H31" t="n">
-        <v>97</v>
+        <v>74.8</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.1</v>
+        <v>1.13</v>
       </c>
       <c r="K31" t="n">
-        <v>62.76</v>
+        <v>33.17</v>
       </c>
       <c r="L31" t="n">
-        <v>62.79</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:25:31</t>
+          <t>08:20:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="F32" t="n">
-        <v>3.03</v>
+        <v>6.55</v>
       </c>
       <c r="G32" t="n">
-        <v>140.2</v>
+        <v>127.6</v>
       </c>
       <c r="H32" t="n">
-        <v>97.5</v>
+        <v>69.2</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-90.27</v>
+        <v>42.93</v>
       </c>
       <c r="K32" t="n">
-        <v>43.56</v>
+        <v>-37.78</v>
       </c>
       <c r="L32" t="n">
-        <v>100.23</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:27:49</t>
+          <t>08:21:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="F33" t="n">
-        <v>5.2</v>
+        <v>4.42</v>
       </c>
       <c r="G33" t="n">
-        <v>122.2</v>
+        <v>111.4</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.34999999999999</v>
+        <v>16.54</v>
       </c>
       <c r="K33" t="n">
-        <v>17.6</v>
+        <v>41.37</v>
       </c>
       <c r="L33" t="n">
-        <v>78.34999999999999</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:28:30</t>
+          <t>08:22:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="F34" t="n">
-        <v>4.28</v>
+        <v>6.41</v>
       </c>
       <c r="G34" t="n">
-        <v>124.5</v>
+        <v>130.5</v>
       </c>
       <c r="H34" t="n">
-        <v>98.5</v>
+        <v>73.8</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-33.19</v>
+        <v>42.34</v>
       </c>
       <c r="K34" t="n">
-        <v>85.06999999999999</v>
+        <v>-33.55</v>
       </c>
       <c r="L34" t="n">
-        <v>91.31999999999999</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:31:58</t>
+          <t>08:26:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.09</v>
+        <v>1.43</v>
       </c>
       <c r="F35" t="n">
-        <v>5.92</v>
+        <v>5.01</v>
       </c>
       <c r="G35" t="n">
-        <v>133.4</v>
+        <v>129.3</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>37.8</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-142.26</v>
+        <v>50.93</v>
       </c>
       <c r="K35" t="n">
-        <v>117.16</v>
+        <v>-39.43</v>
       </c>
       <c r="L35" t="n">
-        <v>184.29</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:34:21</t>
+          <t>08:28:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="F36" t="n">
-        <v>3.78</v>
+        <v>6.55</v>
       </c>
       <c r="G36" t="n">
-        <v>123.5</v>
+        <v>135.9</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>73.2</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>18.45</v>
+        <v>44.3</v>
       </c>
       <c r="K36" t="n">
-        <v>179.48</v>
+        <v>-57.21</v>
       </c>
       <c r="L36" t="n">
-        <v>180.42</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:35:10</t>
+          <t>08:30:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="F37" t="n">
-        <v>3.03</v>
+        <v>6.55</v>
       </c>
       <c r="G37" t="n">
-        <v>134.8</v>
+        <v>132.1</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>64.5</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>144.18</v>
+        <v>-55.99</v>
       </c>
       <c r="K37" t="n">
-        <v>13.8</v>
+        <v>-65.05</v>
       </c>
       <c r="L37" t="n">
-        <v>144.83</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:39:11</t>
+          <t>08:34:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="F38" t="n">
-        <v>6.55</v>
+        <v>3.89</v>
       </c>
       <c r="G38" t="n">
-        <v>120.4</v>
+        <v>138.3</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>52.1</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-161.23</v>
+        <v>-77.17</v>
       </c>
       <c r="K38" t="n">
-        <v>60.23</v>
+        <v>-90.34999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>172.11</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:39:59</t>
+          <t>08:36:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="F39" t="n">
-        <v>4.28</v>
+        <v>5.11</v>
       </c>
       <c r="G39" t="n">
-        <v>142.7</v>
+        <v>135.9</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>48.7</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>20.71</v>
+        <v>113.06</v>
       </c>
       <c r="K39" t="n">
-        <v>176.92</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>178.12</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:42:01</t>
+          <t>08:37:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="F40" t="n">
-        <v>3.91</v>
+        <v>2.92</v>
       </c>
       <c r="G40" t="n">
-        <v>136.9</v>
+        <v>141.7</v>
       </c>
       <c r="H40" t="n">
-        <v>99.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-136.95</v>
+        <v>-103.72</v>
       </c>
       <c r="K40" t="n">
-        <v>-120.16</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>182.19</v>
+        <v>140.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:46:33</t>
+          <t>08:41:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="F41" t="n">
-        <v>3.63</v>
+        <v>5.31</v>
       </c>
       <c r="G41" t="n">
-        <v>134</v>
+        <v>131.8</v>
       </c>
       <c r="H41" t="n">
-        <v>99.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>141.12</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-201.5</v>
+        <v>54.53</v>
       </c>
       <c r="L41" t="n">
-        <v>246.01</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:48:30</t>
+          <t>08:42:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="F42" t="n">
-        <v>4.59</v>
+        <v>6.55</v>
       </c>
       <c r="G42" t="n">
-        <v>120.6</v>
+        <v>120.9</v>
       </c>
       <c r="H42" t="n">
-        <v>98.40000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>89.88</v>
+        <v>-111.62</v>
       </c>
       <c r="K42" t="n">
-        <v>-323.97</v>
+        <v>117.61</v>
       </c>
       <c r="L42" t="n">
-        <v>336.21</v>
+        <v>162.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:50:19</t>
+          <t>08:44:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="F43" t="n">
         <v>6.55</v>
       </c>
       <c r="G43" t="n">
-        <v>138.3</v>
+        <v>125.3</v>
       </c>
       <c r="H43" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-182.73</v>
+        <v>-161.81</v>
       </c>
       <c r="K43" t="n">
-        <v>102.94</v>
+        <v>123.15</v>
       </c>
       <c r="L43" t="n">
-        <v>209.73</v>
+        <v>203.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:58:31</t>
+          <t>08:57:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>6.55</v>
       </c>
       <c r="G44" t="n">
-        <v>132.3</v>
+        <v>138.8</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>60.7</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-23.47</v>
+        <v>28.24</v>
       </c>
       <c r="K44" t="n">
-        <v>-79.14</v>
+        <v>30.19</v>
       </c>
       <c r="L44" t="n">
-        <v>82.55</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:59:49</t>
+          <t>08:59:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="F45" t="n">
-        <v>4.29</v>
+        <v>6.55</v>
       </c>
       <c r="G45" t="n">
-        <v>134.6</v>
+        <v>154.2</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.18</v>
+        <v>-3.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-31.95</v>
+        <v>-45.39</v>
       </c>
       <c r="L45" t="n">
-        <v>52.12</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:01:09</t>
+          <t>09:00:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="F46" t="n">
-        <v>3.94</v>
+        <v>4.57</v>
       </c>
       <c r="G46" t="n">
-        <v>137.3</v>
+        <v>118.1</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>33.22</v>
       </c>
       <c r="K46" t="n">
-        <v>60.06</v>
+        <v>-18.83</v>
       </c>
       <c r="L46" t="n">
-        <v>60.36</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:05:27</t>
+          <t>09:03:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="F47" t="n">
-        <v>6.1</v>
+        <v>4.97</v>
       </c>
       <c r="G47" t="n">
-        <v>121.3</v>
+        <v>126.8</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>65.7</v>
       </c>
       <c r="I47" t="n">
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>112.37</v>
+        <v>-30.64</v>
       </c>
       <c r="K47" t="n">
-        <v>0.42</v>
+        <v>65.06</v>
       </c>
       <c r="L47" t="n">
-        <v>112.37</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:06:33</t>
+          <t>09:06:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="F48" t="n">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="G48" t="n">
-        <v>130.5</v>
+        <v>142.2</v>
       </c>
       <c r="H48" t="n">
-        <v>95.2</v>
+        <v>18.9</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>66.44</v>
+        <v>1.75</v>
       </c>
       <c r="K48" t="n">
-        <v>115.85</v>
+        <v>-35.63</v>
       </c>
       <c r="L48" t="n">
-        <v>133.55</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:08:42</t>
+          <t>09:08:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="F49" t="n">
-        <v>4.74</v>
+        <v>6.37</v>
       </c>
       <c r="G49" t="n">
-        <v>123.4</v>
+        <v>133.3</v>
       </c>
       <c r="H49" t="n">
-        <v>99.8</v>
+        <v>65.7</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-105.43</v>
+        <v>-24.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-43.92</v>
+        <v>-47.53</v>
       </c>
       <c r="L49" t="n">
-        <v>114.21</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:11:42</t>
+          <t>09:13:31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="F50" t="n">
-        <v>6.12</v>
+        <v>6.45</v>
       </c>
       <c r="G50" t="n">
-        <v>145.2</v>
+        <v>127.9</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>134.78</v>
+        <v>-99.36</v>
       </c>
       <c r="K50" t="n">
-        <v>133.03</v>
+        <v>12.28</v>
       </c>
       <c r="L50" t="n">
-        <v>189.37</v>
+        <v>100.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:12:46</t>
+          <t>09:15:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="F51" t="n">
-        <v>5.9</v>
+        <v>4.59</v>
       </c>
       <c r="G51" t="n">
-        <v>143.2</v>
+        <v>121.2</v>
       </c>
       <c r="H51" t="n">
-        <v>97.8</v>
+        <v>51.8</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-54.41</v>
+        <v>24.8</v>
       </c>
       <c r="K51" t="n">
-        <v>-115.59</v>
+        <v>79.39</v>
       </c>
       <c r="L51" t="n">
-        <v>127.76</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:14:07</t>
+          <t>09:17:32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="F52" t="n">
-        <v>6.55</v>
+        <v>5.94</v>
       </c>
       <c r="G52" t="n">
-        <v>139.8</v>
+        <v>133.5</v>
       </c>
       <c r="H52" t="n">
-        <v>96.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>28.13</v>
+        <v>-73.44</v>
       </c>
       <c r="K52" t="n">
-        <v>121.8</v>
+        <v>-77.11</v>
       </c>
       <c r="L52" t="n">
-        <v>125</v>
+        <v>106.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:20:22</t>
+          <t>09:23:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="F53" t="n">
-        <v>4.68</v>
+        <v>5.37</v>
       </c>
       <c r="G53" t="n">
-        <v>143.5</v>
+        <v>134.2</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>44.6</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>196.36</v>
+        <v>-123.67</v>
       </c>
       <c r="K53" t="n">
-        <v>-94.84999999999999</v>
+        <v>-64.70999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>218.06</v>
+        <v>139.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:21:55</t>
+          <t>09:25:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="F54" t="n">
-        <v>4.39</v>
+        <v>6.55</v>
       </c>
       <c r="G54" t="n">
-        <v>110.4</v>
+        <v>125.5</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>171.2</v>
+        <v>64.03</v>
       </c>
       <c r="K54" t="n">
-        <v>-48.96</v>
+        <v>-146.24</v>
       </c>
       <c r="L54" t="n">
-        <v>178.06</v>
+        <v>159.65</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:23:49</t>
+          <t>09:27:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="F55" t="n">
-        <v>6.55</v>
+        <v>5.47</v>
       </c>
       <c r="G55" t="n">
-        <v>135.8</v>
+        <v>125.1</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>147.45</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>141.34</v>
+        <v>172.69</v>
       </c>
       <c r="L55" t="n">
-        <v>204.26</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:29:10</t>
+          <t>09:33:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="F56" t="n">
-        <v>6.55</v>
+        <v>6.22</v>
       </c>
       <c r="G56" t="n">
-        <v>142.1</v>
+        <v>127.5</v>
       </c>
       <c r="H56" t="n">
-        <v>98.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="I56" t="n">
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>323.75</v>
+        <v>-186.39</v>
       </c>
       <c r="K56" t="n">
-        <v>-175.22</v>
+        <v>-94.13</v>
       </c>
       <c r="L56" t="n">
-        <v>368.13</v>
+        <v>208.81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:31:16</t>
+          <t>09:35:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="F57" t="n">
-        <v>3.75</v>
+        <v>6.55</v>
       </c>
       <c r="G57" t="n">
-        <v>118.3</v>
+        <v>145.7</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>256.16</v>
+        <v>166.69</v>
       </c>
       <c r="K57" t="n">
-        <v>-28.09</v>
+        <v>118.19</v>
       </c>
       <c r="L57" t="n">
-        <v>257.69</v>
+        <v>204.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:33:39</t>
+          <t>09:37:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="F58" t="n">
-        <v>4.28</v>
+        <v>5.71</v>
       </c>
       <c r="G58" t="n">
-        <v>130.4</v>
+        <v>128.3</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>115.16</v>
+        <v>-186.08</v>
       </c>
       <c r="K58" t="n">
-        <v>235.66</v>
+        <v>8.32</v>
       </c>
       <c r="L58" t="n">
-        <v>262.29</v>
+        <v>186.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:43:05</t>
+          <t>09:49:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="F59" t="n">
-        <v>6.55</v>
+        <v>4.65</v>
       </c>
       <c r="G59" t="n">
-        <v>129.2</v>
+        <v>118.3</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="I59" t="n">
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>23.37</v>
+        <v>29.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-66.31</v>
+        <v>-19.07</v>
       </c>
       <c r="L59" t="n">
-        <v>70.31</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:44:06</t>
+          <t>09:52:04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="F60" t="n">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="G60" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H60" t="n">
-        <v>93.7</v>
+        <v>78</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-28.06</v>
+        <v>26.83</v>
       </c>
       <c r="K60" t="n">
-        <v>65.83</v>
+        <v>-43.44</v>
       </c>
       <c r="L60" t="n">
-        <v>71.56</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:46:40</t>
+          <t>09:54:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="F61" t="n">
-        <v>5.87</v>
+        <v>6.55</v>
       </c>
       <c r="G61" t="n">
-        <v>139.3</v>
+        <v>123.4</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>60.5</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>59.91</v>
+        <v>-31.74</v>
       </c>
       <c r="K61" t="n">
-        <v>-45.74</v>
+        <v>32.46</v>
       </c>
       <c r="L61" t="n">
-        <v>75.38</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:50:25</t>
+          <t>09:59:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="F62" t="n">
-        <v>6.55</v>
+        <v>3.31</v>
       </c>
       <c r="G62" t="n">
-        <v>139.7</v>
+        <v>142.5</v>
       </c>
       <c r="H62" t="n">
-        <v>95.3</v>
+        <v>78</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-37.43</v>
+        <v>-53.15</v>
       </c>
       <c r="K62" t="n">
-        <v>98.67</v>
+        <v>45.22</v>
       </c>
       <c r="L62" t="n">
-        <v>105.53</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:51:19</t>
+          <t>10:01:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="F63" t="n">
-        <v>5.68</v>
+        <v>6.55</v>
       </c>
       <c r="G63" t="n">
-        <v>134</v>
+        <v>135.2</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-111.32</v>
+        <v>36.24</v>
       </c>
       <c r="K63" t="n">
-        <v>-27.61</v>
+        <v>58.24</v>
       </c>
       <c r="L63" t="n">
-        <v>114.7</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:53:52</t>
+          <t>10:03:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="F64" t="n">
         <v>6.55</v>
       </c>
       <c r="G64" t="n">
-        <v>141.1</v>
+        <v>144.1</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-112.84</v>
+        <v>-47.54</v>
       </c>
       <c r="K64" t="n">
-        <v>74.92</v>
+        <v>-15.51</v>
       </c>
       <c r="L64" t="n">
-        <v>135.45</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:58:05</t>
+          <t>10:07:51</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="F65" t="n">
-        <v>6.37</v>
+        <v>6.55</v>
       </c>
       <c r="G65" t="n">
-        <v>117.1</v>
+        <v>131.3</v>
       </c>
       <c r="H65" t="n">
-        <v>95.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>84.43000000000001</v>
+        <v>89.86</v>
       </c>
       <c r="K65" t="n">
-        <v>-135.96</v>
+        <v>62.74</v>
       </c>
       <c r="L65" t="n">
-        <v>160.04</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:59:39</t>
+          <t>10:10:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="F66" t="n">
-        <v>4.19</v>
+        <v>5.35</v>
       </c>
       <c r="G66" t="n">
-        <v>133.3</v>
+        <v>138.5</v>
       </c>
       <c r="H66" t="n">
-        <v>97.8</v>
+        <v>75</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-115.02</v>
+        <v>83.77</v>
       </c>
       <c r="K66" t="n">
-        <v>7.17</v>
+        <v>-12.42</v>
       </c>
       <c r="L66" t="n">
-        <v>115.24</v>
+        <v>84.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:00:55</t>
+          <t>10:11:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="F67" t="n">
-        <v>6.55</v>
+        <v>5.63</v>
       </c>
       <c r="G67" t="n">
-        <v>138.4</v>
+        <v>124</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>35.3</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>110.63</v>
+        <v>-41.48</v>
       </c>
       <c r="K67" t="n">
-        <v>76.36</v>
+        <v>-78.67</v>
       </c>
       <c r="L67" t="n">
-        <v>134.43</v>
+        <v>88.93000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:06:04</t>
+          <t>10:16:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="F68" t="n">
         <v>6.55</v>
       </c>
       <c r="G68" t="n">
-        <v>119.3</v>
+        <v>128.7</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.38</v>
+        <v>3.54</v>
       </c>
       <c r="K68" t="n">
-        <v>-83.06</v>
+        <v>23.69</v>
       </c>
       <c r="L68" t="n">
-        <v>83.09999999999999</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:08:25</t>
+          <t>10:17:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="F69" t="n">
         <v>6.55</v>
       </c>
       <c r="G69" t="n">
-        <v>127.2</v>
+        <v>135.1</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>15.69</v>
+        <v>229.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-32.11</v>
+        <v>246.7</v>
       </c>
       <c r="L69" t="n">
-        <v>35.74</v>
+        <v>336.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:10:54</t>
+          <t>10:19:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="F70" t="n">
-        <v>6.34</v>
+        <v>6.55</v>
       </c>
       <c r="G70" t="n">
-        <v>139.1</v>
+        <v>130.7</v>
       </c>
       <c r="H70" t="n">
-        <v>99.7</v>
+        <v>77.3</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>85.77</v>
+        <v>-39.23</v>
       </c>
       <c r="K70" t="n">
-        <v>-181.66</v>
+        <v>143.79</v>
       </c>
       <c r="L70" t="n">
-        <v>200.89</v>
+        <v>149.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:15:20</t>
+          <t>10:24:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="F71" t="n">
-        <v>5.53</v>
+        <v>6.55</v>
       </c>
       <c r="G71" t="n">
-        <v>134.3</v>
+        <v>132.1</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-189.96</v>
+        <v>7.3</v>
       </c>
       <c r="K71" t="n">
-        <v>10.65</v>
+        <v>-229.43</v>
       </c>
       <c r="L71" t="n">
-        <v>190.26</v>
+        <v>229.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:17:43</t>
+          <t>10:25:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="F72" t="n">
-        <v>4.87</v>
+        <v>5.57</v>
       </c>
       <c r="G72" t="n">
-        <v>136.9</v>
+        <v>137.1</v>
       </c>
       <c r="H72" t="n">
-        <v>97.59999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-59.29</v>
+        <v>-107.82</v>
       </c>
       <c r="K72" t="n">
-        <v>-238.66</v>
+        <v>164.85</v>
       </c>
       <c r="L72" t="n">
-        <v>245.91</v>
+        <v>196.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:19:49</t>
+          <t>10:27:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="F73" t="n">
         <v>6.55</v>
       </c>
       <c r="G73" t="n">
-        <v>138.3</v>
+        <v>121.8</v>
       </c>
       <c r="H73" t="n">
-        <v>94.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>54.55</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-232.14</v>
+        <v>208.1</v>
       </c>
       <c r="L73" t="n">
-        <v>238.46</v>
+        <v>219.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:31:35</t>
+          <t>10:38:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="F74" t="n">
         <v>6.55</v>
       </c>
       <c r="G74" t="n">
-        <v>138.5</v>
+        <v>119.8</v>
       </c>
       <c r="H74" t="n">
-        <v>97.3</v>
+        <v>80</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>70.88</v>
+        <v>38.79</v>
       </c>
       <c r="K74" t="n">
-        <v>38.56</v>
+        <v>-15.7</v>
       </c>
       <c r="L74" t="n">
-        <v>80.69</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:33:11</t>
+          <t>10:40:37</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="F75" t="n">
-        <v>6.55</v>
+        <v>6.05</v>
       </c>
       <c r="G75" t="n">
-        <v>137.6</v>
+        <v>136</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>29.81</v>
+        <v>47.68</v>
       </c>
       <c r="K75" t="n">
-        <v>55.01</v>
+        <v>8.19</v>
       </c>
       <c r="L75" t="n">
-        <v>62.57</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:34:25</t>
+          <t>10:42:37</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="F76" t="n">
         <v>6.55</v>
       </c>
       <c r="G76" t="n">
-        <v>139</v>
+        <v>135.6</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>53.7</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>12.89</v>
+        <v>-39.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-59.28</v>
+        <v>-19.51</v>
       </c>
       <c r="L76" t="n">
-        <v>60.66</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:39:07</t>
+          <t>10:46:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="F77" t="n">
-        <v>6.55</v>
+        <v>4.13</v>
       </c>
       <c r="G77" t="n">
-        <v>139.7</v>
+        <v>124.6</v>
       </c>
       <c r="H77" t="n">
-        <v>93.3</v>
+        <v>89.3</v>
       </c>
       <c r="I77" t="n">
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-23.73</v>
+        <v>18.61</v>
       </c>
       <c r="K77" t="n">
-        <v>65.12</v>
+        <v>-40.02</v>
       </c>
       <c r="L77" t="n">
-        <v>69.31</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:40:58</t>
+          <t>10:47:52</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="G78" t="n">
-        <v>121.7</v>
+        <v>134.7</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>81.19</v>
+        <v>-51.83</v>
       </c>
       <c r="K78" t="n">
-        <v>28.32</v>
+        <v>0.49</v>
       </c>
       <c r="L78" t="n">
-        <v>85.98999999999999</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:43:23</t>
+          <t>10:49:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="F79" t="n">
-        <v>5.08</v>
+        <v>2.54</v>
       </c>
       <c r="G79" t="n">
-        <v>148.7</v>
+        <v>137.5</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>62.81</v>
+        <v>28.86</v>
       </c>
       <c r="K79" t="n">
-        <v>46.06</v>
+        <v>-49.14</v>
       </c>
       <c r="L79" t="n">
-        <v>77.89</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:48:28</t>
+          <t>10:53:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="F80" t="n">
-        <v>5.8</v>
+        <v>4.78</v>
       </c>
       <c r="G80" t="n">
-        <v>134.5</v>
+        <v>128.4</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>28.4</v>
       </c>
       <c r="I80" t="n">
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>106</v>
+        <v>21.09</v>
       </c>
       <c r="K80" t="n">
-        <v>-150.25</v>
+        <v>89.12</v>
       </c>
       <c r="L80" t="n">
-        <v>183.88</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:50:21</t>
+          <t>10:55:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="F81" t="n">
         <v>6.55</v>
       </c>
       <c r="G81" t="n">
-        <v>131.7</v>
+        <v>136.2</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.63</v>
+        <v>64.37</v>
       </c>
       <c r="K81" t="n">
-        <v>100.01</v>
+        <v>-37.78</v>
       </c>
       <c r="L81" t="n">
-        <v>100.68</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:52:18</t>
+          <t>10:57:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="F82" t="n">
         <v>6.55</v>
       </c>
       <c r="G82" t="n">
-        <v>132.1</v>
+        <v>143.4</v>
       </c>
       <c r="H82" t="n">
-        <v>93.5</v>
+        <v>81.5</v>
       </c>
       <c r="I82" t="n">
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>30.96</v>
+        <v>24.78</v>
       </c>
       <c r="K82" t="n">
-        <v>-101.72</v>
+        <v>-90.7</v>
       </c>
       <c r="L82" t="n">
-        <v>106.33</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:57:22</t>
+          <t>11:01:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="F83" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="G83" t="n">
-        <v>130.3</v>
+        <v>140.5</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>58.6</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>38.36</v>
+        <v>14.52</v>
       </c>
       <c r="K83" t="n">
-        <v>169.24</v>
+        <v>-166.54</v>
       </c>
       <c r="L83" t="n">
-        <v>173.53</v>
+        <v>167.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:58:46</t>
+          <t>11:02:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="F84" t="n">
-        <v>6.55</v>
+        <v>5.08</v>
       </c>
       <c r="G84" t="n">
-        <v>134.9</v>
+        <v>135.8</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>32.8</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>78.59</v>
+        <v>67.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-190.64</v>
+        <v>-158.52</v>
       </c>
       <c r="L84" t="n">
-        <v>206.21</v>
+        <v>172.34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:00:22</t>
+          <t>11:04:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="F85" t="n">
         <v>6.55</v>
       </c>
       <c r="G85" t="n">
-        <v>137.1</v>
+        <v>118.3</v>
       </c>
       <c r="H85" t="n">
-        <v>98.7</v>
+        <v>58.6</v>
       </c>
       <c r="I85" t="n">
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-210.22</v>
+        <v>136.5</v>
       </c>
       <c r="K85" t="n">
-        <v>22.4</v>
+        <v>14.14</v>
       </c>
       <c r="L85" t="n">
-        <v>211.41</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:05:41</t>
+          <t>11:08:56</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="F86" t="n">
         <v>6.55</v>
       </c>
       <c r="G86" t="n">
-        <v>137.7</v>
+        <v>135.6</v>
       </c>
       <c r="H86" t="n">
-        <v>99.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="I86" t="n">
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>7.36</v>
+        <v>-76.37</v>
       </c>
       <c r="K86" t="n">
-        <v>-291.76</v>
+        <v>-274.69</v>
       </c>
       <c r="L86" t="n">
-        <v>291.86</v>
+        <v>285.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:07:33</t>
+          <t>11:10:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="F87" t="n">
         <v>6.55</v>
       </c>
       <c r="G87" t="n">
-        <v>148.9</v>
+        <v>142.2</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>52.1</v>
+        <v>181.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-252.63</v>
+        <v>33.58</v>
       </c>
       <c r="L87" t="n">
-        <v>257.94</v>
+        <v>184.59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:09:17</t>
+          <t>11:12:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="F88" t="n">
-        <v>6.55</v>
+        <v>4.44</v>
       </c>
       <c r="G88" t="n">
-        <v>135.6</v>
+        <v>138.8</v>
       </c>
       <c r="H88" t="n">
-        <v>98.59999999999999</v>
+        <v>39.5</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>10.8</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-260.26</v>
+        <v>164.43</v>
       </c>
       <c r="L88" t="n">
-        <v>260.49</v>
+        <v>190.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="F14" t="n">
-        <v>4.47</v>
+        <v>5.74</v>
       </c>
       <c r="G14" t="n">
-        <v>132.3</v>
+        <v>130.5</v>
       </c>
       <c r="H14" t="n">
-        <v>68.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>33.85</v>
+        <v>-4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>11.77</v>
+        <v>-38.8</v>
       </c>
       <c r="L14" t="n">
-        <v>35.83</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:31:45</t>
+          <t>07:31:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="F15" t="n">
-        <v>6.19</v>
+        <v>6.55</v>
       </c>
       <c r="G15" t="n">
-        <v>125.1</v>
+        <v>129.9</v>
       </c>
       <c r="H15" t="n">
-        <v>24.5</v>
+        <v>58</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-43.87</v>
+        <v>19.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.66</v>
+        <v>-26.81</v>
       </c>
       <c r="L15" t="n">
-        <v>44.03</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:34:02</t>
+          <t>07:32:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="F16" t="n">
-        <v>6.55</v>
+        <v>5.55</v>
       </c>
       <c r="G16" t="n">
-        <v>141.8</v>
+        <v>137</v>
       </c>
       <c r="H16" t="n">
-        <v>74.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.02</v>
+        <v>-7.49</v>
       </c>
       <c r="K16" t="n">
-        <v>-19.19</v>
+        <v>-31.96</v>
       </c>
       <c r="L16" t="n">
-        <v>44.39</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:37:50</t>
+          <t>07:38:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="F17" t="n">
-        <v>4.19</v>
+        <v>6.55</v>
       </c>
       <c r="G17" t="n">
-        <v>122</v>
+        <v>143.8</v>
       </c>
       <c r="H17" t="n">
-        <v>46.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-15.17</v>
+        <v>41.96</v>
       </c>
       <c r="K17" t="n">
-        <v>-47.42</v>
+        <v>-27.53</v>
       </c>
       <c r="L17" t="n">
-        <v>49.78</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:39:39</t>
+          <t>07:39:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="F18" t="n">
-        <v>5.42</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>145.4</v>
+        <v>143.3</v>
       </c>
       <c r="H18" t="n">
-        <v>65.5</v>
+        <v>79.7</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.91</v>
+        <v>-22.04</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.83</v>
+        <v>-49.78</v>
       </c>
       <c r="L18" t="n">
-        <v>46.35</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:40:55</t>
+          <t>07:42:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="F19" t="n">
-        <v>6.55</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>132.6</v>
+        <v>142.7</v>
       </c>
       <c r="H19" t="n">
-        <v>59.8</v>
+        <v>79.7</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>46.3</v>
+        <v>-18.65</v>
       </c>
       <c r="K19" t="n">
-        <v>-29.82</v>
+        <v>-51.92</v>
       </c>
       <c r="L19" t="n">
-        <v>55.07</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:45:12</t>
+          <t>07:47:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="F20" t="n">
         <v>6.55</v>
       </c>
       <c r="G20" t="n">
-        <v>131.6</v>
+        <v>128.7</v>
       </c>
       <c r="H20" t="n">
-        <v>62.9</v>
+        <v>66.5</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>78.68000000000001</v>
+        <v>67.95</v>
       </c>
       <c r="K20" t="n">
-        <v>52.41</v>
+        <v>-27.5</v>
       </c>
       <c r="L20" t="n">
-        <v>94.54000000000001</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:46:36</t>
+          <t>07:48:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="F21" t="n">
-        <v>6.55</v>
+        <v>5.26</v>
       </c>
       <c r="G21" t="n">
-        <v>133.2</v>
+        <v>128.7</v>
       </c>
       <c r="H21" t="n">
-        <v>43.7</v>
+        <v>41.9</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>112.39</v>
+        <v>17.46</v>
       </c>
       <c r="K21" t="n">
-        <v>23.19</v>
+        <v>-76.61</v>
       </c>
       <c r="L21" t="n">
-        <v>114.76</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:47:55</t>
+          <t>07:49:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="F22" t="n">
-        <v>6.44</v>
+        <v>6.25</v>
       </c>
       <c r="G22" t="n">
-        <v>120.8</v>
+        <v>126.5</v>
       </c>
       <c r="H22" t="n">
-        <v>40.8</v>
+        <v>39.9</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-49.62</v>
+        <v>80.42</v>
       </c>
       <c r="K22" t="n">
-        <v>-42.68</v>
+        <v>48.28</v>
       </c>
       <c r="L22" t="n">
-        <v>65.45</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:52:53</t>
+          <t>07:55:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="F23" t="n">
-        <v>3.27</v>
+        <v>5.08</v>
       </c>
       <c r="G23" t="n">
-        <v>137.5</v>
+        <v>129.8</v>
       </c>
       <c r="H23" t="n">
-        <v>70.5</v>
+        <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>104.99</v>
+        <v>-69.08</v>
       </c>
       <c r="K23" t="n">
-        <v>-41.23</v>
+        <v>-120.89</v>
       </c>
       <c r="L23" t="n">
-        <v>112.8</v>
+        <v>139.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:53:42</t>
+          <t>07:57:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="F24" t="n">
-        <v>2.68</v>
+        <v>3.51</v>
       </c>
       <c r="G24" t="n">
-        <v>141</v>
+        <v>130.2</v>
       </c>
       <c r="H24" t="n">
-        <v>72.40000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-29.41</v>
+        <v>-130.43</v>
       </c>
       <c r="K24" t="n">
-        <v>125.88</v>
+        <v>81.89</v>
       </c>
       <c r="L24" t="n">
-        <v>129.27</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:54:42</t>
+          <t>07:59:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="F25" t="n">
-        <v>5.87</v>
+        <v>6.34</v>
       </c>
       <c r="G25" t="n">
-        <v>119.8</v>
+        <v>146.5</v>
       </c>
       <c r="H25" t="n">
-        <v>91.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-22.51</v>
+        <v>114.11</v>
       </c>
       <c r="K25" t="n">
-        <v>-67.03</v>
+        <v>1.3</v>
       </c>
       <c r="L25" t="n">
-        <v>70.70999999999999</v>
+        <v>114.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:59:08</t>
+          <t>08:05:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="F26" t="n">
-        <v>5.39</v>
+        <v>5.55</v>
       </c>
       <c r="G26" t="n">
-        <v>130.2</v>
+        <v>140.6</v>
       </c>
       <c r="H26" t="n">
-        <v>61.2</v>
+        <v>79</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-68.11</v>
+        <v>81.94</v>
       </c>
       <c r="K26" t="n">
-        <v>-161.62</v>
+        <v>-166.11</v>
       </c>
       <c r="L26" t="n">
-        <v>175.38</v>
+        <v>185.22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:00:38</t>
+          <t>08:07:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="F27" t="n">
-        <v>2.81</v>
+        <v>6.55</v>
       </c>
       <c r="G27" t="n">
-        <v>156.6</v>
+        <v>120.4</v>
       </c>
       <c r="H27" t="n">
-        <v>50.8</v>
+        <v>84.7</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>33.41</v>
+        <v>-185.97</v>
       </c>
       <c r="K27" t="n">
-        <v>141.89</v>
+        <v>-91.81999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>145.77</v>
+        <v>207.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:03:21</t>
+          <t>08:09:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="F28" t="n">
-        <v>4.9</v>
+        <v>4.37</v>
       </c>
       <c r="G28" t="n">
-        <v>127.8</v>
+        <v>124.1</v>
       </c>
       <c r="H28" t="n">
-        <v>56.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>102.71</v>
+        <v>-69.8</v>
       </c>
       <c r="K28" t="n">
-        <v>237.67</v>
+        <v>-139.71</v>
       </c>
       <c r="L28" t="n">
-        <v>258.91</v>
+        <v>156.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:12:42</t>
+          <t>08:18:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="F29" t="n">
-        <v>5.7</v>
+        <v>3.31</v>
       </c>
       <c r="G29" t="n">
-        <v>140.3</v>
+        <v>140</v>
       </c>
       <c r="H29" t="n">
-        <v>84.5</v>
+        <v>49.4</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>31.17</v>
+        <v>-9.99</v>
       </c>
       <c r="K29" t="n">
-        <v>-21.4</v>
+        <v>-24.79</v>
       </c>
       <c r="L29" t="n">
-        <v>37.81</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:14:04</t>
+          <t>08:20:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="F30" t="n">
-        <v>6.21</v>
+        <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>129</v>
+        <v>139.4</v>
       </c>
       <c r="H30" t="n">
-        <v>65.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I30" t="n">
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.61</v>
+        <v>-27.62</v>
       </c>
       <c r="K30" t="n">
-        <v>36.91</v>
+        <v>-8.33</v>
       </c>
       <c r="L30" t="n">
-        <v>38.4</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:15:11</t>
+          <t>08:22:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="F31" t="n">
-        <v>6.55</v>
+        <v>6.26</v>
       </c>
       <c r="G31" t="n">
-        <v>131.2</v>
+        <v>135.2</v>
       </c>
       <c r="H31" t="n">
-        <v>74.8</v>
+        <v>62.1</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>1.13</v>
+        <v>4.36</v>
       </c>
       <c r="K31" t="n">
-        <v>33.17</v>
+        <v>-30.55</v>
       </c>
       <c r="L31" t="n">
-        <v>33.19</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:20:08</t>
+          <t>08:27:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="F32" t="n">
         <v>6.55</v>
       </c>
       <c r="G32" t="n">
-        <v>127.6</v>
+        <v>127.3</v>
       </c>
       <c r="H32" t="n">
-        <v>69.2</v>
+        <v>55.7</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>42.93</v>
+        <v>19.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-37.78</v>
+        <v>-4.97</v>
       </c>
       <c r="L32" t="n">
-        <v>57.19</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:21:17</t>
+          <t>08:29:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="F33" t="n">
-        <v>4.42</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>111.4</v>
+        <v>139.4</v>
       </c>
       <c r="H33" t="n">
-        <v>89.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>16.54</v>
+        <v>-22.8</v>
       </c>
       <c r="K33" t="n">
-        <v>41.37</v>
+        <v>-49.09</v>
       </c>
       <c r="L33" t="n">
-        <v>44.56</v>
+        <v>54.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:22:07</t>
+          <t>08:30:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F34" t="n">
-        <v>6.41</v>
+        <v>2.86</v>
       </c>
       <c r="G34" t="n">
-        <v>130.5</v>
+        <v>138.8</v>
       </c>
       <c r="H34" t="n">
-        <v>73.8</v>
+        <v>63.8</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>42.34</v>
+        <v>50.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-33.55</v>
+        <v>28.3</v>
       </c>
       <c r="L34" t="n">
-        <v>54.02</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:26:54</t>
+          <t>08:36:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="F35" t="n">
-        <v>5.01</v>
+        <v>6.15</v>
       </c>
       <c r="G35" t="n">
-        <v>129.3</v>
+        <v>144.2</v>
       </c>
       <c r="H35" t="n">
-        <v>37.8</v>
+        <v>44.6</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>50.93</v>
+        <v>51.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-39.43</v>
+        <v>50.72</v>
       </c>
       <c r="L35" t="n">
-        <v>64.41</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:28:53</t>
+          <t>08:38:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="F36" t="n">
-        <v>6.55</v>
+        <v>4.29</v>
       </c>
       <c r="G36" t="n">
-        <v>135.9</v>
+        <v>134.6</v>
       </c>
       <c r="H36" t="n">
-        <v>73.2</v>
+        <v>41.1</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>44.3</v>
+        <v>-75.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-57.21</v>
+        <v>19.95</v>
       </c>
       <c r="L36" t="n">
-        <v>72.36</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:30:06</t>
+          <t>08:39:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="F37" t="n">
         <v>6.55</v>
       </c>
       <c r="G37" t="n">
-        <v>132.1</v>
+        <v>141</v>
       </c>
       <c r="H37" t="n">
-        <v>64.5</v>
+        <v>55.9</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-55.99</v>
+        <v>-65.92</v>
       </c>
       <c r="K37" t="n">
-        <v>-65.05</v>
+        <v>-26.37</v>
       </c>
       <c r="L37" t="n">
-        <v>85.83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:34:53</t>
+          <t>08:43:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="F38" t="n">
-        <v>3.89</v>
+        <v>5.38</v>
       </c>
       <c r="G38" t="n">
-        <v>138.3</v>
+        <v>131.7</v>
       </c>
       <c r="H38" t="n">
-        <v>52.1</v>
+        <v>89.7</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-77.17</v>
+        <v>121.83</v>
       </c>
       <c r="K38" t="n">
-        <v>-90.34999999999999</v>
+        <v>11.36</v>
       </c>
       <c r="L38" t="n">
-        <v>118.83</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:36:06</t>
+          <t>08:45:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="F39" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="G39" t="n">
-        <v>135.9</v>
+        <v>134.5</v>
       </c>
       <c r="H39" t="n">
-        <v>48.7</v>
+        <v>84.3</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>113.06</v>
+        <v>80.63</v>
       </c>
       <c r="K39" t="n">
-        <v>73.29000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="L39" t="n">
-        <v>134.74</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:37:21</t>
+          <t>08:46:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="F40" t="n">
-        <v>2.92</v>
+        <v>6.55</v>
       </c>
       <c r="G40" t="n">
-        <v>141.7</v>
+        <v>120.6</v>
       </c>
       <c r="H40" t="n">
-        <v>64.59999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-103.72</v>
+        <v>-34.21</v>
       </c>
       <c r="K40" t="n">
-        <v>94.45999999999999</v>
+        <v>-106.4</v>
       </c>
       <c r="L40" t="n">
-        <v>140.29</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:41:03</t>
+          <t>08:52:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="F41" t="n">
-        <v>5.31</v>
+        <v>4.45</v>
       </c>
       <c r="G41" t="n">
-        <v>131.8</v>
+        <v>134.3</v>
       </c>
       <c r="H41" t="n">
-        <v>86.59999999999999</v>
+        <v>42.5</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>80.70999999999999</v>
+        <v>134.84</v>
       </c>
       <c r="K41" t="n">
-        <v>54.53</v>
+        <v>94.38</v>
       </c>
       <c r="L41" t="n">
-        <v>97.41</v>
+        <v>164.59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:42:49</t>
+          <t>08:54:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="F42" t="n">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="G42" t="n">
-        <v>120.9</v>
+        <v>130.3</v>
       </c>
       <c r="H42" t="n">
-        <v>50.5</v>
+        <v>58.9</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-111.62</v>
+        <v>-126.08</v>
       </c>
       <c r="K42" t="n">
-        <v>117.61</v>
+        <v>-114.63</v>
       </c>
       <c r="L42" t="n">
-        <v>162.15</v>
+        <v>170.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:44:57</t>
+          <t>08:56:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="F43" t="n">
         <v>6.55</v>
       </c>
       <c r="G43" t="n">
-        <v>125.3</v>
+        <v>129</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-161.81</v>
+        <v>-118.73</v>
       </c>
       <c r="K43" t="n">
-        <v>123.15</v>
+        <v>119.36</v>
       </c>
       <c r="L43" t="n">
-        <v>203.34</v>
+        <v>168.35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:57:19</t>
+          <t>09:05:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="F44" t="n">
-        <v>6.55</v>
+        <v>4.74</v>
       </c>
       <c r="G44" t="n">
-        <v>138.8</v>
+        <v>119.4</v>
       </c>
       <c r="H44" t="n">
-        <v>60.7</v>
+        <v>43.2</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>28.24</v>
+        <v>-5.66</v>
       </c>
       <c r="K44" t="n">
-        <v>30.19</v>
+        <v>19.77</v>
       </c>
       <c r="L44" t="n">
-        <v>41.34</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:59:13</t>
+          <t>09:06:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.04</v>
+        <v>2.79</v>
       </c>
       <c r="F45" t="n">
         <v>6.55</v>
       </c>
       <c r="G45" t="n">
-        <v>154.2</v>
+        <v>134.6</v>
       </c>
       <c r="H45" t="n">
-        <v>41.7</v>
+        <v>54.2</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.09</v>
+        <v>-24.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-45.39</v>
+        <v>-36.29</v>
       </c>
       <c r="L45" t="n">
-        <v>45.5</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:00:37</t>
+          <t>09:08:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="F46" t="n">
-        <v>4.57</v>
+        <v>3.61</v>
       </c>
       <c r="G46" t="n">
-        <v>118.1</v>
+        <v>118.3</v>
       </c>
       <c r="H46" t="n">
-        <v>63.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>33.22</v>
+        <v>-20.14</v>
       </c>
       <c r="K46" t="n">
-        <v>-18.83</v>
+        <v>24.35</v>
       </c>
       <c r="L46" t="n">
-        <v>38.18</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:03:56</t>
+          <t>09:12:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="F47" t="n">
-        <v>4.97</v>
+        <v>6.55</v>
       </c>
       <c r="G47" t="n">
-        <v>126.8</v>
+        <v>129.8</v>
       </c>
       <c r="H47" t="n">
-        <v>65.7</v>
+        <v>63.8</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-30.64</v>
+        <v>-43.28</v>
       </c>
       <c r="K47" t="n">
-        <v>65.06</v>
+        <v>-17.66</v>
       </c>
       <c r="L47" t="n">
-        <v>71.91</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:06:26</t>
+          <t>09:15:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="F48" t="n">
-        <v>5.86</v>
+        <v>3.68</v>
       </c>
       <c r="G48" t="n">
-        <v>142.2</v>
+        <v>135.8</v>
       </c>
       <c r="H48" t="n">
-        <v>18.9</v>
+        <v>61.5</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>1.75</v>
+        <v>-41.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.63</v>
+        <v>-40.76</v>
       </c>
       <c r="L48" t="n">
-        <v>35.67</v>
+        <v>58.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:08:11</t>
+          <t>09:16:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2098,31 +2098,31 @@
         <v>2.02</v>
       </c>
       <c r="F49" t="n">
-        <v>6.37</v>
+        <v>6.55</v>
       </c>
       <c r="G49" t="n">
-        <v>133.3</v>
+        <v>122.1</v>
       </c>
       <c r="H49" t="n">
-        <v>65.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.32</v>
+        <v>16.03</v>
       </c>
       <c r="K49" t="n">
-        <v>-47.53</v>
+        <v>-62.7</v>
       </c>
       <c r="L49" t="n">
-        <v>53.39</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:13:31</t>
+          <t>09:20:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="F50" t="n">
-        <v>6.45</v>
+        <v>5.94</v>
       </c>
       <c r="G50" t="n">
-        <v>127.9</v>
+        <v>135</v>
       </c>
       <c r="H50" t="n">
-        <v>59.1</v>
+        <v>74</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-99.36</v>
+        <v>31.92</v>
       </c>
       <c r="K50" t="n">
-        <v>12.28</v>
+        <v>82.11</v>
       </c>
       <c r="L50" t="n">
-        <v>100.12</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:15:20</t>
+          <t>09:22:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.07</v>
+        <v>2.69</v>
       </c>
       <c r="F51" t="n">
-        <v>4.59</v>
+        <v>6.55</v>
       </c>
       <c r="G51" t="n">
-        <v>121.2</v>
+        <v>132.8</v>
       </c>
       <c r="H51" t="n">
-        <v>51.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>24.8</v>
+        <v>62.8</v>
       </c>
       <c r="K51" t="n">
-        <v>79.39</v>
+        <v>-6.3</v>
       </c>
       <c r="L51" t="n">
-        <v>83.18000000000001</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:17:32</t>
+          <t>09:23:37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="F52" t="n">
-        <v>5.94</v>
+        <v>2.27</v>
       </c>
       <c r="G52" t="n">
-        <v>133.5</v>
+        <v>140.8</v>
       </c>
       <c r="H52" t="n">
-        <v>61.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-73.44</v>
+        <v>-61.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.11</v>
+        <v>49.63</v>
       </c>
       <c r="L52" t="n">
-        <v>106.49</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:23:38</t>
+          <t>09:27:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="F53" t="n">
-        <v>5.37</v>
+        <v>6.55</v>
       </c>
       <c r="G53" t="n">
-        <v>134.2</v>
+        <v>136.3</v>
       </c>
       <c r="H53" t="n">
-        <v>44.6</v>
+        <v>69.8</v>
       </c>
       <c r="I53" t="n">
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-123.67</v>
+        <v>118.63</v>
       </c>
       <c r="K53" t="n">
-        <v>-64.70999999999999</v>
+        <v>52.79</v>
       </c>
       <c r="L53" t="n">
-        <v>139.57</v>
+        <v>129.85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:25:47</t>
+          <t>09:28:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="F54" t="n">
         <v>6.55</v>
       </c>
       <c r="G54" t="n">
-        <v>125.5</v>
+        <v>139.9</v>
       </c>
       <c r="H54" t="n">
-        <v>78.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>64.03</v>
+        <v>200.6</v>
       </c>
       <c r="K54" t="n">
-        <v>-146.24</v>
+        <v>43.23</v>
       </c>
       <c r="L54" t="n">
-        <v>159.65</v>
+        <v>205.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:27:37</t>
+          <t>09:31:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="F55" t="n">
-        <v>5.47</v>
+        <v>5.79</v>
       </c>
       <c r="G55" t="n">
-        <v>125.1</v>
+        <v>120.2</v>
       </c>
       <c r="H55" t="n">
-        <v>52.4</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>8.390000000000001</v>
+        <v>-130.92</v>
       </c>
       <c r="K55" t="n">
-        <v>172.69</v>
+        <v>-42.46</v>
       </c>
       <c r="L55" t="n">
-        <v>172.9</v>
+        <v>137.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:33:50</t>
+          <t>09:36:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="F56" t="n">
-        <v>6.22</v>
+        <v>6.55</v>
       </c>
       <c r="G56" t="n">
-        <v>127.5</v>
+        <v>124.9</v>
       </c>
       <c r="H56" t="n">
-        <v>64</v>
+        <v>54.3</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-186.39</v>
+        <v>-192.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-94.13</v>
+        <v>-101.23</v>
       </c>
       <c r="L56" t="n">
-        <v>208.81</v>
+        <v>217.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:35:04</t>
+          <t>09:39:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="F57" t="n">
         <v>6.55</v>
       </c>
       <c r="G57" t="n">
-        <v>145.7</v>
+        <v>123.1</v>
       </c>
       <c r="H57" t="n">
-        <v>62.5</v>
+        <v>47.8</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>166.69</v>
+        <v>-43.3</v>
       </c>
       <c r="K57" t="n">
-        <v>118.19</v>
+        <v>-162.66</v>
       </c>
       <c r="L57" t="n">
-        <v>204.33</v>
+        <v>168.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:37:34</t>
+          <t>09:41:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="F58" t="n">
-        <v>5.71</v>
+        <v>5.92</v>
       </c>
       <c r="G58" t="n">
-        <v>128.3</v>
+        <v>121.4</v>
       </c>
       <c r="H58" t="n">
-        <v>82.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-186.08</v>
+        <v>129.67</v>
       </c>
       <c r="K58" t="n">
-        <v>8.32</v>
+        <v>-142.92</v>
       </c>
       <c r="L58" t="n">
-        <v>186.26</v>
+        <v>192.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:49:52</t>
+          <t>09:49:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="F59" t="n">
-        <v>4.65</v>
+        <v>5.28</v>
       </c>
       <c r="G59" t="n">
-        <v>118.3</v>
+        <v>132.1</v>
       </c>
       <c r="H59" t="n">
-        <v>95.3</v>
+        <v>62.8</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>29.08</v>
+        <v>-13.43</v>
       </c>
       <c r="K59" t="n">
-        <v>-19.07</v>
+        <v>-29.13</v>
       </c>
       <c r="L59" t="n">
-        <v>34.78</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:52:04</t>
+          <t>09:52:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="F60" t="n">
-        <v>4.8</v>
+        <v>6.55</v>
       </c>
       <c r="G60" t="n">
-        <v>137</v>
+        <v>136.6</v>
       </c>
       <c r="H60" t="n">
-        <v>78</v>
+        <v>64.7</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>26.83</v>
+        <v>-34.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-43.44</v>
+        <v>13.05</v>
       </c>
       <c r="L60" t="n">
-        <v>51.06</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:54:11</t>
+          <t>09:53:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="F61" t="n">
         <v>6.55</v>
       </c>
       <c r="G61" t="n">
-        <v>123.4</v>
+        <v>135.4</v>
       </c>
       <c r="H61" t="n">
-        <v>60.5</v>
+        <v>82.8</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.74</v>
+        <v>-8.74</v>
       </c>
       <c r="K61" t="n">
-        <v>32.46</v>
+        <v>-42.85</v>
       </c>
       <c r="L61" t="n">
-        <v>45.4</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:59:36</t>
+          <t>09:58:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="F62" t="n">
-        <v>3.31</v>
+        <v>6.28</v>
       </c>
       <c r="G62" t="n">
-        <v>142.5</v>
+        <v>152.2</v>
       </c>
       <c r="H62" t="n">
-        <v>78</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.15</v>
+        <v>-50.37</v>
       </c>
       <c r="K62" t="n">
-        <v>45.22</v>
+        <v>23.99</v>
       </c>
       <c r="L62" t="n">
-        <v>69.78</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:01:43</t>
+          <t>09:59:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="F63" t="n">
         <v>6.55</v>
       </c>
       <c r="G63" t="n">
-        <v>135.2</v>
+        <v>128.2</v>
       </c>
       <c r="H63" t="n">
-        <v>70</v>
+        <v>88.7</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>36.24</v>
+        <v>48.79</v>
       </c>
       <c r="K63" t="n">
-        <v>58.24</v>
+        <v>24.49</v>
       </c>
       <c r="L63" t="n">
-        <v>68.59</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:03:51</t>
+          <t>10:00:42</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.72</v>
+        <v>2.29</v>
       </c>
       <c r="F64" t="n">
         <v>6.55</v>
       </c>
       <c r="G64" t="n">
-        <v>144.1</v>
+        <v>125.2</v>
       </c>
       <c r="H64" t="n">
-        <v>54.5</v>
+        <v>56.6</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-47.54</v>
+        <v>-14.04</v>
       </c>
       <c r="K64" t="n">
-        <v>-15.51</v>
+        <v>70.08</v>
       </c>
       <c r="L64" t="n">
-        <v>50.01</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:07:51</t>
+          <t>10:05:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="F65" t="n">
-        <v>6.55</v>
+        <v>4.53</v>
       </c>
       <c r="G65" t="n">
-        <v>131.3</v>
+        <v>124.1</v>
       </c>
       <c r="H65" t="n">
-        <v>71.2</v>
+        <v>58.2</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>89.86</v>
+        <v>-65.08</v>
       </c>
       <c r="K65" t="n">
-        <v>62.74</v>
+        <v>20.3</v>
       </c>
       <c r="L65" t="n">
-        <v>109.6</v>
+        <v>68.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:10:17</t>
+          <t>10:07:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="F66" t="n">
-        <v>5.35</v>
+        <v>5.63</v>
       </c>
       <c r="G66" t="n">
-        <v>138.5</v>
+        <v>133.4</v>
       </c>
       <c r="H66" t="n">
-        <v>75</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>83.77</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-12.42</v>
+        <v>-49.16</v>
       </c>
       <c r="L66" t="n">
-        <v>84.69</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:11:10</t>
+          <t>10:08:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="F67" t="n">
-        <v>5.63</v>
+        <v>6.55</v>
       </c>
       <c r="G67" t="n">
-        <v>124</v>
+        <v>142.2</v>
       </c>
       <c r="H67" t="n">
-        <v>35.3</v>
+        <v>65.3</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-41.48</v>
+        <v>-34.89</v>
       </c>
       <c r="K67" t="n">
-        <v>-78.67</v>
+        <v>-97.58</v>
       </c>
       <c r="L67" t="n">
-        <v>88.93000000000001</v>
+        <v>103.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:16:01</t>
+          <t>10:14:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="F68" t="n">
         <v>6.55</v>
       </c>
       <c r="G68" t="n">
-        <v>128.7</v>
+        <v>132.1</v>
       </c>
       <c r="H68" t="n">
-        <v>76.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>3.54</v>
+        <v>-114.55</v>
       </c>
       <c r="K68" t="n">
-        <v>23.69</v>
+        <v>88.2</v>
       </c>
       <c r="L68" t="n">
-        <v>23.96</v>
+        <v>144.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:17:04</t>
+          <t>10:15:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="F69" t="n">
-        <v>6.55</v>
+        <v>6.46</v>
       </c>
       <c r="G69" t="n">
-        <v>135.1</v>
+        <v>136.7</v>
       </c>
       <c r="H69" t="n">
-        <v>71.40000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>229.28</v>
+        <v>15.77</v>
       </c>
       <c r="K69" t="n">
-        <v>246.7</v>
+        <v>-114.01</v>
       </c>
       <c r="L69" t="n">
-        <v>336.79</v>
+        <v>115.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:19:23</t>
+          <t>10:17:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="F70" t="n">
-        <v>6.55</v>
+        <v>5.08</v>
       </c>
       <c r="G70" t="n">
-        <v>130.7</v>
+        <v>138.7</v>
       </c>
       <c r="H70" t="n">
-        <v>77.3</v>
+        <v>29.6</v>
       </c>
       <c r="I70" t="n">
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-39.23</v>
+        <v>11.5</v>
       </c>
       <c r="K70" t="n">
-        <v>143.79</v>
+        <v>128.02</v>
       </c>
       <c r="L70" t="n">
-        <v>149.04</v>
+        <v>128.53</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:24:15</t>
+          <t>10:21:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="F71" t="n">
         <v>6.55</v>
       </c>
       <c r="G71" t="n">
-        <v>132.1</v>
+        <v>132.4</v>
       </c>
       <c r="H71" t="n">
-        <v>22.5</v>
+        <v>36.5</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>7.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-229.43</v>
+        <v>-144.68</v>
       </c>
       <c r="L71" t="n">
-        <v>229.54</v>
+        <v>158.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:25:28</t>
+          <t>10:23:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="F72" t="n">
-        <v>5.57</v>
+        <v>4.42</v>
       </c>
       <c r="G72" t="n">
-        <v>137.1</v>
+        <v>135.2</v>
       </c>
       <c r="H72" t="n">
-        <v>62.4</v>
+        <v>31.9</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-107.82</v>
+        <v>-54.66</v>
       </c>
       <c r="K72" t="n">
-        <v>164.85</v>
+        <v>-194.34</v>
       </c>
       <c r="L72" t="n">
-        <v>196.98</v>
+        <v>201.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:27:46</t>
+          <t>10:25:52</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="F73" t="n">
-        <v>6.55</v>
+        <v>3.11</v>
       </c>
       <c r="G73" t="n">
-        <v>121.8</v>
+        <v>128.3</v>
       </c>
       <c r="H73" t="n">
-        <v>88.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-70.29000000000001</v>
+        <v>170.6</v>
       </c>
       <c r="K73" t="n">
-        <v>208.1</v>
+        <v>-15.74</v>
       </c>
       <c r="L73" t="n">
-        <v>219.65</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:38:46</t>
+          <t>10:38:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="F74" t="n">
         <v>6.55</v>
       </c>
       <c r="G74" t="n">
-        <v>119.8</v>
+        <v>137.3</v>
       </c>
       <c r="H74" t="n">
-        <v>80</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>38.79</v>
+        <v>41.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-15.7</v>
+        <v>29.85</v>
       </c>
       <c r="L74" t="n">
-        <v>41.84</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:40:37</t>
+          <t>10:40:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="F75" t="n">
-        <v>6.05</v>
+        <v>4.72</v>
       </c>
       <c r="G75" t="n">
-        <v>136</v>
+        <v>127.9</v>
       </c>
       <c r="H75" t="n">
-        <v>92.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>47.68</v>
+        <v>22.23</v>
       </c>
       <c r="K75" t="n">
-        <v>8.19</v>
+        <v>-7.28</v>
       </c>
       <c r="L75" t="n">
-        <v>48.38</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:42:37</t>
+          <t>10:42:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="F76" t="n">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="G76" t="n">
-        <v>135.6</v>
+        <v>140.6</v>
       </c>
       <c r="H76" t="n">
-        <v>53.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.61</v>
+        <v>-25.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.51</v>
+        <v>29.1</v>
       </c>
       <c r="L76" t="n">
-        <v>44.16</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:46:35</t>
+          <t>10:46:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="F77" t="n">
-        <v>4.13</v>
+        <v>6.55</v>
       </c>
       <c r="G77" t="n">
-        <v>124.6</v>
+        <v>132.3</v>
       </c>
       <c r="H77" t="n">
-        <v>89.3</v>
+        <v>55.4</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>18.61</v>
+        <v>-23.67</v>
       </c>
       <c r="K77" t="n">
-        <v>-40.02</v>
+        <v>61.47</v>
       </c>
       <c r="L77" t="n">
-        <v>44.13</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:47:52</t>
+          <t>10:48:55</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="F78" t="n">
-        <v>3.29</v>
+        <v>6.55</v>
       </c>
       <c r="G78" t="n">
-        <v>134.7</v>
+        <v>147.8</v>
       </c>
       <c r="H78" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-51.83</v>
+        <v>-36.22</v>
       </c>
       <c r="K78" t="n">
-        <v>0.49</v>
+        <v>30.93</v>
       </c>
       <c r="L78" t="n">
-        <v>51.83</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:49:07</t>
+          <t>10:49:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="F79" t="n">
-        <v>2.54</v>
+        <v>4.99</v>
       </c>
       <c r="G79" t="n">
-        <v>137.5</v>
+        <v>147.8</v>
       </c>
       <c r="H79" t="n">
-        <v>81.3</v>
+        <v>61.8</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>28.86</v>
+        <v>-53.64</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.14</v>
+        <v>-14.73</v>
       </c>
       <c r="L79" t="n">
-        <v>56.99</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:53:47</t>
+          <t>10:53:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="F80" t="n">
-        <v>4.78</v>
+        <v>6.55</v>
       </c>
       <c r="G80" t="n">
-        <v>128.4</v>
+        <v>142.5</v>
       </c>
       <c r="H80" t="n">
-        <v>28.4</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>21.09</v>
+        <v>-58.03</v>
       </c>
       <c r="K80" t="n">
-        <v>89.12</v>
+        <v>-39.7</v>
       </c>
       <c r="L80" t="n">
-        <v>91.59</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:55:44</t>
+          <t>10:56:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="F81" t="n">
-        <v>6.55</v>
+        <v>5.59</v>
       </c>
       <c r="G81" t="n">
-        <v>136.2</v>
+        <v>136.8</v>
       </c>
       <c r="H81" t="n">
-        <v>84.40000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>64.37</v>
+        <v>103.32</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.78</v>
+        <v>19.97</v>
       </c>
       <c r="L81" t="n">
-        <v>74.64</v>
+        <v>105.23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:57:15</t>
+          <t>10:57:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="F82" t="n">
         <v>6.55</v>
       </c>
       <c r="G82" t="n">
-        <v>143.4</v>
+        <v>136.8</v>
       </c>
       <c r="H82" t="n">
-        <v>81.5</v>
+        <v>60.4</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>24.78</v>
+        <v>-24.02</v>
       </c>
       <c r="K82" t="n">
-        <v>-90.7</v>
+        <v>-56.74</v>
       </c>
       <c r="L82" t="n">
-        <v>94.02</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:01:32</t>
+          <t>11:01:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="F83" t="n">
-        <v>6.47</v>
+        <v>6.55</v>
       </c>
       <c r="G83" t="n">
-        <v>140.5</v>
+        <v>129.2</v>
       </c>
       <c r="H83" t="n">
-        <v>58.6</v>
+        <v>55.3</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>14.52</v>
+        <v>-122.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-166.54</v>
+        <v>-100.49</v>
       </c>
       <c r="L83" t="n">
-        <v>167.17</v>
+        <v>158.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:02:15</t>
+          <t>11:03:13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>2.14</v>
       </c>
       <c r="F84" t="n">
-        <v>5.08</v>
+        <v>6.46</v>
       </c>
       <c r="G84" t="n">
-        <v>135.8</v>
+        <v>131.3</v>
       </c>
       <c r="H84" t="n">
-        <v>32.8</v>
+        <v>81.5</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>67.61</v>
+        <v>-37.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-158.52</v>
+        <v>-124.51</v>
       </c>
       <c r="L84" t="n">
-        <v>172.34</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:04:22</t>
+          <t>11:04:21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="F85" t="n">
         <v>6.55</v>
       </c>
       <c r="G85" t="n">
-        <v>118.3</v>
+        <v>143.6</v>
       </c>
       <c r="H85" t="n">
-        <v>58.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>136.5</v>
+        <v>-138.07</v>
       </c>
       <c r="K85" t="n">
-        <v>14.14</v>
+        <v>-114.76</v>
       </c>
       <c r="L85" t="n">
-        <v>137.23</v>
+        <v>179.54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:08:56</t>
+          <t>11:07:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="F86" t="n">
-        <v>6.55</v>
+        <v>5.94</v>
       </c>
       <c r="G86" t="n">
-        <v>135.6</v>
+        <v>125.8</v>
       </c>
       <c r="H86" t="n">
-        <v>66.8</v>
+        <v>49.9</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-76.37</v>
+        <v>-145.49</v>
       </c>
       <c r="K86" t="n">
-        <v>-274.69</v>
+        <v>130.8</v>
       </c>
       <c r="L86" t="n">
-        <v>285.11</v>
+        <v>195.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:10:56</t>
+          <t>11:10:15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="F87" t="n">
         <v>6.55</v>
       </c>
       <c r="G87" t="n">
-        <v>142.2</v>
+        <v>148</v>
       </c>
       <c r="H87" t="n">
-        <v>82.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>181.51</v>
+        <v>-128.29</v>
       </c>
       <c r="K87" t="n">
-        <v>33.58</v>
+        <v>-70.44</v>
       </c>
       <c r="L87" t="n">
-        <v>184.59</v>
+        <v>146.35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:12:09</t>
+          <t>11:11:54</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="F88" t="n">
-        <v>4.44</v>
+        <v>6.55</v>
       </c>
       <c r="G88" t="n">
-        <v>138.8</v>
+        <v>117.4</v>
       </c>
       <c r="H88" t="n">
-        <v>39.5</v>
+        <v>70.7</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>96.23999999999999</v>
+        <v>-176.27</v>
       </c>
       <c r="K88" t="n">
-        <v>164.43</v>
+        <v>31.54</v>
       </c>
       <c r="L88" t="n">
-        <v>190.52</v>
+        <v>179.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-07.xlsx
+++ b/output/2024-10-07.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.57</v>
+        <v>-12.75</v>
       </c>
       <c r="K14" t="n">
-        <v>-34.27</v>
+        <v>-41.31</v>
       </c>
       <c r="L14" t="n">
-        <v>35.86</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>29.11</v>
+        <v>32.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.91</v>
+        <v>-38.86</v>
       </c>
       <c r="L15" t="n">
-        <v>45.45</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>42.22</v>
+        <v>46.56</v>
       </c>
       <c r="K16" t="n">
-        <v>12.43</v>
+        <v>13.71</v>
       </c>
       <c r="L16" t="n">
-        <v>44.01</v>
+        <v>48.54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-10</v>
+        <v>-10.41</v>
       </c>
       <c r="K17" t="n">
-        <v>-81.97</v>
+        <v>-85.37</v>
       </c>
       <c r="L17" t="n">
-        <v>82.58</v>
+        <v>86.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.99</v>
+        <v>-51.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.17</v>
+        <v>-35.6</v>
       </c>
       <c r="L18" t="n">
-        <v>53.34</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>28.95</v>
+        <v>34.03</v>
       </c>
       <c r="K19" t="n">
-        <v>-36.23</v>
+        <v>-42.59</v>
       </c>
       <c r="L19" t="n">
-        <v>46.38</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>61.38</v>
+        <v>74.37</v>
       </c>
       <c r="K20" t="n">
-        <v>-46.33</v>
+        <v>-56.13</v>
       </c>
       <c r="L20" t="n">
-        <v>76.90000000000001</v>
+        <v>93.17</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-31.46</v>
+        <v>-36.86</v>
       </c>
       <c r="K21" t="n">
-        <v>77.11</v>
+        <v>90.34</v>
       </c>
       <c r="L21" t="n">
-        <v>83.28</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-82.06</v>
+        <v>-93.73</v>
       </c>
       <c r="K22" t="n">
-        <v>50.47</v>
+        <v>57.65</v>
       </c>
       <c r="L22" t="n">
-        <v>96.34</v>
+        <v>110.05</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-75.91</v>
+        <v>-86.72</v>
       </c>
       <c r="K23" t="n">
-        <v>-123.76</v>
+        <v>-141.39</v>
       </c>
       <c r="L23" t="n">
-        <v>145.18</v>
+        <v>165.87</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>96.87</v>
+        <v>115.83</v>
       </c>
       <c r="K24" t="n">
-        <v>90.53</v>
+        <v>108.26</v>
       </c>
       <c r="L24" t="n">
-        <v>132.59</v>
+        <v>158.54</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>41.93</v>
+        <v>48.75</v>
       </c>
       <c r="K25" t="n">
-        <v>-136.55</v>
+        <v>-158.78</v>
       </c>
       <c r="L25" t="n">
-        <v>142.84</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>113.46</v>
+        <v>149.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-83.81</v>
+        <v>-110.26</v>
       </c>
       <c r="L26" t="n">
-        <v>141.06</v>
+        <v>185.59</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-29.38</v>
+        <v>-39.69</v>
       </c>
       <c r="K27" t="n">
-        <v>-135.04</v>
+        <v>-182.43</v>
       </c>
       <c r="L27" t="n">
-        <v>138.2</v>
+        <v>186.7</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>24.94</v>
+        <v>31.99</v>
       </c>
       <c r="K28" t="n">
-        <v>-180.83</v>
+        <v>-231.92</v>
       </c>
       <c r="L28" t="n">
-        <v>182.54</v>
+        <v>234.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>24.13</v>
+        <v>27.22</v>
       </c>
       <c r="K29" t="n">
-        <v>31.98</v>
+        <v>36.08</v>
       </c>
       <c r="L29" t="n">
-        <v>40.07</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.27</v>
+        <v>-0.32</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.52</v>
+        <v>-19.97</v>
       </c>
       <c r="L30" t="n">
-        <v>16.52</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>36.53</v>
+        <v>38.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.74</v>
+        <v>-42.99</v>
       </c>
       <c r="L31" t="n">
-        <v>54.72</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>28.74</v>
+        <v>30.84</v>
       </c>
       <c r="K32" t="n">
-        <v>-71.43000000000001</v>
+        <v>-76.65000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>76.98999999999999</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6</v>
+        <v>-0.72</v>
       </c>
       <c r="K33" t="n">
-        <v>-42.98</v>
+        <v>-52.31</v>
       </c>
       <c r="L33" t="n">
-        <v>42.99</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.43</v>
+        <v>-34.24</v>
       </c>
       <c r="K34" t="n">
-        <v>-56.4</v>
+        <v>-65.61</v>
       </c>
       <c r="L34" t="n">
-        <v>63.62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.49</v>
+        <v>-27.59</v>
       </c>
       <c r="K35" t="n">
-        <v>31.55</v>
+        <v>40.5</v>
       </c>
       <c r="L35" t="n">
-        <v>38.17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>44.56</v>
+        <v>56.89</v>
       </c>
       <c r="K36" t="n">
-        <v>-48.07</v>
+        <v>-61.37</v>
       </c>
       <c r="L36" t="n">
-        <v>65.54000000000001</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-99.34999999999999</v>
+        <v>-112.2</v>
       </c>
       <c r="K37" t="n">
-        <v>65.64</v>
+        <v>74.14</v>
       </c>
       <c r="L37" t="n">
-        <v>119.08</v>
+        <v>134.48</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-64.14</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>84.31</v>
+        <v>103.1</v>
       </c>
       <c r="L38" t="n">
-        <v>105.94</v>
+        <v>129.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-44.81</v>
+        <v>-52.16</v>
       </c>
       <c r="K39" t="n">
-        <v>133.15</v>
+        <v>154.98</v>
       </c>
       <c r="L39" t="n">
-        <v>140.49</v>
+        <v>163.52</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>114.08</v>
+        <v>132.84</v>
       </c>
       <c r="K40" t="n">
-        <v>-74.78</v>
+        <v>-87.08</v>
       </c>
       <c r="L40" t="n">
-        <v>136.41</v>
+        <v>158.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-192.59</v>
+        <v>-238.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.54</v>
+        <v>-22.99</v>
       </c>
       <c r="L41" t="n">
-        <v>193.48</v>
+        <v>239.9</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>147.95</v>
+        <v>185.6</v>
       </c>
       <c r="K42" t="n">
-        <v>-91.13</v>
+        <v>-114.31</v>
       </c>
       <c r="L42" t="n">
-        <v>173.76</v>
+        <v>217.98</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>96.18000000000001</v>
+        <v>113.42</v>
       </c>
       <c r="K43" t="n">
-        <v>-215.7</v>
+        <v>-254.36</v>
       </c>
       <c r="L43" t="n">
-        <v>236.17</v>
+        <v>278.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.58</v>
+        <v>-2.61</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.14</v>
+        <v>-60.98</v>
       </c>
       <c r="L44" t="n">
-        <v>60.2</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.59</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.84</v>
+        <v>-43.55</v>
       </c>
       <c r="L45" t="n">
-        <v>38.8</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.49</v>
+        <v>-15.68</v>
       </c>
       <c r="K46" t="n">
-        <v>32.82</v>
+        <v>38.15</v>
       </c>
       <c r="L46" t="n">
-        <v>35.48</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.47</v>
+        <v>-48.17</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.8</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>41.21</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="K48" t="n">
-        <v>95.98</v>
+        <v>96.11</v>
       </c>
       <c r="L48" t="n">
-        <v>108.22</v>
+        <v>108.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>33.03</v>
+        <v>37.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.03</v>
+        <v>-54.8</v>
       </c>
       <c r="L49" t="n">
-        <v>58.29</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>40.75</v>
+        <v>50.87</v>
       </c>
       <c r="K50" t="n">
-        <v>47.81</v>
+        <v>59.68</v>
       </c>
       <c r="L50" t="n">
-        <v>62.82</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>10.51</v>
+        <v>13.29</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.09</v>
+        <v>-16.55</v>
       </c>
       <c r="L51" t="n">
-        <v>16.79</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.47</v>
+        <v>-88.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-19.73</v>
+        <v>-24.08</v>
       </c>
       <c r="L52" t="n">
-        <v>75.11</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-110.13</v>
+        <v>-127.33</v>
       </c>
       <c r="K53" t="n">
-        <v>-93.26000000000001</v>
+        <v>-107.83</v>
       </c>
       <c r="L53" t="n">
-        <v>144.31</v>
+        <v>166.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-77.62</v>
+        <v>-99.73</v>
       </c>
       <c r="K54" t="n">
-        <v>-57.01</v>
+        <v>-73.25</v>
       </c>
       <c r="L54" t="n">
-        <v>96.3</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>148.74</v>
+        <v>169.1</v>
       </c>
       <c r="K55" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="L55" t="n">
-        <v>148.75</v>
+        <v>169.11</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>10.5</v>
+        <v>14.15</v>
       </c>
       <c r="K56" t="n">
-        <v>-135.49</v>
+        <v>-182.68</v>
       </c>
       <c r="L56" t="n">
-        <v>135.9</v>
+        <v>183.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>114.49</v>
+        <v>141.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-153.25</v>
+        <v>-188.8</v>
       </c>
       <c r="L57" t="n">
-        <v>191.3</v>
+        <v>235.67</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-148.81</v>
+        <v>-191.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-58.35</v>
+        <v>-75.08</v>
       </c>
       <c r="L58" t="n">
-        <v>159.84</v>
+        <v>205.67</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>35.15</v>
+        <v>35.95</v>
       </c>
       <c r="K59" t="n">
-        <v>40.73</v>
+        <v>41.66</v>
       </c>
       <c r="L59" t="n">
-        <v>53.8</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>16.16</v>
+        <v>17.01</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.85</v>
+        <v>-53.52</v>
       </c>
       <c r="L60" t="n">
-        <v>53.36</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>12.87</v>
+        <v>15.24</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.79</v>
+        <v>-25.81</v>
       </c>
       <c r="L61" t="n">
-        <v>25.31</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-55.73</v>
+        <v>-65.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-11.17</v>
+        <v>-13.2</v>
       </c>
       <c r="L62" t="n">
-        <v>56.84</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>94.16</v>
+        <v>99.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.93</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>94.48999999999999</v>
+        <v>99.93000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>23.78</v>
+        <v>26.97</v>
       </c>
       <c r="K64" t="n">
-        <v>61.11</v>
+        <v>69.33</v>
       </c>
       <c r="L64" t="n">
-        <v>65.56999999999999</v>
+        <v>74.39</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>57.3</v>
+        <v>73.19</v>
       </c>
       <c r="K65" t="n">
-        <v>24.8</v>
+        <v>31.68</v>
       </c>
       <c r="L65" t="n">
-        <v>62.43</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-71.84999999999999</v>
+        <v>-85.68000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>33.33</v>
+        <v>39.75</v>
       </c>
       <c r="L66" t="n">
-        <v>79.2</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.12</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>12.99</v>
+        <v>15.05</v>
       </c>
       <c r="L67" t="n">
-        <v>86.09999999999999</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>98.18000000000001</v>
+        <v>119.46</v>
       </c>
       <c r="K68" t="n">
-        <v>36.2</v>
+        <v>44.04</v>
       </c>
       <c r="L68" t="n">
-        <v>104.64</v>
+        <v>127.32</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-57.73</v>
+        <v>-65.64</v>
       </c>
       <c r="K69" t="n">
-        <v>151.85</v>
+        <v>172.65</v>
       </c>
       <c r="L69" t="n">
-        <v>162.46</v>
+        <v>184.71</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.95</v>
+        <v>-2.25</v>
       </c>
       <c r="K70" t="n">
-        <v>134.19</v>
+        <v>155.31</v>
       </c>
       <c r="L70" t="n">
-        <v>134.2</v>
+        <v>155.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>66.08</v>
+        <v>91.22</v>
       </c>
       <c r="K71" t="n">
-        <v>-105.31</v>
+        <v>-145.38</v>
       </c>
       <c r="L71" t="n">
-        <v>124.33</v>
+        <v>171.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-105.58</v>
+        <v>-140.3</v>
       </c>
       <c r="K72" t="n">
-        <v>95.27</v>
+        <v>126.61</v>
       </c>
       <c r="L72" t="n">
-        <v>142.21</v>
+        <v>188.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-159.15</v>
+        <v>-195.76</v>
       </c>
       <c r="K73" t="n">
-        <v>80.93000000000001</v>
+        <v>99.55</v>
       </c>
       <c r="L73" t="n">
-        <v>178.54</v>
+        <v>219.62</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-28.25</v>
+        <v>-30.8</v>
       </c>
       <c r="K74" t="n">
-        <v>30.27</v>
+        <v>33</v>
       </c>
       <c r="L74" t="n">
-        <v>41.4</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>12.26</v>
+        <v>13.87</v>
       </c>
       <c r="K75" t="n">
-        <v>35.59</v>
+        <v>40.28</v>
       </c>
       <c r="L75" t="n">
-        <v>37.64</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>60.31</v>
+        <v>61.56</v>
       </c>
       <c r="K76" t="n">
-        <v>24.01</v>
+        <v>24.51</v>
       </c>
       <c r="L76" t="n">
-        <v>64.91</v>
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-69.41</v>
+        <v>-74.28</v>
       </c>
       <c r="K77" t="n">
-        <v>36.91</v>
+        <v>39.5</v>
       </c>
       <c r="L77" t="n">
-        <v>78.61</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>5.39</v>
+        <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>-71.81999999999999</v>
+        <v>-79.83</v>
       </c>
       <c r="L78" t="n">
-        <v>72.02</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>10.92</v>
+        <v>11.66</v>
       </c>
       <c r="K79" t="n">
-        <v>84.97</v>
+        <v>90.8</v>
       </c>
       <c r="L79" t="n">
-        <v>85.67</v>
+        <v>91.54000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>91.42</v>
+        <v>109.92</v>
       </c>
       <c r="K80" t="n">
-        <v>18.44</v>
+        <v>22.18</v>
       </c>
       <c r="L80" t="n">
-        <v>93.26000000000001</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>82.38</v>
+        <v>97.39</v>
       </c>
       <c r="K81" t="n">
-        <v>-10.5</v>
+        <v>-12.41</v>
       </c>
       <c r="L81" t="n">
-        <v>83.04000000000001</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-105.14</v>
+        <v>-120.37</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.24</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>105.39</v>
+        <v>120.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-45.35</v>
+        <v>-60.2</v>
       </c>
       <c r="K83" t="n">
-        <v>103.84</v>
+        <v>137.84</v>
       </c>
       <c r="L83" t="n">
-        <v>113.31</v>
+        <v>150.41</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>52.47</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>93.17</v>
+        <v>116.94</v>
       </c>
       <c r="L84" t="n">
-        <v>106.93</v>
+        <v>134.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>48.08</v>
+        <v>55.05</v>
       </c>
       <c r="K85" t="n">
-        <v>135.37</v>
+        <v>155.01</v>
       </c>
       <c r="L85" t="n">
-        <v>143.66</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>93.29000000000001</v>
+        <v>115.31</v>
       </c>
       <c r="K86" t="n">
-        <v>144.67</v>
+        <v>178.81</v>
       </c>
       <c r="L86" t="n">
-        <v>172.14</v>
+        <v>212.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-101.17</v>
+        <v>-128.92</v>
       </c>
       <c r="K87" t="n">
-        <v>144.78</v>
+        <v>184.49</v>
       </c>
       <c r="L87" t="n">
-        <v>176.63</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>68.84999999999999</v>
+        <v>94.36</v>
       </c>
       <c r="K88" t="n">
-        <v>-120.57</v>
+        <v>-165.26</v>
       </c>
       <c r="L88" t="n">
-        <v>138.84</v>
+        <v>190.3</v>
       </c>
     </row>
   </sheetData>
